--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25360000-2B95-409D-964E-72DABA07B83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AA8CFE-484A-49B6-B6D4-987D4B4148E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
+    <sheet name="Unit Sheets" sheetId="4" r:id="rId2"/>
+    <sheet name="Policy Tree" sheetId="3" r:id="rId3"/>
+    <sheet name="Locations" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="270">
   <si>
     <t>Line1</t>
   </si>
@@ -411,18 +412,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Scout/Skirmisher</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Close Combat/Assult</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Ranged Combat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Siege</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1052,6 +1045,62 @@
   </si>
   <si>
     <t>Barn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranged Combat/Skirmisher</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scout/Scavengers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Administration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Early Military</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self-Sustain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tinkering</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scavenge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Late Game</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spring</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Summer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Autumn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winter</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1059,7 +1108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1094,12 +1143,51 @@
     <font>
       <sz val="11"/>
       <name val="等线"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1200,49 +1288,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1261,7 +1313,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
@@ -1273,29 +1325,101 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1611,393 +1735,424 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
-  <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultColWidth="17.25" defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr defaultColWidth="19.625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="19.625" style="24"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30" t="s">
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30" t="s">
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-    </row>
-    <row r="2" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+    </row>
+    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" s="24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24">
         <v>3</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="4" t="s">
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="26"/>
-    </row>
-    <row r="4" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="29"/>
+    </row>
+    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="24">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="E4" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
+      <c r="G4" s="26"/>
+      <c r="H4" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="4" t="s">
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="24" t="s">
+      <c r="M4" s="27"/>
+      <c r="N4" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-    </row>
-    <row r="5" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+    </row>
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="24">
         <v>5</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="4" t="s">
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4" t="s">
+      <c r="N5" s="27"/>
+      <c r="O5" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="P5" s="25" t="s">
+      <c r="P5" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="Q5" s="26"/>
-    </row>
-    <row r="6" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="Q5" s="29"/>
+    </row>
+    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="24">
         <v>6</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="32"/>
+      <c r="F6" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="32"/>
+      <c r="H6" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="13" t="s">
+      <c r="I6" s="33"/>
+      <c r="J6" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4" t="s">
+      <c r="L6" s="33"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-    </row>
-    <row r="7" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="O6" s="27"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+    </row>
+    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="s">
+      <c r="F7" s="32"/>
+      <c r="G7" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
+      <c r="H7" s="33"/>
+      <c r="I7" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4" t="s">
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="29" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="P7" s="29"/>
+      <c r="Q7" s="37" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="24">
         <v>8</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="E8" s="32"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8" t="s">
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="25" t="s">
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="Q8" s="26"/>
-    </row>
-    <row r="9" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="Q8" s="29"/>
+    </row>
+    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="24">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="11" t="s">
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="11" t="s">
+      <c r="K9" s="40"/>
+      <c r="L9" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8" t="s">
+      <c r="M9" s="40"/>
+      <c r="N9" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-    </row>
-    <row r="10" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+    </row>
+    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="24">
         <v>10</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="s">
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="8" t="s">
+      <c r="I10" s="41"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="25" t="s">
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="Q10" s="26"/>
-    </row>
-    <row r="11" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="Q10" s="29"/>
+    </row>
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="24">
         <v>11</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7" t="s">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="38"/>
+      <c r="G11" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="38"/>
+      <c r="I11" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8" t="s">
+      <c r="J11" s="43"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+    </row>
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>258</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2016,261 +2171,264 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultColWidth="18.125" defaultRowHeight="48" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="18.125" style="15"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
+      <c r="B1" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="I1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" t="s">
-        <v>120</v>
-      </c>
-      <c r="K1" t="s">
-        <v>135</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="B4" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I2" t="s">
-        <v>241</v>
-      </c>
-      <c r="J2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" t="s">
-        <v>131</v>
-      </c>
-      <c r="L3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" t="s">
-        <v>127</v>
-      </c>
-      <c r="L7" t="s">
-        <v>133</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="E18" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="F9" t="s">
-        <v>130</v>
-      </c>
-      <c r="L9" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+    <row r="19" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="L13" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+    </row>
+    <row r="24" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="18" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
+    <row r="25" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="22" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
+    <row r="26" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="23" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25" t="s">
-        <v>118</v>
-      </c>
-    </row>
     <row r="28" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="23" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2289,320 +2447,320 @@
       <c r="A1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="31" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="G2" s="19" t="s">
+      <c r="F2" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
         <v>171</v>
       </c>
-      <c r="J2" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="C4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="F4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="I4" t="s">
+        <v>209</v>
+      </c>
+      <c r="J4" t="s">
+        <v>210</v>
+      </c>
+      <c r="K4" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="M4" t="s">
+        <v>226</v>
+      </c>
+      <c r="N4" t="s">
+        <v>228</v>
+      </c>
+      <c r="O4" t="s">
+        <v>234</v>
+      </c>
+      <c r="P4" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="G5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="K5" t="s">
+        <v>219</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3" s="28" t="s">
+      <c r="C6" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="M3" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="N3" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="O3" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="P3" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q3" s="28" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="I4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="E7" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="H7" t="s">
+        <v>202</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="K4" t="s">
-        <v>220</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="M4" t="s">
-        <v>228</v>
-      </c>
-      <c r="N4" t="s">
-        <v>230</v>
-      </c>
-      <c r="O4" t="s">
-        <v>236</v>
-      </c>
-      <c r="P4" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" t="s">
-        <v>200</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="I5" t="s">
-        <v>208</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="K5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L5" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="N5" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="O5" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="P5" s="28" t="s">
+      <c r="P7" s="12" t="s">
         <v>246</v>
-      </c>
-      <c r="Q5" s="28" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="L6" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="N6" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="O6" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="P6" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q6" s="28" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="H7" t="s">
-        <v>204</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="P7" s="28" t="s">
-        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -2624,139 +2782,164 @@
   <sheetData>
     <row r="1" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" t="s">
         <v>149</v>
       </c>
-      <c r="C1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>150</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1" t="s">
         <v>151</v>
       </c>
-      <c r="H1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J1" t="s">
-        <v>155</v>
-      </c>
-      <c r="K1" t="s">
-        <v>153</v>
-      </c>
       <c r="L1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" t="s">
         <v>156</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>157</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>157</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>158</v>
       </c>
-      <c r="F2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H2" t="s">
-        <v>160</v>
-      </c>
       <c r="L2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" t="s">
         <v>162</v>
       </c>
-      <c r="B4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" t="s">
-        <v>164</v>
-      </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M4" t="s">
-        <v>163</v>
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="34.5" defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05440E8-286B-4B9C-8445-2964A46AB9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B63912-0AD5-41DF-812B-02E733BA1629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
     <sheet name="Building Sheets" sheetId="9" r:id="rId2"/>
     <sheet name="Unit Sheets" sheetId="4" r:id="rId3"/>
-    <sheet name="Policy Tree" sheetId="3" r:id="rId4"/>
-    <sheet name="Locations(RES)" sheetId="5" r:id="rId5"/>
-    <sheet name="C.Mechanics" sheetId="6" r:id="rId6"/>
-    <sheet name="U.Mechanics" sheetId="8" r:id="rId7"/>
+    <sheet name="Promotion" sheetId="10" r:id="rId4"/>
+    <sheet name="Policy Tree" sheetId="3" r:id="rId5"/>
+    <sheet name="Locations(RES)" sheetId="5" r:id="rId6"/>
+    <sheet name="C.Mechanics" sheetId="6" r:id="rId7"/>
+    <sheet name="U.Mechanics" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="469">
   <si>
     <t>Line1</t>
   </si>
@@ -402,1063 +403,1272 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Defenders/Engineers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Close Combat Ship</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gunboat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Mobilization 2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Search Party 3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makeshift Weapons 4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Army 5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>River Patrol 6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Permanent Structure8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makeshift Vehicle9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vehicle Patrol10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cement7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grid Rebuild11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demolition12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Makeshift Artillery13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Standardization14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heavy Vehicles15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slow Zombies</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fast Zombies</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Humanity's Journey0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armed Civilian</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mechanized Infantry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armed Fishing Boat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Police Partrol</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pike Militia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scout Squad</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Molotov Squad</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Search Squad</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arsenal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defence Building/ Military building</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Promotion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Motar Squad</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coastal Guard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tercio Militia</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recon Squad</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military Industry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rifle Infantry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cold Storage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parking Slot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supermarket</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suburb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Apartment</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military Check Point</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clinic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hospital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medic Res</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scavange Target</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guns</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scrap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PPP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resource</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military Base</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monarchy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parliaments</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Regrouping</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Post-apacolapse Tech</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reinforced Militia Group</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commisars</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retreat from the Horde</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forage from the Wild</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strike from the Dark</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Tactics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Revenge to the Damned</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maintain the Morale</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abolish all Private Properties</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self-Sufficiency</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decentralisation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monopoly Over Essentials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Newest Testament</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enforce Public Ownership</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Size the Means of Production</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industrial Plans</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>National Guards</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Order Restored</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For the Humanity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For the Leader</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cleansing the World</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Missionary Works</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Church Authority</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Nobilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Royal Guards</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lines of Heritage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Land Distribution</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Laissez-faire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obligarchy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>An-cap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Privatised Security</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Long Live the King</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Town Expansion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agricultral Focus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Traditions</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Building the New World</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Everything will be Fine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Understanding and Acceptance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Against the Depraved</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interstate Support</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exchange of Knowledge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>State Purity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strict Border Control</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inpeccable Defence</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Blood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disinfectancy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Grand Reclaimation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ashes to Ashes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Secret Police</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hostile Takeover</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Infected Masses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special Infected</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armored Car</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore Power</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore Water</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore Agriculture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Out of the hell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Federation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gather the Force</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gather the Will</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Independence Day</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7Humanity's Journey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military Survivor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Structure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruined Factory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Barn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranged Combat/Skirmisher</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scout/Scavengers</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Administration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Early Military</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self-Sustain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tinkering</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scavenge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Late Game</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spring</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Summer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Autumn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>FPG</t>
+  </si>
+  <si>
+    <t>Stats</t>
+  </si>
+  <si>
+    <t>Ranger Squad</t>
+  </si>
+  <si>
+    <t>Junk Walls</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Barrack</t>
+  </si>
+  <si>
+    <t>Melee Militia</t>
+  </si>
+  <si>
+    <t>Tank</t>
+  </si>
+  <si>
+    <t>Technical</t>
+  </si>
+  <si>
+    <t>Killdozer</t>
+  </si>
+  <si>
+    <t>Deck Jumping Crew</t>
+  </si>
+  <si>
+    <t>Longbowmen</t>
+  </si>
+  <si>
+    <t>Summon Extra Armed Civilians/Water Units</t>
+  </si>
+  <si>
+    <t>Cannon Boat</t>
+  </si>
+  <si>
+    <t>Munition Factory</t>
+  </si>
+  <si>
+    <t>Sappers</t>
+  </si>
+  <si>
+    <t>Mechanized Infantry/Armored Train</t>
+  </si>
+  <si>
+    <t>Info Squad</t>
+  </si>
+  <si>
+    <t>Great Wars Infantry</t>
+  </si>
+  <si>
+    <t>Marksman</t>
+  </si>
+  <si>
+    <t>Sharpshooter</t>
+  </si>
+  <si>
+    <t>Warship</t>
+  </si>
+  <si>
+    <t>Electrified Wall/Moat</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Chop Shop</t>
+  </si>
+  <si>
+    <t>Weapon Factory</t>
+  </si>
+  <si>
+    <t>Explodsive Plant</t>
+  </si>
+  <si>
+    <t>Caller</t>
+  </si>
+  <si>
+    <t>Horde Mother</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Drone Bomber</t>
+  </si>
+  <si>
+    <t>Technical Fromation</t>
+  </si>
+  <si>
+    <t>Assult Infantry</t>
+  </si>
+  <si>
+    <t>Assult Militia</t>
+  </si>
+  <si>
+    <t>Hunters</t>
+  </si>
+  <si>
+    <t>Turret Ship</t>
+  </si>
+  <si>
+    <t>Beasts of Destruction</t>
+  </si>
+  <si>
+    <t>Sledge Squad</t>
+  </si>
+  <si>
+    <t>Mechanic Shop</t>
+  </si>
+  <si>
+    <t>Contaminator</t>
+  </si>
+  <si>
+    <t>Nothing Against the Unity</t>
+  </si>
+  <si>
+    <t>Need a lot of work in fields</t>
+  </si>
+  <si>
+    <t>Best Season for Hunting/Foraging</t>
+  </si>
+  <si>
+    <t>Need Food Storage and Fuel to survive</t>
+  </si>
+  <si>
+    <t>Major Food Production Season</t>
+  </si>
+  <si>
+    <t>less settlements more work range</t>
+  </si>
+  <si>
+    <t>Scale &amp; Theme</t>
+  </si>
+  <si>
+    <t>A shit ton of barbarian units(Zombis) that can be defeated using varied tactics</t>
+  </si>
+  <si>
+    <t>Shoot em wack em trap em blow em</t>
+  </si>
+  <si>
+    <t>Gas Station</t>
+  </si>
+  <si>
+    <t>Fuel</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>PPG</t>
+  </si>
+  <si>
+    <t>G.V.Force</t>
+  </si>
+  <si>
+    <t>Trust in Gov</t>
+  </si>
+  <si>
+    <t>Agricultural</t>
+  </si>
+  <si>
+    <t>Infrastructural</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Governance</t>
+  </si>
+  <si>
+    <t>Cultural/Religious</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Enable Enact Policy &amp; Foraging</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Confederacy</t>
+  </si>
+  <si>
+    <t>Worker</t>
+  </si>
+  <si>
+    <t>HEMA club</t>
+  </si>
+  <si>
+    <t>J.Witness</t>
+  </si>
+  <si>
+    <t>Gang</t>
+  </si>
+  <si>
+    <t>Hackers</t>
+  </si>
+  <si>
+    <t>Housing</t>
+  </si>
+  <si>
+    <t>Shelter</t>
+  </si>
+  <si>
+    <t>Camp Fire</t>
+  </si>
+  <si>
+    <t>First Scavenge/Foraging/Census</t>
+  </si>
+  <si>
+    <t>Car Graveyard/Scrap Workshop</t>
+  </si>
+  <si>
+    <t>Seed Collection</t>
+  </si>
+  <si>
+    <t>Wooden Wall/Settlement Patrol</t>
+  </si>
+  <si>
+    <t>Irrigation System</t>
+  </si>
+  <si>
+    <t>Smeltry/Carpentry House</t>
+  </si>
+  <si>
+    <t>Fishing Port</t>
+  </si>
+  <si>
+    <t>Water Tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting off </t>
+  </si>
+  <si>
+    <t>Scavenge Priority</t>
+  </si>
+  <si>
+    <t>Intergration</t>
+  </si>
+  <si>
+    <t>Granary/Smokery</t>
+  </si>
+  <si>
+    <t>Trading Hub/Market</t>
+  </si>
+  <si>
+    <t>Road System</t>
+  </si>
+  <si>
+    <t>Carpentry</t>
+  </si>
+  <si>
+    <t>Tinkery</t>
+  </si>
+  <si>
+    <t>Vehicle Construction Yard</t>
+  </si>
+  <si>
+    <t>Torpedo Boat</t>
+  </si>
+  <si>
+    <t>Howitzer/AB Gun</t>
+  </si>
+  <si>
+    <t>Zepplin Mothership</t>
+  </si>
+  <si>
+    <t>Bunkers</t>
+  </si>
+  <si>
+    <t>Artillery Position</t>
+  </si>
+  <si>
+    <t>Ramming Ship/Assult Gunboat</t>
+  </si>
+  <si>
+    <t>Airport</t>
+  </si>
+  <si>
+    <t>Drone Workshop</t>
+  </si>
+  <si>
+    <t>Grey Barricade/Moat</t>
+  </si>
+  <si>
+    <t>Training Ground</t>
+  </si>
+  <si>
+    <t>Bonus Against zombies</t>
+  </si>
+  <si>
+    <t>Zombie Dolphin</t>
+  </si>
+  <si>
+    <t>Rusher Horde</t>
+  </si>
+  <si>
+    <t>Hunter Horde</t>
+  </si>
+  <si>
+    <t>Brute</t>
+  </si>
+  <si>
+    <t>Brute Horde</t>
+  </si>
+  <si>
+    <t>Evo Brute</t>
+  </si>
+  <si>
+    <t>Adv.Vehicle Promotion</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>Radio Station</t>
+  </si>
+  <si>
+    <t>Agriculture(Seed required)</t>
+  </si>
+  <si>
+    <t>Wiring(Generator)</t>
+  </si>
+  <si>
+    <t>Cement Plant</t>
+  </si>
+  <si>
+    <t>Hunting Hut</t>
+  </si>
+  <si>
+    <t>Wooden Shack</t>
+  </si>
+  <si>
+    <t>Dormitory</t>
+  </si>
+  <si>
+    <t>Special Political Buildings</t>
+  </si>
+  <si>
+    <t>Chapel</t>
+  </si>
+  <si>
+    <t>Special Distribution System</t>
+  </si>
+  <si>
+    <t>Memorial/Pubs</t>
+  </si>
+  <si>
+    <t>Grid Repair</t>
+  </si>
+  <si>
+    <t>The Generator/Seed</t>
+  </si>
+  <si>
+    <t>Pop Growth Choice</t>
+  </si>
+  <si>
+    <t>Inter-State Comm</t>
+  </si>
+  <si>
+    <t>Education Focus</t>
+  </si>
+  <si>
+    <t>Housing Res Allows for immegrants, which may bring more hostiles</t>
+  </si>
+  <si>
+    <t>scavenge trip may bring random artifacts</t>
+  </si>
+  <si>
+    <t>there maybe talented people in the survivor groups</t>
+  </si>
+  <si>
+    <t>zombie may appear out of nowhere</t>
+  </si>
+  <si>
+    <t>starvation brings desertion</t>
+  </si>
+  <si>
+    <t>Zombie is slower</t>
+  </si>
+  <si>
+    <t>Office Tower</t>
+  </si>
+  <si>
+    <t>Rebuild Option</t>
+  </si>
+  <si>
+    <t>Granary</t>
+  </si>
+  <si>
+    <t>Nope</t>
+  </si>
+  <si>
+    <t>Watchtower</t>
+  </si>
+  <si>
+    <t>Restore</t>
+  </si>
+  <si>
+    <t>Crusade against the unholy</t>
+  </si>
+  <si>
+    <t>Preparation</t>
+  </si>
+  <si>
+    <t>First Conference</t>
+  </si>
+  <si>
+    <t>Revitalised Party System</t>
+  </si>
+  <si>
+    <t>Trap Engineering</t>
+  </si>
+  <si>
+    <t>Army with a State</t>
+  </si>
+  <si>
+    <t>Maximum Work Hours</t>
+  </si>
+  <si>
+    <t>Freedom and Sufferage</t>
+  </si>
+  <si>
+    <t>Base Line Rights</t>
+  </si>
+  <si>
+    <t>Revolution Overdrive</t>
+  </si>
+  <si>
+    <t>Anti-Hierarchy</t>
+  </si>
+  <si>
+    <t>Benevolence for the Chosen</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Immortal Habits</t>
+  </si>
+  <si>
+    <t>Love for Convenience</t>
+  </si>
+  <si>
+    <t>Return Trips</t>
+  </si>
+  <si>
+    <t>S.Caliber</t>
+  </si>
+  <si>
     <t>Siege</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defenders/Engineers</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Close Combat Ship</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Line0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gunboat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total Mobilization 2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Search Party 3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Makeshift Weapons 4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Army 5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>River Patrol 6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Permanent Structure8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Makeshift Vehicle9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vehicle Patrol10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cement7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Grid Rebuild11</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Demolition12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Makeshift Artillery13</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Standardization14</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Heavy Vehicles15</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slow Zombies</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fast Zombies</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Humanity's Journey0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armed Civilian</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mechanized Infantry</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armed Fishing Boat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Police Partrol</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pike Militia</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scout Squad</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Molotov Squad</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Search Squad</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Arsenal</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defence Building/ Military building</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Promotion</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Motar Squad</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coastal Guard</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tercio Militia</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recon Squad</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Military Industry</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rifle Infantry</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cold Storage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Parking Slot</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Supermarket</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suburb</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Apartment</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Military Check Point</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Clinic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hospital</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FF</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>P</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Medic Res</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scavange Target</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Guns</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scrap</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PPP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Resource</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Military Base</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monarchy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Parliaments</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Regrouping</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Post-apacolapse Tech</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reinforced Militia Group</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Commisars</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Retreat from the Horde</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Forage from the Wild</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strike from the Dark</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>New Tactics</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Revenge to the Damned</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maintain the Morale</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Abolish all Private Properties</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self-Sufficiency</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decentralisation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monopoly Over Essentials</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Newest Testament</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enforce Public Ownership</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Size the Means of Production</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Industrial Plans</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>National Guards</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Order Restored</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>For the Humanity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>For the Leader</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cleansing the World</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Missionary Works</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Church Authority</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>New Nobilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Royal Guards</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lines of Heritage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Land Distribution</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Laissez-faire</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Obligarchy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>An-cap</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Privatised Security</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Long Live the King</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Town Expansion</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Agricultral Focus</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>New Traditions</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Building the New World</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Everything will be Fine</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Understanding and Acceptance</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Against the Depraved</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Interstate Support</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exchange of Knowledge</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>State Purity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strict Border Control</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inpeccable Defence</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>New Blood</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Disinfectancy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Grand Reclaimation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ashes to Ashes</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Secret Police</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hostile Takeover</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Infected Masses</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Special Infected</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armored Car</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Restore Power</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Restore Water</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Restore Agriculture</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Out of the hell</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>New Federation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gather the Force</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gather the Will</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Independence Day</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>7Humanity's Journey</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Military Survivor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Structure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruined Factory</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Barn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ranged Combat/Skirmisher</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scout/Scavengers</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>New Administration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Early Military</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Self-Sustain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tinkering</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scavenge</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Military</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Industry</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Late Game</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spring</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Summer</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Autumn</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winter</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>Passive</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>FPG</t>
-  </si>
-  <si>
-    <t>Stats</t>
-  </si>
-  <si>
-    <t>Ranger Squad</t>
-  </si>
-  <si>
-    <t>Junk Walls</t>
-  </si>
-  <si>
-    <t>Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Barrack</t>
-  </si>
-  <si>
-    <t>Melee Militia</t>
-  </si>
-  <si>
-    <t>Tank</t>
-  </si>
-  <si>
-    <t>Technical</t>
-  </si>
-  <si>
-    <t>Killdozer</t>
-  </si>
-  <si>
-    <t>Deck Jumping Crew</t>
-  </si>
-  <si>
-    <t>Longbowmen</t>
-  </si>
-  <si>
-    <t>Summon Extra Armed Civilians/Water Units</t>
-  </si>
-  <si>
-    <t>Cannon Boat</t>
-  </si>
-  <si>
-    <t>Munition Factory</t>
-  </si>
-  <si>
-    <t>Sappers</t>
-  </si>
-  <si>
-    <t>Mechanized Infantry/Armored Train</t>
-  </si>
-  <si>
-    <t>Info Squad</t>
-  </si>
-  <si>
-    <t>Great Wars Infantry</t>
-  </si>
-  <si>
-    <t>Marksman</t>
-  </si>
-  <si>
-    <t>Sharpshooter</t>
-  </si>
-  <si>
-    <t>Advanced Sapper</t>
-  </si>
-  <si>
-    <t>Warship</t>
-  </si>
-  <si>
-    <t>Electrified Wall/Moat</t>
-  </si>
-  <si>
-    <t>Watch Tower</t>
-  </si>
-  <si>
-    <t>Chop Shop</t>
-  </si>
-  <si>
-    <t>Weapon Factory</t>
-  </si>
-  <si>
-    <t>Explodsive Plant</t>
-  </si>
-  <si>
-    <t>Caller</t>
-  </si>
-  <si>
-    <t>Horde Mother</t>
-  </si>
-  <si>
-    <t>Biomass</t>
-  </si>
-  <si>
-    <t>Ranged</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Drone Bomber</t>
-  </si>
-  <si>
-    <t>Technical Fromation</t>
-  </si>
-  <si>
-    <t>Assult Infantry</t>
-  </si>
-  <si>
-    <t>Assult Militia</t>
-  </si>
-  <si>
-    <t>Hunters</t>
-  </si>
-  <si>
-    <t>Turret Ship</t>
-  </si>
-  <si>
-    <t>Beasts of Destruction</t>
-  </si>
-  <si>
-    <t>Sledge Squad</t>
-  </si>
-  <si>
-    <t>Mechanic Shop</t>
-  </si>
-  <si>
-    <t>Contaminator</t>
-  </si>
-  <si>
-    <t>Nothing Against the Unity</t>
-  </si>
-  <si>
-    <t>Need a lot of work in fields</t>
-  </si>
-  <si>
-    <t>Best Season for Hunting/Foraging</t>
-  </si>
-  <si>
-    <t>Need Food Storage and Fuel to survive</t>
-  </si>
-  <si>
-    <t>Major Food Production Season</t>
-  </si>
-  <si>
-    <t>less settlements more work range</t>
-  </si>
-  <si>
-    <t>Scale &amp; Theme</t>
-  </si>
-  <si>
-    <t>A shit ton of barbarian units(Zombis) that can be defeated using varied tactics</t>
-  </si>
-  <si>
-    <t>Shoot em wack em trap em blow em</t>
-  </si>
-  <si>
-    <t>Gas Station</t>
-  </si>
-  <si>
-    <t>Fuel</t>
-  </si>
-  <si>
-    <t>PP</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>PPG</t>
-  </si>
-  <si>
-    <t>G.V.Force</t>
-  </si>
-  <si>
-    <t>Trust in Gov</t>
-  </si>
-  <si>
-    <t>Agricultural</t>
-  </si>
-  <si>
-    <t>Infrastructural</t>
-  </si>
-  <si>
-    <t>Commercial</t>
-  </si>
-  <si>
-    <t>Industrial</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Governance</t>
-  </si>
-  <si>
-    <t>Cultural/Religious</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>Enable Enact Policy &amp; Foraging</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Confederacy</t>
-  </si>
-  <si>
-    <t>Worker</t>
-  </si>
-  <si>
-    <t>HEMA club</t>
-  </si>
-  <si>
-    <t>J.Witness</t>
-  </si>
-  <si>
-    <t>Gang</t>
-  </si>
-  <si>
-    <t>Hackers</t>
-  </si>
-  <si>
-    <t>Housing</t>
-  </si>
-  <si>
-    <t>Shelter</t>
-  </si>
-  <si>
-    <t>Camp Fire</t>
-  </si>
-  <si>
-    <t>First Scavenge/Foraging/Census</t>
-  </si>
-  <si>
-    <t>Car Graveyard/Scrap Workshop</t>
-  </si>
-  <si>
-    <t>Seed Collection</t>
-  </si>
-  <si>
-    <t>Wooden Wall/Settlement Patrol</t>
-  </si>
-  <si>
-    <t>Irrigation System</t>
-  </si>
-  <si>
-    <t>Smeltry/Carpentry House</t>
-  </si>
-  <si>
-    <t>Fishing Port</t>
-  </si>
-  <si>
-    <t>Water Tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starting off </t>
-  </si>
-  <si>
-    <t>Scavenge Priority</t>
-  </si>
-  <si>
-    <t>Intergration</t>
-  </si>
-  <si>
-    <t>Granary/Smokery</t>
-  </si>
-  <si>
-    <t>Trading Hub/Market</t>
-  </si>
-  <si>
-    <t>Road System</t>
-  </si>
-  <si>
-    <t>Carpentry</t>
-  </si>
-  <si>
-    <t>Tinkery</t>
-  </si>
-  <si>
-    <t>Vehicle Construction Yard</t>
-  </si>
-  <si>
-    <t>Torpedo Boat</t>
-  </si>
-  <si>
-    <t>Howitzer/AB Gun</t>
-  </si>
-  <si>
-    <t>Zepplin Mothership</t>
-  </si>
-  <si>
-    <t>Bunkers</t>
-  </si>
-  <si>
-    <t>Artillery Position</t>
-  </si>
-  <si>
-    <t>Ramming Ship/Assult Gunboat</t>
-  </si>
-  <si>
-    <t>Airport</t>
-  </si>
-  <si>
-    <t>Drone Workshop</t>
-  </si>
-  <si>
-    <t>Grey Barricade/Moat</t>
-  </si>
-  <si>
-    <t>Training Ground</t>
-  </si>
-  <si>
-    <t>Bonus Against zombies</t>
-  </si>
-  <si>
-    <t>Zombie Dolphin</t>
-  </si>
-  <si>
-    <t>Rusher Horde</t>
-  </si>
-  <si>
-    <t>Hunter Horde</t>
-  </si>
-  <si>
-    <t>Brute</t>
-  </si>
-  <si>
-    <t>Brute Horde</t>
-  </si>
-  <si>
-    <t>Evo Brute</t>
-  </si>
-  <si>
-    <t>Adv.Vehicle Promotion</t>
-  </si>
-  <si>
-    <t>School</t>
-  </si>
-  <si>
-    <t>Radio Station</t>
-  </si>
-  <si>
-    <t>Agriculture(Seed required)</t>
-  </si>
-  <si>
-    <t>Wiring(Generator)</t>
-  </si>
-  <si>
-    <t>Cement Plant</t>
-  </si>
-  <si>
-    <t>Hunting Hut</t>
-  </si>
-  <si>
-    <t>Wooden Shack</t>
-  </si>
-  <si>
-    <t>Dormitory</t>
-  </si>
-  <si>
-    <t>Special Political Buildings</t>
-  </si>
-  <si>
-    <t>Chapel</t>
-  </si>
-  <si>
-    <t>Special Distribution System</t>
-  </si>
-  <si>
-    <t>Memorial/Pubs</t>
-  </si>
-  <si>
-    <t>Grid Repair</t>
-  </si>
-  <si>
-    <t>The Generator/Seed</t>
-  </si>
-  <si>
-    <t>Pop Growth Choice</t>
-  </si>
-  <si>
-    <t>Inter-State Comm</t>
-  </si>
-  <si>
-    <t>Education Focus</t>
-  </si>
-  <si>
-    <t>Housing Res Allows for immegrants, which may bring more hostiles</t>
-  </si>
-  <si>
-    <t>scavenge trip may bring random artifacts</t>
-  </si>
-  <si>
-    <t>there maybe talented people in the survivor groups</t>
-  </si>
-  <si>
-    <t>zombie may appear out of nowhere</t>
-  </si>
-  <si>
-    <t>starvation brings desertion</t>
-  </si>
-  <si>
-    <t>Zombie is slower</t>
-  </si>
-  <si>
-    <t>Office Tower</t>
-  </si>
-  <si>
-    <t>Rebuild Option</t>
-  </si>
-  <si>
-    <t>Granary</t>
-  </si>
-  <si>
-    <t>Nope</t>
-  </si>
-  <si>
-    <t>Watchtower</t>
-  </si>
-  <si>
-    <t>Restore</t>
-  </si>
-  <si>
-    <t>Crusade against the unholy</t>
-  </si>
-  <si>
-    <t>Preparation</t>
-  </si>
-  <si>
-    <t>First Conference</t>
-  </si>
-  <si>
-    <t>Revitalised Party System</t>
-  </si>
-  <si>
-    <t>Trap Engineering</t>
-  </si>
-  <si>
-    <t>Army with a State</t>
-  </si>
-  <si>
-    <t>Maximum Work Hours</t>
-  </si>
-  <si>
-    <t>Freedom and Sufferage</t>
-  </si>
-  <si>
-    <t>Base Line Rights</t>
-  </si>
-  <si>
-    <t>Revolution Overdrive</t>
-  </si>
-  <si>
-    <t>Anti-Hierarchy</t>
-  </si>
-  <si>
-    <t>Benevolence for the Chosen</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>Immortal Habits</t>
-  </si>
-  <si>
-    <t>Love for Convenience</t>
-  </si>
-  <si>
-    <t>Return Trips</t>
+  </si>
+  <si>
+    <t>M.Caliber</t>
+  </si>
+  <si>
+    <t>Advanced Sapper/B.Caliber</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>Stewardship</t>
+  </si>
+  <si>
+    <t>Centralised Command</t>
+  </si>
+  <si>
+    <t>Defense In Depth</t>
+  </si>
+  <si>
+    <t>Planned Offense</t>
+  </si>
+  <si>
+    <t>Dispersed Command</t>
+  </si>
+  <si>
+    <t>Initiative in Hand</t>
+  </si>
+  <si>
+    <t>First Strike</t>
+  </si>
+  <si>
+    <t>Survival Doctrine</t>
+  </si>
+  <si>
+    <t>Self-sufficiency</t>
+  </si>
+  <si>
+    <t>Ammo Conservasion</t>
+  </si>
+  <si>
+    <t>Hardened</t>
+  </si>
+  <si>
+    <t>Veteran</t>
+  </si>
+  <si>
+    <t>Melee Doctrine</t>
+  </si>
+  <si>
+    <t>Swift Formation</t>
+  </si>
+  <si>
+    <t>Shield Wall</t>
+  </si>
+  <si>
+    <t>Defense Doctrine</t>
+  </si>
+  <si>
+    <t>Reinforced Position</t>
+  </si>
+  <si>
+    <t>Fort Builder</t>
+  </si>
+  <si>
+    <t>CQB Doctrine</t>
+  </si>
+  <si>
+    <t>Tactical Squads</t>
+  </si>
+  <si>
+    <t>Area Denial</t>
+  </si>
+  <si>
+    <t>Accuracy Doctrine</t>
+  </si>
+  <si>
+    <t>Aquiring Targets</t>
+  </si>
+  <si>
+    <t>Sharpshooting</t>
+  </si>
+  <si>
+    <t>Mobility Doctrine</t>
+  </si>
+  <si>
+    <t>Run and Gun</t>
+  </si>
+  <si>
+    <t>Constant Harassment</t>
+  </si>
+  <si>
+    <t>Melee Arms</t>
+  </si>
+  <si>
+    <t>Shovel</t>
+  </si>
+  <si>
+    <t>Pike</t>
+  </si>
+  <si>
+    <t>Halberd</t>
+  </si>
+  <si>
+    <t>Javalin</t>
+  </si>
+  <si>
+    <t>Scrap Armor</t>
+  </si>
+  <si>
+    <t>Plate Armor</t>
+  </si>
+  <si>
+    <t>Archery Weapons</t>
+  </si>
+  <si>
+    <t>Short Bow</t>
+  </si>
+  <si>
+    <t>Crossbow</t>
+  </si>
+  <si>
+    <t>Composite Bow</t>
+  </si>
+  <si>
+    <t>Zeds Arrow</t>
+  </si>
+  <si>
+    <t>Rocket Arrow</t>
+  </si>
+  <si>
+    <t>Small Caliber Firearms</t>
+  </si>
+  <si>
+    <t>Common Firearms</t>
+  </si>
+  <si>
+    <t>Heavy Firearms</t>
+  </si>
+  <si>
+    <t>Explosives</t>
+  </si>
+  <si>
+    <t>Gimmick Weapons</t>
+  </si>
+  <si>
+    <t>"Liberator" ripoffs</t>
+  </si>
+  <si>
+    <t>8 Shot Revolvers</t>
+  </si>
+  <si>
+    <t>Pipe Guns</t>
+  </si>
+  <si>
+    <t>6 Shot Revolvers</t>
+  </si>
+  <si>
+    <t>Automatic Rifle</t>
+  </si>
+  <si>
+    <t>HMG</t>
+  </si>
+  <si>
+    <t>Pipe Bombs</t>
+  </si>
+  <si>
+    <t>Land Mine</t>
+  </si>
+  <si>
+    <t>Potato Cannon</t>
+  </si>
+  <si>
+    <t>22 Hunting Rifles</t>
+  </si>
+  <si>
+    <t>Machine Pistols</t>
+  </si>
+  <si>
+    <t>Pump Actions</t>
+  </si>
+  <si>
+    <t>Lever Actions</t>
+  </si>
+  <si>
+    <t>Sharpshooter Rifle</t>
+  </si>
+  <si>
+    <t>Grenade Launcher</t>
+  </si>
+  <si>
+    <t>Anti-Material Rifle</t>
+  </si>
+  <si>
+    <t>Molotov Cocktail</t>
+  </si>
+  <si>
+    <t>Potatomasher</t>
+  </si>
+  <si>
+    <t>Cock'n Burn</t>
+  </si>
+  <si>
+    <t>Flamethrower</t>
+  </si>
+  <si>
+    <t>Zed Lure</t>
+  </si>
+  <si>
+    <t>Booby Trap</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1824,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1699,6 +1909,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1729,7 +1945,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1874,6 +2090,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1883,14 +2108,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2216,34 +2444,34 @@
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48" t="s">
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48" t="s">
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
     </row>
     <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>0</v>
@@ -2333,14 +2561,14 @@
         <v>46</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F4" s="34" t="s">
         <v>31</v>
       </c>
       <c r="G4" s="34"/>
-      <c r="H4" s="52" t="s">
-        <v>357</v>
+      <c r="H4" s="49" t="s">
+        <v>355</v>
       </c>
       <c r="I4" s="34" t="s">
         <v>60</v>
@@ -2372,7 +2600,7 @@
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
       <c r="G5" s="34" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
@@ -2432,7 +2660,7 @@
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>18</v>
@@ -2441,8 +2669,8 @@
         <v>27</v>
       </c>
       <c r="D7" s="24"/>
-      <c r="E7" s="51" t="s">
-        <v>356</v>
+      <c r="E7" s="48" t="s">
+        <v>354</v>
       </c>
       <c r="F7" s="24"/>
       <c r="G7" s="24" t="s">
@@ -2455,7 +2683,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
       <c r="L7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -2463,8 +2691,8 @@
         <v>87</v>
       </c>
       <c r="P7" s="35"/>
-      <c r="Q7" s="53" t="s">
-        <v>157</v>
+      <c r="Q7" s="50" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2540,7 +2768,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>29</v>
@@ -2601,28 +2829,28 @@
     </row>
     <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="D13" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="E13" s="28" t="s">
+      <c r="G13" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="G13" s="18" t="s">
+      <c r="H13" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>233</v>
-      </c>
       <c r="I13" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2648,66 +2876,66 @@
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>307</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="49" t="s">
-        <v>327</v>
-      </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
+      <c r="B3" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
       <c r="J3" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2715,14 +2943,14 @@
         <v>1</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H4" s="46"/>
       <c r="K4" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2730,16 +2958,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2747,19 +2975,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2767,22 +2995,22 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2790,10 +3018,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2801,16 +3029,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2818,13 +3046,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2916,97 +3144,97 @@
   <sheetData>
     <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>93</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="H1" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="E2" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="I2" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="49" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+        <v>98</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
       <c r="I3" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3014,7 +3242,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3022,75 +3250,75 @@
         <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>346</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
+      <c r="B8" s="52" t="s">
+        <v>344</v>
+      </c>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
     </row>
     <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3098,16 +3326,16 @@
         <v>34</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3115,24 +3343,24 @@
         <v>35</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3140,24 +3368,24 @@
         <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3165,27 +3393,27 @@
         <v>53</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3193,50 +3421,53 @@
         <v>57</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>397</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3244,13 +3475,16 @@
         <v>58</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3258,58 +3492,58 @@
         <v>54</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3317,21 +3551,21 @@
         <v>89</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3339,7 +3573,7 @@
         <v>90</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -3353,6 +3587,312 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="57" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="54"/>
+      <c r="B2" s="54" t="s">
+        <v>403</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>404</v>
+      </c>
+      <c r="D2" s="54"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="54" t="s">
+        <v>402</v>
+      </c>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D3" s="54"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="54"/>
+      <c r="B4" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>407</v>
+      </c>
+      <c r="D4" s="54"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="54"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="D5" s="54"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="55"/>
+      <c r="B6" s="55" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>410</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" s="55"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="55" t="s">
+        <v>412</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>414</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>415</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>416</v>
+      </c>
+      <c r="E7" s="55" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="55"/>
+      <c r="B8" s="55" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>419</v>
+      </c>
+      <c r="E8" s="55"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="55"/>
+      <c r="B9" s="55" t="s">
+        <v>420</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>422</v>
+      </c>
+      <c r="E9" s="55"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="55"/>
+      <c r="B10" s="55" t="s">
+        <v>423</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>424</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>425</v>
+      </c>
+      <c r="E10" s="55"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="55"/>
+      <c r="B11" s="55" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>427</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>428</v>
+      </c>
+      <c r="E11" s="55"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="56" t="s">
+        <v>429</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>431</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="56"/>
+      <c r="B13" s="56" t="s">
+        <v>434</v>
+      </c>
+      <c r="C13" s="56" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>437</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>438</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>439</v>
+      </c>
+      <c r="E14" s="56"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="56" t="s">
+        <v>440</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>441</v>
+      </c>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="56" t="s">
+        <v>442</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>447</v>
+      </c>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
+      <c r="B17" s="56" t="s">
+        <v>448</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>456</v>
+      </c>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="56" t="s">
+        <v>443</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>449</v>
+      </c>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="56" t="s">
+        <v>450</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>457</v>
+      </c>
+      <c r="D19" s="56" t="s">
+        <v>458</v>
+      </c>
+      <c r="E19" s="56" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="56"/>
+      <c r="B20" s="56" t="s">
+        <v>451</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>460</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="56" t="s">
+        <v>444</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>461</v>
+      </c>
+      <c r="D21" s="56" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" s="56"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="56" t="s">
+        <v>445</v>
+      </c>
+      <c r="B22" s="56" t="s">
+        <v>453</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>463</v>
+      </c>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="56"/>
+      <c r="B23" s="56" t="s">
+        <v>454</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>464</v>
+      </c>
+      <c r="D23" s="56" t="s">
+        <v>468</v>
+      </c>
+      <c r="E23" s="56"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="56" t="s">
+        <v>446</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>455</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>465</v>
+      </c>
+      <c r="D24" s="56" t="s">
+        <v>466</v>
+      </c>
+      <c r="E24" s="56" t="s">
+        <v>467</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3361,30 +3901,30 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50" t="s">
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
@@ -3401,7 +3941,7 @@
         <v>69</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>67</v>
@@ -3410,16 +3950,16 @@
         <v>79</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>80</v>
@@ -3442,52 +3982,52 @@
         <v>81</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>166</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="L3" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M3" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>196</v>
-      </c>
       <c r="O3" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -3495,52 +4035,52 @@
         <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -3548,52 +4088,52 @@
         <v>83</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="F5" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -3601,52 +4141,52 @@
         <v>74</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>194</v>
-      </c>
       <c r="M6" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -3656,37 +4196,37 @@
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3701,211 +4241,211 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" s="31" t="s">
+      <c r="G1" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="H1" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>138</v>
-      </c>
       <c r="L1" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M1" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N1" s="31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" t="s">
         <v>141</v>
       </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>142</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" t="s">
         <v>143</v>
       </c>
-      <c r="G2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H2" t="s">
-        <v>144</v>
-      </c>
       <c r="I2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L3" t="s">
         <v>149</v>
       </c>
-      <c r="L3" t="s">
-        <v>150</v>
-      </c>
       <c r="M3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" t="s">
         <v>146</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>147</v>
       </c>
-      <c r="C4" t="s">
-        <v>148</v>
-      </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E5" t="s">
         <v>378</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G5" t="s">
+        <v>314</v>
+      </c>
+      <c r="H5" t="s">
         <v>379</v>
       </c>
-      <c r="C5" t="s">
-        <v>379</v>
-      </c>
-      <c r="D5" t="s">
-        <v>379</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
+        <v>378</v>
+      </c>
+      <c r="J5" t="s">
+        <v>378</v>
+      </c>
+      <c r="K5" t="s">
         <v>380</v>
       </c>
-      <c r="F5" t="s">
-        <v>316</v>
-      </c>
-      <c r="G5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H5" t="s">
-        <v>381</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>380</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>380</v>
       </c>
-      <c r="K5" t="s">
-        <v>382</v>
-      </c>
-      <c r="L5" t="s">
-        <v>382</v>
-      </c>
-      <c r="M5" t="s">
-        <v>382</v>
-      </c>
       <c r="N5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3914,84 +4454,84 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B1" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="D1" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="F1" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="G1" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="H1" s="32" t="s">
         <v>239</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>287</v>
-      </c>
       <c r="F2" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>372</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -4001,7 +4541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4011,30 +4551,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B1" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="E1" s="44" t="s">
         <v>311</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="F1" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="G1" s="44" t="s">
         <v>313</v>
-      </c>
-      <c r="F1" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="G1" s="44" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B63912-0AD5-41DF-812B-02E733BA1629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A3B5A4-0104-4A11-A98D-3D0655031411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="Unit Sheets" sheetId="4" r:id="rId3"/>
     <sheet name="Promotion" sheetId="10" r:id="rId4"/>
     <sheet name="Policy Tree" sheetId="3" r:id="rId5"/>
-    <sheet name="Locations(RES)" sheetId="5" r:id="rId6"/>
-    <sheet name="C.Mechanics" sheetId="6" r:id="rId7"/>
-    <sheet name="U.Mechanics" sheetId="8" r:id="rId8"/>
+    <sheet name="Locations(Wonder)" sheetId="11" r:id="rId6"/>
+    <sheet name="Locations(RES)" sheetId="5" r:id="rId7"/>
+    <sheet name="C.Mechanics" sheetId="6" r:id="rId8"/>
+    <sheet name="U.Mechanics" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="490">
   <si>
     <t>Line1</t>
   </si>
@@ -1158,18 +1159,12 @@
     <t>Trust in Gov</t>
   </si>
   <si>
-    <t>Agricultural</t>
-  </si>
-  <si>
     <t>Infrastructural</t>
   </si>
   <si>
     <t>Commercial</t>
   </si>
   <si>
-    <t>Industrial</t>
-  </si>
-  <si>
     <t>Research</t>
   </si>
   <si>
@@ -1669,13 +1664,105 @@
   </si>
   <si>
     <t>Booby Trap</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Whispering Birch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Liberty Mall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lighthouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mercy Hospital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Airport</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sugar Mill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Truck Depot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plane Grave</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Watch tower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Housing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reactivation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repairshop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S/C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Housing</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agriculture</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industry</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1823,6 +1910,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1945,7 +2040,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2099,6 +2194,18 @@
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2108,17 +2215,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2138,9 +2242,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2178,7 +2282,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2284,7 +2388,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2426,7 +2530,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2435,41 +2539,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="19.6640625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="19.6640625" style="16"/>
+    <col min="1" max="16384" width="19.625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51" t="s">
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51" t="s">
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-    </row>
-    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+    </row>
+    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
@@ -2522,7 +2626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -2549,7 +2653,7 @@
       <c r="P3" s="26"/>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -2568,7 +2672,7 @@
       </c>
       <c r="G4" s="34"/>
       <c r="H4" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I4" s="34" t="s">
         <v>60</v>
@@ -2588,7 +2692,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -2600,7 +2704,7 @@
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
       <c r="G5" s="34" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
@@ -2625,7 +2729,7 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -2658,7 +2762,7 @@
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
     </row>
-    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>218</v>
       </c>
@@ -2670,7 +2774,7 @@
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="48" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F7" s="24"/>
       <c r="G7" s="24" t="s">
@@ -2695,7 +2799,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -2730,7 +2834,7 @@
       </c>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -2763,7 +2867,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
     </row>
-    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33">
         <v>10</v>
       </c>
@@ -2798,7 +2902,7 @@
       </c>
       <c r="Q10" s="35"/>
     </row>
-    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -2827,7 +2931,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
     </row>
-    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="27" t="s">
         <v>226</v>
       </c>
@@ -2869,260 +2973,260 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65E430D-86E9-43E2-AFAF-E995519B62A8}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="23.109375" style="7"/>
+    <col min="1" max="16384" width="23.125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="7" t="s">
-        <v>314</v>
+        <v>485</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="52" t="s">
-        <v>325</v>
-      </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
+      <c r="B3" s="56" t="s">
+        <v>323</v>
+      </c>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
       <c r="J3" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H4" s="46"/>
       <c r="K4" s="7" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="33" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="33"/>
     </row>
-    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="33"/>
     </row>
-    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="33"/>
     </row>
-    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="33"/>
     </row>
-    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="33"/>
     </row>
-    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="47"/>
     </row>
-    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="47"/>
     </row>
-    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="47"/>
     </row>
-    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="47"/>
     </row>
-    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="47"/>
     </row>
   </sheetData>
@@ -3137,12 +3241,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="19.88671875" style="7"/>
+    <col min="1" max="1" width="19.875" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="19.875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="7" t="s">
         <v>224</v>
       </c>
@@ -3156,7 +3261,7 @@
         <v>223</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>95</v>
@@ -3180,7 +3285,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>114</v>
       </c>
@@ -3209,27 +3314,27 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="56" t="s">
         <v>252</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
       <c r="I3" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>99</v>
       </c>
@@ -3237,7 +3342,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
@@ -3245,7 +3350,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
@@ -3256,10 +3361,10 @@
         <v>279</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>100</v>
       </c>
@@ -3276,21 +3381,21 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="52" t="s">
-        <v>344</v>
-      </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-    </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="56" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+    </row>
+    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>101</v>
       </c>
@@ -3301,16 +3406,16 @@
         <v>275</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>102</v>
       </c>
@@ -3318,10 +3423,10 @@
         <v>117</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
@@ -3338,7 +3443,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -3352,7 +3457,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>106</v>
       </c>
@@ -3363,7 +3468,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
@@ -3377,18 +3482,18 @@
         <v>267</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>103</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>53</v>
       </c>
@@ -3399,10 +3504,10 @@
         <v>248</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>104</v>
       </c>
@@ -3416,7 +3521,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -3433,19 +3538,19 @@
         <v>126</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -3453,13 +3558,13 @@
         <v>209</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>107</v>
       </c>
@@ -3470,7 +3575,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>58</v>
       </c>
@@ -3484,10 +3589,10 @@
         <v>260</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>54</v>
       </c>
@@ -3498,10 +3603,10 @@
         <v>272</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>108</v>
       </c>
@@ -3512,24 +3617,24 @@
         <v>278</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
         <v>110</v>
       </c>
@@ -3543,18 +3648,18 @@
         <v>261</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>89</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>111</v>
       </c>
@@ -3562,18 +3667,18 @@
         <v>256</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>90</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -3589,305 +3694,306 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="54" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="51"/>
+      <c r="B2" s="51" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54" t="s">
+      <c r="C2" s="51" t="s">
+        <v>402</v>
+      </c>
+      <c r="D2" s="51"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
+        <v>400</v>
+      </c>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51" t="s">
         <v>403</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="D3" s="51"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51" t="s">
         <v>404</v>
       </c>
-      <c r="D2" s="54"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
-        <v>402</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54" t="s">
+      <c r="C4" s="51" t="s">
         <v>405</v>
       </c>
-      <c r="D3" s="54"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54" t="s">
+      <c r="D4" s="51"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51" t="s">
         <v>406</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="D5" s="51"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52"/>
+      <c r="B6" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="D4" s="54"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54" t="s">
+      <c r="C6" s="52" t="s">
         <v>408</v>
       </c>
-      <c r="D5" s="54"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55" t="s">
+      <c r="D6" s="52" t="s">
         <v>409</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="E6" s="52"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
         <v>410</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="B7" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>414</v>
+      </c>
+      <c r="E7" s="52" t="s">
         <v>411</v>
       </c>
-      <c r="E6" s="55"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
-        <v>412</v>
-      </c>
-      <c r="B7" s="55" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="55" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52"/>
+      <c r="B8" s="52" t="s">
         <v>415</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="C8" s="52" t="s">
         <v>416</v>
       </c>
-      <c r="E7" s="55" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="55" t="s">
+      <c r="D8" s="52" t="s">
         <v>417</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="E8" s="52"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52"/>
+      <c r="B9" s="52" t="s">
         <v>418</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="C9" s="52" t="s">
         <v>419</v>
       </c>
-      <c r="E8" s="55"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
-      <c r="B9" s="55" t="s">
+      <c r="D9" s="52" t="s">
         <v>420</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="E9" s="52"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="52"/>
+      <c r="B10" s="52" t="s">
         <v>421</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="C10" s="52" t="s">
         <v>422</v>
       </c>
-      <c r="E9" s="55"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
-      <c r="B10" s="55" t="s">
+      <c r="D10" s="52" t="s">
         <v>423</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="E10" s="52"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="52"/>
+      <c r="B11" s="52" t="s">
         <v>424</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="C11" s="52" t="s">
         <v>425</v>
       </c>
-      <c r="E10" s="55"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
-      <c r="B11" s="55" t="s">
+      <c r="D11" s="52" t="s">
         <v>426</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="E11" s="52"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="53" t="s">
         <v>427</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="B12" s="53" t="s">
         <v>428</v>
       </c>
-      <c r="E11" s="55"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
+      <c r="C12" s="53" t="s">
         <v>429</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="D12" s="53" t="s">
         <v>430</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="E12" s="53" t="s">
         <v>431</v>
       </c>
-      <c r="D12" s="56" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="53"/>
+      <c r="B13" s="53" t="s">
         <v>432</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="C13" s="53" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="56"/>
-      <c r="B13" s="56" t="s">
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="53" t="s">
         <v>434</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="B14" s="53" t="s">
         <v>435</v>
       </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="C14" s="53" t="s">
         <v>436</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="D14" s="53" t="s">
         <v>437</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="E14" s="53"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="53"/>
+      <c r="B15" s="53" t="s">
         <v>438</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="C15" s="53" t="s">
         <v>439</v>
       </c>
-      <c r="E14" s="56"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56"/>
-      <c r="B15" s="56" t="s">
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="53" t="s">
         <v>440</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="B16" s="53" t="s">
+        <v>445</v>
+      </c>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="53"/>
+      <c r="B17" s="53" t="s">
+        <v>446</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>454</v>
+      </c>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="53" t="s">
         <v>441</v>
       </c>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
+      <c r="B18" s="53" t="s">
+        <v>447</v>
+      </c>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="53"/>
+      <c r="B19" s="53" t="s">
+        <v>448</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>455</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>456</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="53"/>
+      <c r="B20" s="53" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="53" t="s">
         <v>442</v>
       </c>
-      <c r="B16" s="56" t="s">
-        <v>447</v>
-      </c>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56"/>
-      <c r="B17" s="56" t="s">
-        <v>448</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>456</v>
-      </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="B21" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>459</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="E21" s="53"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="53" t="s">
         <v>443</v>
       </c>
-      <c r="B18" s="56" t="s">
-        <v>449</v>
-      </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56"/>
-      <c r="B19" s="56" t="s">
-        <v>450</v>
-      </c>
-      <c r="C19" s="56" t="s">
-        <v>457</v>
-      </c>
-      <c r="D19" s="56" t="s">
-        <v>458</v>
-      </c>
-      <c r="E19" s="56" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="56"/>
-      <c r="B20" s="56" t="s">
+      <c r="B22" s="53" t="s">
         <v>451</v>
       </c>
-      <c r="C20" s="56" t="s">
-        <v>460</v>
-      </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="56" t="s">
+      <c r="C22" s="53" t="s">
+        <v>461</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="53"/>
+      <c r="B23" s="53" t="s">
+        <v>452</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>462</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>466</v>
+      </c>
+      <c r="E23" s="53"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="53" t="s">
         <v>444</v>
       </c>
-      <c r="B21" s="56" t="s">
-        <v>452</v>
-      </c>
-      <c r="C21" s="56" t="s">
-        <v>461</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>462</v>
-      </c>
-      <c r="E21" s="56"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
-        <v>445</v>
-      </c>
-      <c r="B22" s="56" t="s">
+      <c r="B24" s="53" t="s">
         <v>453</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C24" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="56"/>
-      <c r="B23" s="56" t="s">
-        <v>454</v>
-      </c>
-      <c r="C23" s="56" t="s">
+      <c r="D24" s="53" t="s">
         <v>464</v>
       </c>
-      <c r="D23" s="56" t="s">
-        <v>468</v>
-      </c>
-      <c r="E23" s="56"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="56" t="s">
-        <v>446</v>
-      </c>
-      <c r="B24" s="56" t="s">
-        <v>455</v>
-      </c>
-      <c r="C24" s="56" t="s">
+      <c r="E24" s="53" t="s">
         <v>465</v>
       </c>
-      <c r="D24" s="56" t="s">
-        <v>466</v>
-      </c>
-      <c r="E24" s="56" t="s">
-        <v>467</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3895,38 +4001,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53" t="s">
+      <c r="C1" s="57"/>
+      <c r="D1" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53" t="s">
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-    </row>
-    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+    </row>
+    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="39" t="s">
         <v>65</v>
@@ -3959,7 +4065,7 @@
         <v>73</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>80</v>
@@ -3977,7 +4083,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
         <v>81</v>
       </c>
@@ -3994,7 +4100,7 @@
         <v>170</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>282</v>
@@ -4012,7 +4118,7 @@
         <v>189</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>194</v>
@@ -4021,7 +4127,7 @@
         <v>195</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>203</v>
@@ -4030,7 +4136,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -4038,7 +4144,7 @@
         <v>155</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>166</v>
@@ -4047,10 +4153,10 @@
         <v>171</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>178</v>
@@ -4065,7 +4171,7 @@
         <v>190</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M4" s="6" t="s">
         <v>196</v>
@@ -4083,7 +4189,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>83</v>
       </c>
@@ -4106,7 +4212,7 @@
         <v>175</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>181</v>
@@ -4118,7 +4224,7 @@
         <v>191</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>197</v>
@@ -4136,7 +4242,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42" t="s">
         <v>74</v>
       </c>
@@ -4153,13 +4259,13 @@
         <v>172</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>180</v>
@@ -4186,20 +4292,20 @@
         <v>212</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="41" t="s">
         <v>84</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>174</v>
@@ -4214,7 +4320,7 @@
         <v>182</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -4242,210 +4348,138 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="20.75" style="58"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>375</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="L1" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="M1" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="N1" s="31" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="60" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>469</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>471</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>472</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" s="59" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+    </row>
+    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="58" t="s">
         <v>241</v>
       </c>
-      <c r="B2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B2" s="58" t="s">
+        <v>468</v>
+      </c>
+      <c r="C2" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="G2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J2" t="s">
-        <v>294</v>
-      </c>
-      <c r="L2" t="s">
-        <v>150</v>
-      </c>
-      <c r="M2" t="s">
-        <v>295</v>
-      </c>
-      <c r="N2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D2" s="58" t="s">
+        <v>482</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>481</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>484</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>480</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C3" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="I3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K3" t="s">
-        <v>148</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="F3" s="58" t="s">
         <v>149</v>
       </c>
-      <c r="M3" t="s">
-        <v>148</v>
-      </c>
-      <c r="N3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="H3" s="58" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="58" t="s">
         <v>145</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="C4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C4" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D4" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E4" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F4" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="I4" t="s">
+      <c r="G4" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="J4" t="s">
+      <c r="H4" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="K4" t="s">
-        <v>146</v>
-      </c>
-      <c r="L4" t="s">
-        <v>146</v>
-      </c>
-      <c r="M4" t="s">
-        <v>146</v>
-      </c>
-      <c r="N4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B5" t="s">
-        <v>377</v>
-      </c>
-      <c r="C5" t="s">
-        <v>377</v>
-      </c>
-      <c r="D5" t="s">
-        <v>377</v>
-      </c>
-      <c r="E5" t="s">
-        <v>378</v>
-      </c>
-      <c r="F5" t="s">
-        <v>314</v>
-      </c>
-      <c r="G5" t="s">
-        <v>314</v>
-      </c>
-      <c r="H5" t="s">
-        <v>379</v>
-      </c>
-      <c r="I5" t="s">
-        <v>378</v>
-      </c>
-      <c r="J5" t="s">
-        <v>378</v>
-      </c>
-      <c r="K5" t="s">
-        <v>380</v>
-      </c>
-      <c r="L5" t="s">
-        <v>380</v>
-      </c>
-      <c r="M5" t="s">
-        <v>380</v>
-      </c>
-      <c r="N5" t="s">
-        <v>378</v>
+    </row>
+    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="58" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>478</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>477</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>475</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>478</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -4455,11 +4489,254 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F5" t="s">
+        <v>375</v>
+      </c>
+      <c r="G5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H5" t="s">
+        <v>377</v>
+      </c>
+      <c r="I5" t="s">
+        <v>376</v>
+      </c>
+      <c r="J5" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" t="s">
+        <v>378</v>
+      </c>
+      <c r="D11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>375</v>
+      </c>
+      <c r="C17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="43" t="s">
         <v>288</v>
       </c>
@@ -4485,7 +4762,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>289</v>
       </c>
@@ -4502,16 +4779,16 @@
         <v>285</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>290</v>
       </c>
@@ -4519,17 +4796,17 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>287</v>
       </c>
@@ -4541,43 +4818,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>296</v>
       </c>
       <c r="B1" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1" s="44" t="s">
         <v>308</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="E1" s="44" t="s">
         <v>309</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="F1" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="G1" s="44" t="s">
         <v>311</v>
       </c>
-      <c r="F1" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="G1" s="44" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="44"/>
+    </row>
+    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
         <v>297</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A3B5A4-0104-4A11-A98D-3D0655031411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A214BA1F-3795-44F5-B631-A01908896CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="7" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,9 @@
     <sheet name="Policy Tree" sheetId="3" r:id="rId5"/>
     <sheet name="Locations(Wonder)" sheetId="11" r:id="rId6"/>
     <sheet name="Locations(RES)" sheetId="5" r:id="rId7"/>
-    <sheet name="C.Mechanics" sheetId="6" r:id="rId8"/>
-    <sheet name="U.Mechanics" sheetId="8" r:id="rId9"/>
+    <sheet name="Terrain" sheetId="13" r:id="rId8"/>
+    <sheet name="C.Mechanics" sheetId="6" r:id="rId9"/>
+    <sheet name="U.Mechanics" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="526">
   <si>
     <t>Line1</t>
   </si>
@@ -576,10 +577,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Military Check Point</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Clinic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -636,10 +633,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Military Base</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Monarchy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -909,10 +902,6 @@
   </si>
   <si>
     <t>Basic Structure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruined Factory</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1756,13 +1745,130 @@
   <si>
     <t>Restore</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>Military Site</t>
+  </si>
+  <si>
+    <t>ZED Infestation</t>
+  </si>
+  <si>
+    <t>Coast</t>
+  </si>
+  <si>
+    <t>Plains</t>
+  </si>
+  <si>
+    <t>Desert</t>
+  </si>
+  <si>
+    <t>Lakes</t>
+  </si>
+  <si>
+    <t>Hill</t>
+  </si>
+  <si>
+    <t>Mud</t>
+  </si>
+  <si>
+    <t>Tall Grass</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>Marsh</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
+    <t>Debris</t>
+  </si>
+  <si>
+    <t>Abandoned Market</t>
+  </si>
+  <si>
+    <t>Rubble</t>
+  </si>
+  <si>
+    <t>Facility</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Broken House</t>
+  </si>
+  <si>
+    <t>Construction Site</t>
+  </si>
+  <si>
+    <t>Park</t>
+  </si>
+  <si>
+    <t>Town Square</t>
+  </si>
+  <si>
+    <t>Island</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Big River</t>
+  </si>
+  <si>
+    <t>Farmland</t>
+  </si>
+  <si>
+    <t>Highrise</t>
+  </si>
+  <si>
+    <t>National Park</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>FHH</t>
+  </si>
+  <si>
+    <t>Factory</t>
+  </si>
+  <si>
+    <t>Stadium</t>
+  </si>
+  <si>
+    <t>SCG</t>
+  </si>
+  <si>
+    <t>Scrap</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1918,6 +2024,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -2040,7 +2154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2206,6 +2320,15 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2215,13 +2338,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2242,9 +2362,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2282,7 +2402,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2388,7 +2508,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2530,7 +2650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2539,41 +2659,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="19.625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.6640625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="19.625" style="16"/>
+    <col min="1" max="16384" width="19.6640625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55" t="s">
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55" t="s">
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55" t="s">
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-    </row>
-    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+    </row>
+    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
@@ -2626,7 +2746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -2653,7 +2773,7 @@
       <c r="P3" s="26"/>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -2665,14 +2785,14 @@
         <v>46</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F4" s="34" t="s">
         <v>31</v>
       </c>
       <c r="G4" s="34"/>
       <c r="H4" s="49" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I4" s="34" t="s">
         <v>60</v>
@@ -2692,7 +2812,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -2704,7 +2824,7 @@
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
       <c r="G5" s="34" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
@@ -2729,7 +2849,7 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -2762,9 +2882,9 @@
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
     </row>
-    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>18</v>
@@ -2774,7 +2894,7 @@
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="48" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F7" s="24"/>
       <c r="G7" s="24" t="s">
@@ -2787,7 +2907,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
       <c r="L7" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -2796,10 +2916,10 @@
       </c>
       <c r="P7" s="35"/>
       <c r="Q7" s="50" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -2834,7 +2954,7 @@
       </c>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -2867,12 +2987,12 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
     </row>
-    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>10</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>29</v>
@@ -2902,7 +3022,7 @@
       </c>
       <c r="Q10" s="35"/>
     </row>
-    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -2931,30 +3051,30 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
     </row>
-    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="E13" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="F13" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E13" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>232</v>
-      </c>
       <c r="I13" s="25" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2970,263 +3090,306 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="H1" s="44"/>
+    </row>
+    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65E430D-86E9-43E2-AFAF-E995519B62A8}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="23.125" style="7"/>
+    <col min="1" max="16384" width="23.109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="56" t="s">
-        <v>323</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
+      <c r="B3" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
       <c r="J3" s="7" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H4" s="46"/>
       <c r="K4" s="7" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>322</v>
-      </c>
       <c r="I6" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>330</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
     </row>
-    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
     </row>
-    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
     </row>
-    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
     </row>
-    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
     </row>
-    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="47"/>
     </row>
-    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
     </row>
-    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="47"/>
     </row>
-    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="47"/>
     </row>
-    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="47"/>
     </row>
   </sheetData>
@@ -3241,15 +3404,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.875" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="19.875" style="7"/>
+    <col min="1" max="1" width="19.88671875" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="19.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>93</v>
@@ -3258,10 +3421,10 @@
         <v>94</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>95</v>
@@ -3285,12 +3448,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>114</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>116</v>
@@ -3308,33 +3471,33 @@
         <v>127</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="B3" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
       <c r="I3" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>99</v>
       </c>
@@ -3342,29 +3505,29 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>100</v>
       </c>
@@ -3372,30 +3535,30 @@
         <v>119</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>123</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="56" t="s">
-        <v>342</v>
-      </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-    </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+    </row>
+    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>101</v>
       </c>
@@ -3403,19 +3566,19 @@
         <v>120</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>102</v>
       </c>
@@ -3423,10 +3586,10 @@
         <v>117</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
@@ -3434,41 +3597,41 @@
         <v>128</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>121</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>106</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
@@ -3476,52 +3639,52 @@
         <v>129</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>103</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -3532,153 +3695,153 @@
         <v>131</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>126</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>107</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>58</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>108</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="L24" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="L24" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>89</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>111</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>90</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -3694,302 +3857,302 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51"/>
       <c r="B2" s="51" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D2" s="51"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B3" s="51"/>
       <c r="C3" s="51" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D3" s="51"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="51"/>
       <c r="B4" s="51" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D4" s="51"/>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="51"/>
       <c r="B5" s="51"/>
       <c r="C5" s="51" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D5" s="51"/>
     </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52"/>
       <c r="B6" s="52" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>406</v>
+      </c>
+      <c r="E6" s="52"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="B7" s="52" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="52" t="s">
         <v>408</v>
       </c>
-      <c r="D6" s="52" t="s">
-        <v>409</v>
-      </c>
-      <c r="E6" s="52"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
-        <v>410</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>412</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>413</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>414</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52"/>
       <c r="B8" s="52" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E8" s="52"/>
     </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52"/>
       <c r="B9" s="52" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E9" s="52"/>
     </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="52"/>
       <c r="B10" s="52" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E10" s="52"/>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="52"/>
       <c r="B11" s="52" t="s">
+        <v>421</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>422</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="E11" s="52"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="B12" s="53" t="s">
         <v>425</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="C12" s="53" t="s">
         <v>426</v>
       </c>
-      <c r="E11" s="52"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="53" t="s">
+      <c r="D12" s="53" t="s">
         <v>427</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="E12" s="53" t="s">
         <v>428</v>
       </c>
-      <c r="C12" s="53" t="s">
-        <v>429</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>430</v>
-      </c>
-      <c r="E12" s="53" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="53"/>
       <c r="B13" s="53" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D13" s="53"/>
       <c r="E13" s="53"/>
     </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
+        <v>431</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="D14" s="53" t="s">
         <v>434</v>
       </c>
-      <c r="B14" s="53" t="s">
-        <v>435</v>
-      </c>
-      <c r="C14" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="D14" s="53" t="s">
-        <v>437</v>
-      </c>
       <c r="E14" s="53"/>
     </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="53"/>
       <c r="B15" s="53" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
     </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C16" s="53"/>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
     </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="53"/>
       <c r="B17" s="53" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
     </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
     </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="53"/>
       <c r="B19" s="53" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="53"/>
       <c r="B20" s="53" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
     </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E21" s="53"/>
     </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
     </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="53"/>
       <c r="B23" s="53" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C23" s="53" t="s">
+        <v>459</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>463</v>
+      </c>
+      <c r="E23" s="53"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>461</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>462</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>466</v>
-      </c>
-      <c r="E23" s="53"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="53" t="s">
-        <v>444</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>453</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>463</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>464</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -4001,38 +4164,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57" t="s">
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-    </row>
-    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+    </row>
+    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="39" t="s">
         <v>65</v>
@@ -4047,7 +4210,7 @@
         <v>69</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>67</v>
@@ -4056,16 +4219,16 @@
         <v>79</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>80</v>
@@ -4083,256 +4246,256 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>81</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>386</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I4" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>185</v>
-      </c>
       <c r="K4" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M4" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>198</v>
-      </c>
       <c r="O4" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>162</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M5" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>199</v>
-      </c>
       <c r="O5" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
         <v>74</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>163</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F6" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>390</v>
-      </c>
       <c r="I6" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>84</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="I7" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4350,136 +4513,149 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="20.75" style="58"/>
+    <col min="1" max="16384" width="20.77734375" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="60" t="s">
+    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="57" t="s">
+        <v>464</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>466</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>467</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="E1" s="56" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1" s="56" t="s">
         <v>469</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="G1" s="56" t="s">
         <v>470</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="H1" s="56" t="s">
         <v>471</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="I1" s="56" t="s">
+        <v>519</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>523</v>
+      </c>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+    </row>
+    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>479</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>478</v>
+      </c>
+      <c r="F2" s="55" t="s">
+        <v>481</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>477</v>
+      </c>
+      <c r="H2" s="55" t="s">
+        <v>480</v>
+      </c>
+      <c r="I2" s="55" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="55" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
+        <v>371</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>475</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>474</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>473</v>
+      </c>
+      <c r="E5" s="55" t="s">
+        <v>473</v>
+      </c>
+      <c r="F5" s="55" t="s">
         <v>472</v>
       </c>
-      <c r="G1" s="59" t="s">
-        <v>473</v>
-      </c>
-      <c r="H1" s="59" t="s">
-        <v>474</v>
-      </c>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-    </row>
-    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>468</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>482</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="58" t="s">
-        <v>484</v>
-      </c>
-      <c r="G2" s="58" t="s">
-        <v>480</v>
-      </c>
-      <c r="H2" s="58" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="F4" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" s="58" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="58" t="s">
-        <v>374</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>478</v>
-      </c>
-      <c r="C5" s="58" t="s">
-        <v>477</v>
-      </c>
-      <c r="D5" s="58" t="s">
+      <c r="G5" s="55" t="s">
+        <v>475</v>
+      </c>
+      <c r="H5" s="55" t="s">
         <v>476</v>
       </c>
-      <c r="E5" s="58" t="s">
-        <v>476</v>
-      </c>
-      <c r="F5" s="58" t="s">
-        <v>475</v>
-      </c>
-      <c r="G5" s="58" t="s">
-        <v>478</v>
-      </c>
-      <c r="H5" s="58" t="s">
-        <v>479</v>
+      <c r="I5" s="55" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -4491,9 +4667,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="31" t="s">
         <v>135</v>
       </c>
@@ -4504,225 +4680,234 @@
         <v>133</v>
       </c>
       <c r="E1" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" t="s">
         <v>291</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" t="s">
         <v>143</v>
       </c>
-      <c r="I2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>144</v>
       </c>
-      <c r="J3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>145</v>
       </c>
-      <c r="B4" t="s">
-        <v>146</v>
-      </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F4" t="s">
         <v>146</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H4" t="s">
-        <v>146</v>
-      </c>
-      <c r="I4" t="s">
-        <v>146</v>
-      </c>
-      <c r="J4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F5" t="s">
+        <v>372</v>
+      </c>
+      <c r="G5" t="s">
         <v>374</v>
       </c>
-      <c r="B5" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" t="s">
-        <v>312</v>
-      </c>
-      <c r="D5" t="s">
-        <v>376</v>
-      </c>
-      <c r="E5" t="s">
-        <v>376</v>
-      </c>
-      <c r="F5" t="s">
-        <v>375</v>
-      </c>
-      <c r="G5" t="s">
-        <v>375</v>
-      </c>
       <c r="H5" t="s">
-        <v>377</v>
-      </c>
-      <c r="I5" t="s">
-        <v>376</v>
-      </c>
-      <c r="J5" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
-        <v>139</v>
+        <v>288</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>152</v>
+        <v>522</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>295</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+      <c r="E8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>144</v>
+        <v>289</v>
       </c>
       <c r="C9" t="s">
         <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="E9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+      <c r="E10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D11" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+      <c r="E11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
         <v>132</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+      <c r="D14" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+      <c r="D16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C17" t="s">
-        <v>489</v>
+        <v>486</v>
+      </c>
+      <c r="D17" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -4732,131 +4917,244 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
-        <v>288</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F1" s="32" t="s">
+    <row r="1" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>518</v>
+      </c>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>509</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>506</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="N4" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="O4" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="P4" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q4" s="31" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>513</v>
+      </c>
+      <c r="C5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G5" t="s">
+        <v>514</v>
+      </c>
+      <c r="H5" t="s">
+        <v>291</v>
+      </c>
+      <c r="K5" t="s">
+        <v>513</v>
+      </c>
+      <c r="L5" t="s">
+        <v>513</v>
+      </c>
+      <c r="M5" t="s">
+        <v>291</v>
+      </c>
+      <c r="N5" t="s">
         <v>237</v>
       </c>
-      <c r="G1" s="32" t="s">
-        <v>238</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>287</v>
-      </c>
+      <c r="O5" t="s">
+        <v>292</v>
+      </c>
+      <c r="P5" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="61" t="s">
+        <v>516</v>
+      </c>
+      <c r="C7" s="62" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="6" max="6" width="31.625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="E1" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="F1" s="44" t="s">
-        <v>310</v>
-      </c>
-      <c r="G1" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="H1" s="44"/>
-    </row>
-    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
-        <v>297</v>
+    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A214BA1F-3795-44F5-B631-A01908896CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28828F80-7E03-449D-993B-1BCEA67C5A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="7" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
@@ -1868,7 +1868,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2024,14 +2024,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -2154,7 +2146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2329,6 +2321,9 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2336,12 +2331,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2668,30 +2657,30 @@
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58" t="s">
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58" t="s">
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
     </row>
     <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
@@ -3191,16 +3180,16 @@
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="60" t="s">
         <v>320</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
       <c r="J3" s="7" t="s">
         <v>312</v>
       </c>
@@ -3481,15 +3470,15 @@
       <c r="A3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="60" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="7" t="s">
         <v>340</v>
       </c>
@@ -3548,15 +3537,15 @@
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="60" t="s">
         <v>339</v>
       </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
     </row>
     <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
@@ -4170,30 +4159,30 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60" t="s">
+      <c r="C1" s="61"/>
+      <c r="D1" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60" t="s">
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
@@ -5055,10 +5044,10 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="58" t="s">
         <v>516</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="32" t="s">
         <v>492</v>
       </c>
     </row>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28828F80-7E03-449D-993B-1BCEA67C5A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC25EC5-2B01-4C62-A65E-06320AEB0F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="7" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,11 @@
     <sheet name="Promotion" sheetId="10" r:id="rId4"/>
     <sheet name="Policy Tree" sheetId="3" r:id="rId5"/>
     <sheet name="Locations(Wonder)" sheetId="11" r:id="rId6"/>
-    <sheet name="Locations(RES)" sheetId="5" r:id="rId7"/>
-    <sheet name="Terrain" sheetId="13" r:id="rId8"/>
-    <sheet name="C.Mechanics" sheetId="6" r:id="rId9"/>
-    <sheet name="U.Mechanics" sheetId="8" r:id="rId10"/>
+    <sheet name="Improvements" sheetId="14" r:id="rId7"/>
+    <sheet name="Locations(RES)" sheetId="5" r:id="rId8"/>
+    <sheet name="Terrain" sheetId="13" r:id="rId9"/>
+    <sheet name="C.Mechanics" sheetId="6" r:id="rId10"/>
+    <sheet name="U.Mechanics" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="541">
   <si>
     <t>Line1</t>
   </si>
@@ -1716,10 +1717,6 @@
   </si>
   <si>
     <t>FG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1792,9 +1789,6 @@
     <t>Abandoned Market</t>
   </si>
   <si>
-    <t>Rubble</t>
-  </si>
-  <si>
     <t>Facility</t>
   </si>
   <si>
@@ -1862,6 +1856,74 @@
   </si>
   <si>
     <t>Scrap</t>
+  </si>
+  <si>
+    <t>PPHHH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCGG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strategic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luxury</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Police Station</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Small Outpost</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Safehouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scrapyard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Foraging Hut</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Farm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DLF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fishing Boats</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Traps</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trench</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fort</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2146,7 +2208,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2332,6 +2394,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2351,9 +2419,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2391,7 +2459,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2497,7 +2565,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2639,7 +2707,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2648,12 +2716,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="19.6640625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="19.6640625" style="16"/>
+    <col min="1" max="16384" width="19.625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
@@ -2682,7 +2750,7 @@
       <c r="P1" s="59"/>
       <c r="Q1" s="59"/>
     </row>
-    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
@@ -2735,7 +2803,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -2762,7 +2830,7 @@
       <c r="P3" s="26"/>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -2801,7 +2869,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -2838,7 +2906,7 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -2871,7 +2939,7 @@
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
     </row>
-    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>216</v>
       </c>
@@ -2908,7 +2976,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -2943,7 +3011,7 @@
       </c>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -2976,7 +3044,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
     </row>
-    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33">
         <v>10</v>
       </c>
@@ -3011,7 +3079,7 @@
       </c>
       <c r="Q10" s="35"/>
     </row>
-    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -3040,7 +3108,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
     </row>
-    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="27" t="s">
         <v>223</v>
       </c>
@@ -3080,14 +3148,101 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>293</v>
       </c>
@@ -3111,7 +3266,7 @@
       </c>
       <c r="H1" s="44"/>
     </row>
-    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
         <v>294</v>
       </c>
@@ -3125,20 +3280,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65E430D-86E9-43E2-AFAF-E995519B62A8}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="23.109375" style="7"/>
+    <col min="1" max="16384" width="23.125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>484</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>296</v>
@@ -3162,7 +3317,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
@@ -3176,7 +3331,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
@@ -3194,7 +3349,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
@@ -3209,7 +3364,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
@@ -3226,7 +3381,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="33" t="s">
         <v>3</v>
       </c>
@@ -3246,7 +3401,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>4</v>
       </c>
@@ -3269,7 +3424,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
         <v>5</v>
       </c>
@@ -3280,7 +3435,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
         <v>6</v>
       </c>
@@ -3297,7 +3452,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
         <v>7</v>
       </c>
@@ -3311,74 +3466,74 @@
         <v>362</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="33"/>
     </row>
-    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="33"/>
     </row>
-    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="33"/>
     </row>
-    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="33"/>
     </row>
-    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="33"/>
     </row>
-    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="47"/>
     </row>
-    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="47"/>
     </row>
-    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="47"/>
     </row>
-    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="47"/>
     </row>
-    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="47"/>
     </row>
   </sheetData>
@@ -3393,13 +3548,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="19.88671875" style="7"/>
+    <col min="1" max="1" width="19.875" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="19.875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="7" t="s">
         <v>221</v>
       </c>
@@ -3437,7 +3592,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>114</v>
       </c>
@@ -3466,7 +3621,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>98</v>
       </c>
@@ -3486,7 +3641,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>99</v>
       </c>
@@ -3494,7 +3649,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
@@ -3502,7 +3657,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
@@ -3516,7 +3671,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>100</v>
       </c>
@@ -3533,7 +3688,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -3547,7 +3702,7 @@
       <c r="G8" s="60"/>
       <c r="H8" s="60"/>
     </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>101</v>
       </c>
@@ -3567,7 +3722,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>102</v>
       </c>
@@ -3578,7 +3733,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
@@ -3595,7 +3750,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -3609,7 +3764,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>106</v>
       </c>
@@ -3620,7 +3775,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
@@ -3637,7 +3792,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>103</v>
       </c>
@@ -3645,7 +3800,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>53</v>
       </c>
@@ -3659,7 +3814,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>104</v>
       </c>
@@ -3673,7 +3828,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -3702,7 +3857,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -3716,7 +3871,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>107</v>
       </c>
@@ -3727,7 +3882,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>58</v>
       </c>
@@ -3744,7 +3899,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>54</v>
       </c>
@@ -3758,7 +3913,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>108</v>
       </c>
@@ -3775,7 +3930,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>109</v>
       </c>
@@ -3786,7 +3941,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
         <v>110</v>
       </c>
@@ -3803,7 +3958,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>89</v>
       </c>
@@ -3811,7 +3966,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>111</v>
       </c>
@@ -3825,7 +3980,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>90</v>
       </c>
@@ -3846,14 +4001,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="54" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="51"/>
       <c r="B2" s="51" t="s">
         <v>398</v>
@@ -3863,7 +4018,7 @@
       </c>
       <c r="D2" s="51"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="51" t="s">
         <v>397</v>
       </c>
@@ -3873,7 +4028,7 @@
       </c>
       <c r="D3" s="51"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="51" t="s">
         <v>401</v>
@@ -3883,7 +4038,7 @@
       </c>
       <c r="D4" s="51"/>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="51"/>
       <c r="B5" s="51"/>
       <c r="C5" s="51" t="s">
@@ -3891,7 +4046,7 @@
       </c>
       <c r="D5" s="51"/>
     </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="52"/>
       <c r="B6" s="52" t="s">
         <v>404</v>
@@ -3904,7 +4059,7 @@
       </c>
       <c r="E6" s="52"/>
     </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="52" t="s">
         <v>407</v>
       </c>
@@ -3921,7 +4076,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="52"/>
       <c r="B8" s="52" t="s">
         <v>412</v>
@@ -3934,7 +4089,7 @@
       </c>
       <c r="E8" s="52"/>
     </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="52"/>
       <c r="B9" s="52" t="s">
         <v>415</v>
@@ -3947,7 +4102,7 @@
       </c>
       <c r="E9" s="52"/>
     </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="52"/>
       <c r="B10" s="52" t="s">
         <v>418</v>
@@ -3960,7 +4115,7 @@
       </c>
       <c r="E10" s="52"/>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="52"/>
       <c r="B11" s="52" t="s">
         <v>421</v>
@@ -3973,7 +4128,7 @@
       </c>
       <c r="E11" s="52"/>
     </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="53" t="s">
         <v>424</v>
       </c>
@@ -3990,7 +4145,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="53"/>
       <c r="B13" s="53" t="s">
         <v>429</v>
@@ -4001,7 +4156,7 @@
       <c r="D13" s="53"/>
       <c r="E13" s="53"/>
     </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="53" t="s">
         <v>431</v>
       </c>
@@ -4016,7 +4171,7 @@
       </c>
       <c r="E14" s="53"/>
     </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="53"/>
       <c r="B15" s="53" t="s">
         <v>435</v>
@@ -4027,7 +4182,7 @@
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
     </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="53" t="s">
         <v>437</v>
       </c>
@@ -4038,7 +4193,7 @@
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
     </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="53"/>
       <c r="B17" s="53" t="s">
         <v>443</v>
@@ -4049,7 +4204,7 @@
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
     </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="53" t="s">
         <v>438</v>
       </c>
@@ -4060,7 +4215,7 @@
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
     </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="53"/>
       <c r="B19" s="53" t="s">
         <v>445</v>
@@ -4075,7 +4230,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="53"/>
       <c r="B20" s="53" t="s">
         <v>446</v>
@@ -4086,7 +4241,7 @@
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
     </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="53" t="s">
         <v>439</v>
       </c>
@@ -4101,7 +4256,7 @@
       </c>
       <c r="E21" s="53"/>
     </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="53" t="s">
         <v>440</v>
       </c>
@@ -4114,7 +4269,7 @@
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
     </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="53"/>
       <c r="B23" s="53" t="s">
         <v>449</v>
@@ -4127,7 +4282,7 @@
       </c>
       <c r="E23" s="53"/>
     </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="53" t="s">
         <v>441</v>
       </c>
@@ -4153,9 +4308,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
@@ -4184,7 +4339,7 @@
       <c r="P1" s="61"/>
       <c r="Q1" s="61"/>
     </row>
-    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="39" t="s">
         <v>65</v>
@@ -4235,7 +4390,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
         <v>81</v>
       </c>
@@ -4288,7 +4443,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -4341,7 +4496,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>83</v>
       </c>
@@ -4394,7 +4549,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42" t="s">
         <v>74</v>
       </c>
@@ -4447,7 +4602,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="41" t="s">
         <v>84</v>
       </c>
@@ -4502,12 +4657,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="20.77734375" style="55"/>
+    <col min="1" max="16384" width="20.75" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="57" t="s">
         <v>464</v>
       </c>
@@ -4530,17 +4685,17 @@
         <v>471</v>
       </c>
       <c r="I1" s="56" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="J1" s="56" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K1" s="56"/>
       <c r="L1" s="56"/>
       <c r="M1" s="56"/>
       <c r="N1" s="56"/>
     </row>
-    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
         <v>238</v>
       </c>
@@ -4557,19 +4712,22 @@
         <v>478</v>
       </c>
       <c r="F2" s="55" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G2" s="55" t="s">
         <v>477</v>
       </c>
       <c r="H2" s="55" t="s">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+      <c r="J2" s="55" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55" t="s">
         <v>150</v>
       </c>
@@ -4588,8 +4746,11 @@
       <c r="H3" s="55" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="55" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
         <v>144</v>
       </c>
@@ -4615,10 +4776,13 @@
         <v>145</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="J4" s="55" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
         <v>371</v>
       </c>
@@ -4645,6 +4809,9 @@
       </c>
       <c r="I5" s="55" t="s">
         <v>373</v>
+      </c>
+      <c r="J5" s="55" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -4654,250 +4821,69 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDA60A-2197-46FF-A1E9-DE6B49F4104C}">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="31" t="s">
-        <v>135</v>
+        <v>530</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>136</v>
+        <v>531</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>133</v>
+        <v>532</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>134</v>
+        <v>533</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>219</v>
+        <v>534</v>
       </c>
       <c r="G1" s="31" t="s">
-        <v>370</v>
+        <v>535</v>
       </c>
       <c r="H1" s="31" t="s">
-        <v>137</v>
+        <v>537</v>
       </c>
       <c r="I1" s="31"/>
-      <c r="J1" s="31" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="62" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>238</v>
       </c>
-      <c r="B2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>150</v>
       </c>
-      <c r="B3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" t="s">
-        <v>525</v>
-      </c>
-      <c r="E3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>371</v>
-      </c>
-      <c r="B5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C5" t="s">
-        <v>309</v>
-      </c>
-      <c r="D5" t="s">
-        <v>373</v>
-      </c>
-      <c r="E5" t="s">
-        <v>372</v>
-      </c>
-      <c r="F5" t="s">
-        <v>372</v>
-      </c>
-      <c r="G5" t="s">
-        <v>374</v>
-      </c>
-      <c r="H5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>522</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>290</v>
-      </c>
-      <c r="C8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" t="s">
-        <v>291</v>
-      </c>
-      <c r="E8" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>289</v>
-      </c>
-      <c r="C9" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>373</v>
-      </c>
-      <c r="C11" t="s">
-        <v>375</v>
-      </c>
-      <c r="D11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E11" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>485</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" t="s">
-        <v>487</v>
-      </c>
-      <c r="D14" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>372</v>
-      </c>
-      <c r="C17" t="s">
-        <v>486</v>
-      </c>
-      <c r="D17" t="s">
-        <v>486</v>
-      </c>
+    </row>
+    <row r="6" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="63" t="s">
+        <v>538</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>539</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="H7" s="31"/>
+    </row>
+    <row r="13" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4906,240 +4892,426 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>490</v>
+        <v>135</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>493</v>
+        <v>136</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>491</v>
+        <v>133</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>499</v>
+        <v>134</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>518</v>
-      </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-    </row>
-    <row r="2" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>238</v>
       </c>
       <c r="B2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" t="s">
         <v>291</v>
       </c>
-      <c r="C2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F5" t="s">
+        <v>372</v>
+      </c>
+      <c r="G5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H5" t="s">
+        <v>373</v>
+      </c>
+      <c r="I5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>520</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>527</v>
+      </c>
+      <c r="B8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" t="s">
         <v>291</v>
       </c>
-      <c r="E2" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>511</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>494</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>498</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>495</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>496</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>517</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>497</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>509</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>502</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>508</v>
-      </c>
-      <c r="L4" s="31" t="s">
-        <v>506</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>507</v>
-      </c>
-      <c r="N4" s="31" t="s">
-        <v>501</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>503</v>
-      </c>
-      <c r="P4" s="31" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q4" s="31" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B5" t="s">
-        <v>513</v>
-      </c>
-      <c r="C5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G5" t="s">
-        <v>514</v>
-      </c>
-      <c r="H5" t="s">
-        <v>291</v>
-      </c>
-      <c r="K5" t="s">
-        <v>513</v>
-      </c>
-      <c r="L5" t="s">
-        <v>513</v>
-      </c>
-      <c r="M5" t="s">
-        <v>291</v>
-      </c>
-      <c r="N5" t="s">
-        <v>237</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="E8" t="s">
         <v>292</v>
       </c>
-      <c r="P5" t="s">
-        <v>515</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="58" t="s">
-        <v>516</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
+    </row>
+    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>373</v>
+      </c>
+      <c r="C11" t="s">
+        <v>375</v>
+      </c>
+      <c r="D11" t="s">
+        <v>373</v>
+      </c>
+      <c r="E11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>528</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>484</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" t="s">
+        <v>486</v>
+      </c>
+      <c r="D14" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C17" t="s">
+        <v>485</v>
+      </c>
+      <c r="D17" t="s">
+        <v>485</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>284</v>
-      </c>
+    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>494</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>515</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>506</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>505</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="N4" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="O4" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="P4" s="31" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G5" t="s">
+        <v>512</v>
+      </c>
+      <c r="H5" t="s">
+        <v>291</v>
+      </c>
+      <c r="J5" t="s">
+        <v>511</v>
+      </c>
+      <c r="K5" t="s">
+        <v>511</v>
+      </c>
+      <c r="L5" t="s">
+        <v>291</v>
+      </c>
+      <c r="M5" t="s">
+        <v>237</v>
+      </c>
+      <c r="N5" t="s">
+        <v>292</v>
+      </c>
+      <c r="O5" t="s">
+        <v>513</v>
+      </c>
+      <c r="P5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="58" t="s">
+        <v>514</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC25EC5-2B01-4C62-A65E-06320AEB0F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA9EDCE-668D-4685-A034-F07DB1739468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="556">
   <si>
     <t>Line1</t>
   </si>
@@ -1914,16 +1914,60 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Traps</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Trench</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Fort</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strat.Res from Res tiles</t>
+  </si>
+  <si>
+    <t>17%Def</t>
+  </si>
+  <si>
+    <t>F(F in summer)</t>
+  </si>
+  <si>
+    <t>(5F in autumn)</t>
+  </si>
+  <si>
+    <t>15%Def</t>
+  </si>
+  <si>
+    <t>33%Def</t>
+  </si>
+  <si>
+    <t>Barricade</t>
+  </si>
+  <si>
+    <t>1 Movement Deduction</t>
+  </si>
+  <si>
+    <t>Zed Traps</t>
+  </si>
+  <si>
+    <t>Low level zed cannot escape.</t>
+  </si>
+  <si>
+    <t>Hurt all zeds/human by a small amount</t>
+  </si>
+  <si>
+    <t>Landmine</t>
+  </si>
+  <si>
+    <t>Instant Damage unless upgraded</t>
+  </si>
+  <si>
+    <t>Bastion</t>
+  </si>
+  <si>
+    <t>100%Def</t>
+  </si>
+  <si>
+    <t>3 sight</t>
   </si>
 </sst>
 </file>
@@ -2208,7 +2252,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2386,6 +2430,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2395,11 +2442,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2419,9 +2472,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2459,7 +2512,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2565,7 +2618,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2707,7 +2760,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2716,41 +2769,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="19.625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.6640625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="19.625" style="16"/>
+    <col min="1" max="16384" width="19.6640625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59" t="s">
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59" t="s">
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-    </row>
-    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+    </row>
+    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
@@ -2803,7 +2856,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -2830,7 +2883,7 @@
       <c r="P3" s="26"/>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -2869,7 +2922,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -2906,7 +2959,7 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -2939,7 +2992,7 @@
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
     </row>
-    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>216</v>
       </c>
@@ -2976,7 +3029,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -3011,7 +3064,7 @@
       </c>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -3044,7 +3097,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
     </row>
-    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>10</v>
       </c>
@@ -3079,7 +3132,7 @@
       </c>
       <c r="Q10" s="35"/>
     </row>
-    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -3108,7 +3161,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
     </row>
-    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
         <v>223</v>
       </c>
@@ -3150,9 +3203,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>285</v>
       </c>
@@ -3178,7 +3231,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>286</v>
       </c>
@@ -3204,7 +3257,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>287</v>
       </c>
@@ -3222,7 +3275,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>284</v>
       </c>
@@ -3237,12 +3290,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="31.625" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>293</v>
       </c>
@@ -3266,7 +3319,7 @@
       </c>
       <c r="H1" s="44"/>
     </row>
-    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
         <v>294</v>
       </c>
@@ -3280,12 +3333,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65E430D-86E9-43E2-AFAF-E995519B62A8}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="23.125" style="7"/>
+    <col min="1" max="16384" width="23.109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>481</v>
       </c>
@@ -3317,7 +3370,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>96</v>
       </c>
@@ -3331,25 +3384,25 @@
         <v>301</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="61" t="s">
         <v>320</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
       <c r="J3" s="7" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
@@ -3364,7 +3417,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
@@ -3381,7 +3434,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>3</v>
       </c>
@@ -3401,7 +3454,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>4</v>
       </c>
@@ -3424,7 +3477,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>5</v>
       </c>
@@ -3435,7 +3488,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>6</v>
       </c>
@@ -3452,7 +3505,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>7</v>
       </c>
@@ -3466,74 +3519,74 @@
         <v>362</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
     </row>
-    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
     </row>
-    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
     </row>
-    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
     </row>
-    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
     </row>
-    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="47"/>
     </row>
-    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
     </row>
-    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="47"/>
     </row>
-    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="47"/>
     </row>
-    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="47"/>
     </row>
   </sheetData>
@@ -3548,13 +3601,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.875" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="19.875" style="7"/>
+    <col min="1" max="1" width="19.88671875" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="19.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>221</v>
       </c>
@@ -3592,7 +3645,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>114</v>
       </c>
@@ -3621,19 +3674,19 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="61" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
       <c r="I3" s="7" t="s">
         <v>340</v>
       </c>
@@ -3641,7 +3694,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>99</v>
       </c>
@@ -3649,7 +3702,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
@@ -3657,7 +3710,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
@@ -3671,7 +3724,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>100</v>
       </c>
@@ -3688,21 +3741,21 @@
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="61" t="s">
         <v>339</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-    </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+    </row>
+    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>101</v>
       </c>
@@ -3722,7 +3775,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>102</v>
       </c>
@@ -3733,7 +3786,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
@@ -3750,7 +3803,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -3764,7 +3817,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>106</v>
       </c>
@@ -3775,7 +3828,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>40</v>
       </c>
@@ -3792,7 +3845,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>103</v>
       </c>
@@ -3800,7 +3853,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>53</v>
       </c>
@@ -3814,7 +3867,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>104</v>
       </c>
@@ -3828,7 +3881,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -3857,7 +3910,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -3871,7 +3924,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>107</v>
       </c>
@@ -3882,7 +3935,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>58</v>
       </c>
@@ -3899,7 +3952,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>54</v>
       </c>
@@ -3913,7 +3966,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>108</v>
       </c>
@@ -3930,7 +3983,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>109</v>
       </c>
@@ -3941,7 +3994,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>110</v>
       </c>
@@ -3958,7 +4011,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>89</v>
       </c>
@@ -3966,7 +4019,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>111</v>
       </c>
@@ -3980,7 +4033,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>90</v>
       </c>
@@ -4001,14 +4054,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51"/>
       <c r="B2" s="51" t="s">
         <v>398</v>
@@ -4018,7 +4071,7 @@
       </c>
       <c r="D2" s="51"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>397</v>
       </c>
@@ -4028,7 +4081,7 @@
       </c>
       <c r="D3" s="51"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="51"/>
       <c r="B4" s="51" t="s">
         <v>401</v>
@@ -4038,7 +4091,7 @@
       </c>
       <c r="D4" s="51"/>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="51"/>
       <c r="B5" s="51"/>
       <c r="C5" s="51" t="s">
@@ -4046,7 +4099,7 @@
       </c>
       <c r="D5" s="51"/>
     </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52"/>
       <c r="B6" s="52" t="s">
         <v>404</v>
@@ -4059,7 +4112,7 @@
       </c>
       <c r="E6" s="52"/>
     </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
         <v>407</v>
       </c>
@@ -4076,7 +4129,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52"/>
       <c r="B8" s="52" t="s">
         <v>412</v>
@@ -4089,7 +4142,7 @@
       </c>
       <c r="E8" s="52"/>
     </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52"/>
       <c r="B9" s="52" t="s">
         <v>415</v>
@@ -4102,7 +4155,7 @@
       </c>
       <c r="E9" s="52"/>
     </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="52"/>
       <c r="B10" s="52" t="s">
         <v>418</v>
@@ -4115,7 +4168,7 @@
       </c>
       <c r="E10" s="52"/>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="52"/>
       <c r="B11" s="52" t="s">
         <v>421</v>
@@ -4128,7 +4181,7 @@
       </c>
       <c r="E11" s="52"/>
     </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>424</v>
       </c>
@@ -4145,7 +4198,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="53"/>
       <c r="B13" s="53" t="s">
         <v>429</v>
@@ -4156,7 +4209,7 @@
       <c r="D13" s="53"/>
       <c r="E13" s="53"/>
     </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
         <v>431</v>
       </c>
@@ -4171,7 +4224,7 @@
       </c>
       <c r="E14" s="53"/>
     </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="53"/>
       <c r="B15" s="53" t="s">
         <v>435</v>
@@ -4182,7 +4235,7 @@
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
     </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>437</v>
       </c>
@@ -4193,7 +4246,7 @@
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
     </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="53"/>
       <c r="B17" s="53" t="s">
         <v>443</v>
@@ -4204,7 +4257,7 @@
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
     </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>438</v>
       </c>
@@ -4215,7 +4268,7 @@
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
     </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="53"/>
       <c r="B19" s="53" t="s">
         <v>445</v>
@@ -4230,7 +4283,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="53"/>
       <c r="B20" s="53" t="s">
         <v>446</v>
@@ -4241,7 +4294,7 @@
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
     </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
         <v>439</v>
       </c>
@@ -4256,7 +4309,7 @@
       </c>
       <c r="E21" s="53"/>
     </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
         <v>440</v>
       </c>
@@ -4269,7 +4322,7 @@
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
     </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="53"/>
       <c r="B23" s="53" t="s">
         <v>449</v>
@@ -4282,7 +4335,7 @@
       </c>
       <c r="E23" s="53"/>
     </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="53" t="s">
         <v>441</v>
       </c>
@@ -4308,38 +4361,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61" t="s">
+      <c r="C1" s="62"/>
+      <c r="D1" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61" t="s">
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61" t="s">
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-    </row>
-    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+    </row>
+    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="39" t="s">
         <v>65</v>
@@ -4390,7 +4443,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>81</v>
       </c>
@@ -4443,7 +4496,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -4496,7 +4549,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>83</v>
       </c>
@@ -4549,7 +4602,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
         <v>74</v>
       </c>
@@ -4602,7 +4655,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>84</v>
       </c>
@@ -4657,12 +4710,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="20.75" style="55"/>
+    <col min="1" max="16384" width="20.77734375" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="57" t="s">
         <v>464</v>
       </c>
@@ -4695,7 +4748,7 @@
       <c r="M1" s="56"/>
       <c r="N1" s="56"/>
     </row>
-    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>238</v>
       </c>
@@ -4727,7 +4780,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
         <v>150</v>
       </c>
@@ -4750,7 +4803,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
         <v>144</v>
       </c>
@@ -4782,7 +4835,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
         <v>371</v>
       </c>
@@ -4823,9 +4876,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDA60A-2197-46FF-A1E9-DE6B49F4104C}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="64"/>
       <c r="B1" s="31" t="s">
         <v>530</v>
       </c>
@@ -4848,39 +4902,142 @@
         <v>537</v>
       </c>
       <c r="I1" s="31"/>
-      <c r="K1" s="62" t="s">
+      <c r="J1" s="64"/>
+      <c r="K1" s="65" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="64" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64" t="s">
+        <v>541</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>511</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>542</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>511</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>543</v>
+      </c>
+      <c r="H2" s="64" t="s">
+        <v>291</v>
+      </c>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+    </row>
+    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="64" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="63" t="s">
+      <c r="B3" s="64" t="s">
+        <v>540</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+    </row>
+    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+    </row>
+    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+    </row>
+    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="64"/>
+      <c r="B6" s="66" t="s">
+        <v>548</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>463</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>551</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="66" t="s">
         <v>538</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="G6" s="65" t="s">
+        <v>546</v>
+      </c>
+      <c r="H6" s="66" t="s">
         <v>539</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="H7" s="31"/>
-    </row>
-    <row r="13" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="66" t="s">
+        <v>553</v>
+      </c>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+    </row>
+    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="64"/>
+      <c r="B7" s="59" t="s">
+        <v>549</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>550</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>552</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>555</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>544</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>547</v>
+      </c>
+      <c r="H7" s="64" t="s">
+        <v>545</v>
+      </c>
+      <c r="I7" s="63" t="s">
+        <v>554</v>
+      </c>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+    </row>
+    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
@@ -4894,9 +5051,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>526</v>
       </c>
@@ -4925,7 +5082,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>238</v>
       </c>
@@ -4954,7 +5111,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>150</v>
       </c>
@@ -4974,7 +5131,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>144</v>
       </c>
@@ -5003,7 +5160,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>371</v>
       </c>
@@ -5032,7 +5189,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
         <v>288</v>
       </c>
@@ -5049,7 +5206,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>527</v>
       </c>
@@ -5066,7 +5223,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>289</v>
       </c>
@@ -5080,7 +5237,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>145</v>
       </c>
@@ -5094,7 +5251,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>373</v>
       </c>
@@ -5108,7 +5265,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>528</v>
       </c>
@@ -5122,7 +5279,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>139</v>
       </c>
@@ -5133,12 +5290,12 @@
         <v>522</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>146</v>
       </c>
@@ -5149,7 +5306,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>372</v>
       </c>
@@ -5169,9 +5326,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>508</v>
       </c>
@@ -5193,7 +5350,7 @@
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
     </row>
-    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>238</v>
       </c>
@@ -5210,7 +5367,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>509</v>
       </c>
@@ -5260,7 +5417,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>238</v>
       </c>
@@ -5301,7 +5458,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="58" t="s">
         <v>514</v>
       </c>
@@ -5309,7 +5466,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
     </row>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA9EDCE-668D-4685-A034-F07DB1739468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F9FF65-3E5C-4238-9097-A7AFF79F7BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="558">
   <si>
     <t>Line1</t>
   </si>
@@ -422,10 +422,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Total Mobilization 2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Search Party 3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1354,9 +1350,6 @@
   </si>
   <si>
     <t>Education Focus</t>
-  </si>
-  <si>
-    <t>Housing Res Allows for immegrants, which may bring more hostiles</t>
   </si>
   <si>
     <t>scavenge trip may bring random artifacts</t>
@@ -1910,64 +1903,75 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Trench</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fort</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strat.Res from Res tiles</t>
+  </si>
+  <si>
+    <t>F(F in summer)</t>
+  </si>
+  <si>
+    <t>(5F in autumn)</t>
+  </si>
+  <si>
+    <t>15%Def</t>
+  </si>
+  <si>
+    <t>33%Def</t>
+  </si>
+  <si>
+    <t>Barricade</t>
+  </si>
+  <si>
+    <t>1 Movement Deduction</t>
+  </si>
+  <si>
+    <t>Zed Traps</t>
+  </si>
+  <si>
+    <t>Low level zed cannot escape.</t>
+  </si>
+  <si>
+    <t>Hurt all zeds/human by a small amount</t>
+  </si>
+  <si>
+    <t>Landmine</t>
+  </si>
+  <si>
+    <t>Instant Damage unless upgraded</t>
+  </si>
+  <si>
+    <t>Bastion</t>
+  </si>
+  <si>
+    <t>66%Def</t>
+  </si>
+  <si>
+    <t>15 Def + 3 sight if on highrise</t>
+  </si>
+  <si>
+    <t>Recycle Station</t>
+  </si>
+  <si>
+    <t>Tech: Trapping increases F gain</t>
+  </si>
+  <si>
+    <t>Collect seeds to unlock plants</t>
+  </si>
+  <si>
     <t>Fishing Boats</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Trench</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fort</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strat.Res from Res tiles</t>
-  </si>
-  <si>
-    <t>17%Def</t>
-  </si>
-  <si>
-    <t>F(F in summer)</t>
-  </si>
-  <si>
-    <t>(5F in autumn)</t>
-  </si>
-  <si>
-    <t>15%Def</t>
-  </si>
-  <si>
-    <t>33%Def</t>
-  </si>
-  <si>
-    <t>Barricade</t>
-  </si>
-  <si>
-    <t>1 Movement Deduction</t>
-  </si>
-  <si>
-    <t>Zed Traps</t>
-  </si>
-  <si>
-    <t>Low level zed cannot escape.</t>
-  </si>
-  <si>
-    <t>Hurt all zeds/human by a small amount</t>
-  </si>
-  <si>
-    <t>Landmine</t>
-  </si>
-  <si>
-    <t>Instant Damage unless upgraded</t>
-  </si>
-  <si>
-    <t>Bastion</t>
-  </si>
-  <si>
-    <t>100%Def</t>
-  </si>
-  <si>
-    <t>3 sight</t>
+  </si>
+  <si>
+    <t>Housing Res Allows for vagrants but also risk of diseases and hostiles</t>
+  </si>
+  <si>
+    <t>Total Mobilization 2</t>
   </si>
 </sst>
 </file>
@@ -2252,7 +2256,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2433,6 +2437,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2441,18 +2454,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2778,30 +2779,30 @@
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60" t="s">
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60" t="s">
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60" t="s">
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
     </row>
     <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
@@ -2895,14 +2896,14 @@
         <v>46</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F4" s="34" t="s">
         <v>31</v>
       </c>
       <c r="G4" s="34"/>
       <c r="H4" s="49" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I4" s="34" t="s">
         <v>60</v>
@@ -2934,7 +2935,7 @@
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
       <c r="G5" s="34" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
@@ -2994,7 +2995,7 @@
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>18</v>
@@ -3004,7 +3005,7 @@
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="48" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F7" s="24"/>
       <c r="G7" s="24" t="s">
@@ -3017,7 +3018,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
       <c r="L7" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
@@ -3026,7 +3027,7 @@
       </c>
       <c r="P7" s="35"/>
       <c r="Q7" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3102,7 +3103,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>29</v>
@@ -3163,28 +3164,28 @@
     </row>
     <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="D13" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="E13" s="28" t="s">
+      <c r="G13" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="G13" s="18" t="s">
+      <c r="H13" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>229</v>
-      </c>
       <c r="I13" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3207,77 +3208,77 @@
   <sheetData>
     <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B1" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="D1" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="F1" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="G1" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="H1" s="32" t="s">
         <v>235</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="F2" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>365</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -3297,31 +3298,31 @@
   <sheetData>
     <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B1" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="D1" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="E1" s="44" t="s">
         <v>305</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="F1" s="44" t="s">
         <v>306</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="G1" s="44" t="s">
         <v>307</v>
-      </c>
-      <c r="G1" s="44" t="s">
-        <v>308</v>
       </c>
       <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -3340,34 +3341,34 @@
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>483</v>
-      </c>
       <c r="E1" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>300</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3375,31 +3376,31 @@
         <v>96</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="J2" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="61" t="s">
-        <v>320</v>
-      </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
+      <c r="B3" s="64" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
       <c r="J3" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3407,14 +3408,14 @@
         <v>1</v>
       </c>
       <c r="D4" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="G4" s="46" t="s">
         <v>313</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>314</v>
       </c>
       <c r="H4" s="46"/>
       <c r="K4" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3422,16 +3423,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3439,19 +3440,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3459,22 +3460,22 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>324</v>
-      </c>
       <c r="G7" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,10 +3483,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3493,16 +3494,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3510,13 +3511,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3609,7 +3610,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>93</v>
@@ -3618,10 +3619,10 @@
         <v>94</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>95</v>
@@ -3630,76 +3631,76 @@
         <v>97</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="E2" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="I2" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="61" t="s">
-        <v>249</v>
-      </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
+        <v>557</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
       <c r="I3" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3707,7 +3708,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3715,75 +3716,75 @@
         <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="61" t="s">
-        <v>339</v>
-      </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
+      <c r="B8" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
     </row>
     <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I9" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>342</v>
-      </c>
       <c r="L9" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3791,16 +3792,16 @@
         <v>34</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3808,24 +3809,24 @@
         <v>35</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3833,24 +3834,24 @@
         <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3858,27 +3859,27 @@
         <v>53</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3886,53 +3887,53 @@
         <v>57</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I18" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>345</v>
-      </c>
       <c r="K18" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3940,16 +3941,16 @@
         <v>58</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3957,58 +3958,58 @@
         <v>54</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4016,21 +4017,21 @@
         <v>89</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4038,7 +4039,7 @@
         <v>90</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4058,36 +4059,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51"/>
       <c r="B2" s="51" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D2" s="51"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B3" s="51"/>
       <c r="C3" s="51" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D3" s="51"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="51"/>
       <c r="B4" s="51" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D4" s="51"/>
     </row>
@@ -4095,152 +4096,152 @@
       <c r="A5" s="51"/>
       <c r="B5" s="51"/>
       <c r="C5" s="51" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D5" s="51"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52"/>
       <c r="B6" s="52" t="s">
+        <v>402</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="52" t="s">
         <v>404</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>405</v>
-      </c>
-      <c r="D6" s="52" t="s">
-        <v>406</v>
       </c>
       <c r="E6" s="52"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="B7" s="52" t="s">
         <v>407</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="C7" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="D7" s="52" t="s">
         <v>409</v>
       </c>
-      <c r="C7" s="52" t="s">
-        <v>410</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>411</v>
-      </c>
       <c r="E7" s="52" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52"/>
       <c r="B8" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="D8" s="52" t="s">
         <v>412</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>413</v>
-      </c>
-      <c r="D8" s="52" t="s">
-        <v>414</v>
       </c>
       <c r="E8" s="52"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52"/>
       <c r="B9" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>414</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>415</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>416</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>417</v>
       </c>
       <c r="E9" s="52"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="52"/>
       <c r="B10" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>417</v>
+      </c>
+      <c r="D10" s="52" t="s">
         <v>418</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>419</v>
-      </c>
-      <c r="D10" s="52" t="s">
-        <v>420</v>
       </c>
       <c r="E10" s="52"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="52"/>
       <c r="B11" s="52" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>420</v>
+      </c>
+      <c r="D11" s="52" t="s">
         <v>421</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>422</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>423</v>
       </c>
       <c r="E11" s="52"/>
     </row>
     <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
+        <v>422</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="53" t="s">
         <v>424</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="D12" s="53" t="s">
         <v>425</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="E12" s="53" t="s">
         <v>426</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>427</v>
-      </c>
-      <c r="E12" s="53" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="53"/>
       <c r="B13" s="53" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D13" s="53"/>
       <c r="E13" s="53"/>
     </row>
     <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
+        <v>429</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="53" t="s">
         <v>431</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="D14" s="53" t="s">
         <v>432</v>
-      </c>
-      <c r="C14" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="D14" s="53" t="s">
-        <v>434</v>
       </c>
       <c r="E14" s="53"/>
     </row>
     <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="53"/>
       <c r="B15" s="53" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C16" s="53"/>
       <c r="D16" s="53"/>
@@ -4249,20 +4250,20 @@
     <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="53"/>
       <c r="B17" s="53" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
@@ -4271,53 +4272,53 @@
     <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="53"/>
       <c r="B19" s="53" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C19" s="53" t="s">
+        <v>450</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>451</v>
+      </c>
+      <c r="E19" s="53" t="s">
         <v>452</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>453</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="53"/>
       <c r="B20" s="53" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E21" s="53"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
@@ -4325,31 +4326,31 @@
     <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="53"/>
       <c r="B23" s="53" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E23" s="53"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="53" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C24" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>459</v>
+      </c>
+      <c r="E24" s="53" t="s">
         <v>460</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>461</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -4367,30 +4368,30 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62" t="s">
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62" t="s">
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
@@ -4407,7 +4408,7 @@
         <v>69</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>67</v>
@@ -4416,16 +4417,16 @@
         <v>79</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>80</v>
@@ -4448,52 +4449,52 @@
         <v>81</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>163</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>187</v>
-      </c>
       <c r="L3" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M3" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>193</v>
-      </c>
       <c r="O3" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -4501,52 +4502,52 @@
         <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -4554,52 +4555,52 @@
         <v>83</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>156</v>
-      </c>
       <c r="F5" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -4607,52 +4608,52 @@
         <v>74</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="M6" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -4662,37 +4663,37 @@
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4717,31 +4718,31 @@
   <sheetData>
     <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="57" t="s">
+        <v>462</v>
+      </c>
+      <c r="C1" s="57" t="s">
         <v>464</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="D1" s="32" t="s">
+        <v>465</v>
+      </c>
+      <c r="E1" s="56" t="s">
         <v>466</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="F1" s="56" t="s">
         <v>467</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="G1" s="56" t="s">
         <v>468</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="H1" s="56" t="s">
         <v>469</v>
       </c>
-      <c r="G1" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>471</v>
-      </c>
       <c r="I1" s="56" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="J1" s="56" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K1" s="56"/>
       <c r="L1" s="56"/>
@@ -4750,121 +4751,121 @@
     </row>
     <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E2" s="55" t="s">
+        <v>476</v>
+      </c>
+      <c r="F2" s="55" t="s">
         <v>478</v>
       </c>
-      <c r="F2" s="55" t="s">
-        <v>480</v>
-      </c>
       <c r="G2" s="55" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H2" s="55" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="J2" s="55" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F3" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J3" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="55" t="s">
-        <v>145</v>
-      </c>
       <c r="C4" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H4" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J4" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
+        <v>369</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>473</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>472</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>471</v>
+      </c>
+      <c r="E5" s="55" t="s">
+        <v>471</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>470</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>473</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>474</v>
+      </c>
+      <c r="I5" s="55" t="s">
         <v>371</v>
       </c>
-      <c r="B5" s="55" t="s">
-        <v>475</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>474</v>
-      </c>
-      <c r="D5" s="55" t="s">
+      <c r="J5" s="55" t="s">
         <v>473</v>
-      </c>
-      <c r="E5" s="55" t="s">
-        <v>473</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>472</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>475</v>
-      </c>
-      <c r="H5" s="55" t="s">
-        <v>476</v>
-      </c>
-      <c r="I5" s="55" t="s">
-        <v>373</v>
-      </c>
-      <c r="J5" s="55" t="s">
-        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -4879,163 +4880,165 @@
   <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64"/>
+      <c r="A1" s="60"/>
       <c r="B1" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>529</v>
+      </c>
+      <c r="D1" s="31" t="s">
         <v>530</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="E1" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>532</v>
+      </c>
+      <c r="H1" s="31" t="s">
         <v>531</v>
       </c>
-      <c r="D1" s="31" t="s">
-        <v>532</v>
-      </c>
-      <c r="E1" s="31" t="s">
+      <c r="I1" s="31" t="s">
         <v>533</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="J1" s="31" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>551</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>540</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>509</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" s="60" t="s">
+        <v>509</v>
+      </c>
+      <c r="H2" s="60" t="s">
+        <v>538</v>
+      </c>
+      <c r="I2" s="60" t="s">
+        <v>539</v>
+      </c>
+      <c r="J2" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="K2" s="60"/>
+    </row>
+    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>537</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>308</v>
+      </c>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+    </row>
+    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="59" t="s">
+        <v>553</v>
+      </c>
+      <c r="G4" s="60"/>
+      <c r="H4" s="59" t="s">
+        <v>554</v>
+      </c>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+    </row>
+    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="60"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+    </row>
+    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="60"/>
+      <c r="B6" s="62" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>461</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>547</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>535</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>542</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>536</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>549</v>
+      </c>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+    </row>
+    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="60"/>
+      <c r="B7" s="59" t="s">
+        <v>545</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>546</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>548</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>540</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>543</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>541</v>
+      </c>
+      <c r="I7" s="59" t="s">
+        <v>550</v>
+      </c>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+    </row>
+    <row r="9" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="61" t="s">
         <v>534</v>
       </c>
-      <c r="G1" s="31" t="s">
-        <v>535</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>537</v>
-      </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="65" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64" t="s">
-        <v>541</v>
-      </c>
-      <c r="D2" s="64" t="s">
-        <v>511</v>
-      </c>
-      <c r="E2" s="64" t="s">
-        <v>542</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>511</v>
-      </c>
-      <c r="G2" s="64" t="s">
-        <v>543</v>
-      </c>
-      <c r="H2" s="64" t="s">
-        <v>291</v>
-      </c>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-    </row>
-    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>540</v>
-      </c>
-      <c r="C3" s="64" t="s">
-        <v>309</v>
-      </c>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-    </row>
-    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-    </row>
-    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-    </row>
-    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="64"/>
-      <c r="B6" s="66" t="s">
-        <v>548</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>463</v>
-      </c>
-      <c r="D6" s="65" t="s">
-        <v>551</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>260</v>
-      </c>
-      <c r="F6" s="66" t="s">
-        <v>538</v>
-      </c>
-      <c r="G6" s="65" t="s">
-        <v>546</v>
-      </c>
-      <c r="H6" s="66" t="s">
-        <v>539</v>
-      </c>
-      <c r="I6" s="66" t="s">
-        <v>553</v>
-      </c>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-    </row>
-    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="64"/>
-      <c r="B7" s="59" t="s">
-        <v>549</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>550</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>552</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>555</v>
-      </c>
-      <c r="F7" s="64" t="s">
-        <v>544</v>
-      </c>
-      <c r="G7" s="64" t="s">
-        <v>547</v>
-      </c>
-      <c r="H7" s="64" t="s">
-        <v>545</v>
-      </c>
-      <c r="I7" s="63" t="s">
-        <v>554</v>
-      </c>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="31"/>
@@ -5055,266 +5058,266 @@
   <sheetData>
     <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B1" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>137</v>
-      </c>
       <c r="I1" s="31" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" t="s">
         <v>141</v>
       </c>
-      <c r="C2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I2" t="s">
         <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" t="s">
-        <v>291</v>
-      </c>
-      <c r="I2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" t="s">
         <v>144</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" t="s">
         <v>145</v>
       </c>
-      <c r="C4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" t="s">
-        <v>146</v>
-      </c>
       <c r="G4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" t="s">
         <v>371</v>
       </c>
-      <c r="B5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C5" t="s">
-        <v>309</v>
-      </c>
-      <c r="D5" t="s">
-        <v>373</v>
-      </c>
       <c r="E5" t="s">
+        <v>370</v>
+      </c>
+      <c r="F5" t="s">
+        <v>370</v>
+      </c>
+      <c r="G5" t="s">
         <v>372</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
+        <v>371</v>
+      </c>
+      <c r="I5" t="s">
         <v>372</v>
-      </c>
-      <c r="G5" t="s">
-        <v>374</v>
-      </c>
-      <c r="H5" t="s">
-        <v>373</v>
-      </c>
-      <c r="I5" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" t="s">
         <v>290</v>
       </c>
-      <c r="C8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>291</v>
-      </c>
-      <c r="E8" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>371</v>
+      </c>
+      <c r="C11" t="s">
         <v>373</v>
       </c>
-      <c r="C11" t="s">
-        <v>375</v>
-      </c>
       <c r="D11" t="s">
+        <v>371</v>
+      </c>
+      <c r="E11" t="s">
         <v>373</v>
-      </c>
-      <c r="E11" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C17" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D17" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -5330,140 +5333,140 @@
   <sheetData>
     <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>491</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="31" t="s">
         <v>493</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="F4" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>494</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>505</v>
+      </c>
+      <c r="I4" s="31" t="s">
         <v>497</v>
       </c>
-      <c r="D4" s="31" t="s">
-        <v>494</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>495</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>515</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>496</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>507</v>
-      </c>
-      <c r="I4" s="31" t="s">
+      <c r="J4" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="N4" s="31" t="s">
         <v>499</v>
       </c>
-      <c r="J4" s="31" t="s">
-        <v>506</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>504</v>
-      </c>
-      <c r="L4" s="31" t="s">
-        <v>505</v>
-      </c>
-      <c r="M4" s="31" t="s">
+      <c r="O4" s="31" t="s">
         <v>500</v>
       </c>
-      <c r="N4" s="31" t="s">
+      <c r="P4" s="31" t="s">
         <v>501</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>502</v>
-      </c>
-      <c r="P4" s="31" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G5" t="s">
+        <v>510</v>
+      </c>
+      <c r="H5" t="s">
+        <v>290</v>
+      </c>
+      <c r="J5" t="s">
+        <v>509</v>
+      </c>
+      <c r="K5" t="s">
+        <v>509</v>
+      </c>
+      <c r="L5" t="s">
+        <v>290</v>
+      </c>
+      <c r="M5" t="s">
+        <v>236</v>
+      </c>
+      <c r="N5" t="s">
+        <v>291</v>
+      </c>
+      <c r="O5" t="s">
         <v>511</v>
       </c>
-      <c r="C5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G5" t="s">
-        <v>512</v>
-      </c>
-      <c r="H5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
         <v>511</v>
-      </c>
-      <c r="K5" t="s">
-        <v>511</v>
-      </c>
-      <c r="L5" t="s">
-        <v>291</v>
-      </c>
-      <c r="M5" t="s">
-        <v>237</v>
-      </c>
-      <c r="N5" t="s">
-        <v>292</v>
-      </c>
-      <c r="O5" t="s">
-        <v>513</v>
-      </c>
-      <c r="P5" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="58" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F9FF65-3E5C-4238-9097-A7AFF79F7BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67067A1-2E7A-496E-A5BB-7514A02D4E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="557">
   <si>
     <t>Line1</t>
   </si>
@@ -142,10 +142,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Fishing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Total Mobilization</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -154,10 +150,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Back to the Job</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Welding</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -214,10 +206,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Search Party</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Grid Rebuild</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -898,10 +886,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Basic Structure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Barn</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1226,9 +1210,6 @@
     <t>Scavenge Priority</t>
   </si>
   <si>
-    <t>Intergration</t>
-  </si>
-  <si>
     <t>Granary/Smokery</t>
   </si>
   <si>
@@ -1323,9 +1304,6 @@
   </si>
   <si>
     <t>Dormitory</t>
-  </si>
-  <si>
-    <t>Special Political Buildings</t>
   </si>
   <si>
     <t>Chapel</t>
@@ -1721,10 +1699,6 @@
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
-    <t>Agriculture</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
     <t>Industry</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
@@ -1972,6 +1946,24 @@
   </si>
   <si>
     <t>Total Mobilization 2</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
+    <t>Search Party</t>
+  </si>
+  <si>
+    <t>Basic Structure</t>
+  </si>
+  <si>
+    <t>Back to the Job</t>
+  </si>
+  <si>
+    <t>Intergration/Special Political Buildings</t>
   </si>
 </sst>
 </file>
@@ -2806,7 +2798,7 @@
     </row>
     <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>0</v>
@@ -2869,13 +2861,13 @@
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
       <c r="G3" s="34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H3" s="34"/>
       <c r="I3" s="34"/>
       <c r="J3" s="34"/>
       <c r="K3" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
@@ -2893,32 +2885,32 @@
       </c>
       <c r="C4" s="34"/>
       <c r="D4" s="34" t="s">
-        <v>46</v>
+        <v>553</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>217</v>
+        <v>554</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>31</v>
+        <v>555</v>
       </c>
       <c r="G4" s="34"/>
       <c r="H4" s="49" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J4" s="36"/>
       <c r="K4" s="36"/>
       <c r="L4" s="20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M4" s="20"/>
       <c r="N4" s="20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
@@ -2935,28 +2927,28 @@
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
       <c r="G5" s="34" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M5" s="20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N5" s="20"/>
       <c r="O5" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="P5" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="P5" s="26" t="s">
-        <v>91</v>
       </c>
       <c r="Q5" s="35"/>
     </row>
@@ -2967,27 +2959,27 @@
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24" t="s">
-        <v>28</v>
+        <v>552</v>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G6" s="24"/>
       <c r="H6" s="23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L6" s="23"/>
       <c r="M6" s="20"/>
       <c r="N6" s="20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="O6" s="20"/>
       <c r="P6" s="35"/>
@@ -2995,7 +2987,7 @@
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>18</v>
@@ -3005,29 +2997,29 @@
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="48" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F7" s="24"/>
       <c r="G7" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H7" s="23"/>
       <c r="I7" s="23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
       <c r="L7" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
       <c r="O7" s="20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P7" s="35"/>
       <c r="Q7" s="50" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3037,31 +3029,31 @@
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
       <c r="D8" s="24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="29"/>
       <c r="G8" s="29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I8" s="29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J8" s="37" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K8" s="30"/>
       <c r="L8" s="30"/>
       <c r="M8" s="30" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N8" s="30"/>
       <c r="O8" s="30"/>
       <c r="P8" s="26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q8" s="35"/>
     </row>
@@ -3073,27 +3065,27 @@
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
       <c r="E9" s="29" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
       <c r="I9" s="29"/>
       <c r="J9" s="30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M9" s="30"/>
       <c r="N9" s="30" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
@@ -3103,10 +3095,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="29" t="s">
         <v>19</v>
@@ -3115,21 +3107,21 @@
       <c r="F10" s="29"/>
       <c r="G10" s="29"/>
       <c r="H10" s="29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I10" s="29"/>
       <c r="J10" s="38"/>
       <c r="K10" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L10" s="30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
       <c r="P10" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q10" s="35"/>
     </row>
@@ -3145,17 +3137,17 @@
       </c>
       <c r="F11" s="29"/>
       <c r="G11" s="29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H11" s="29"/>
       <c r="I11" s="29" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J11" s="38"/>
       <c r="K11" s="30"/>
       <c r="L11" s="30"/>
       <c r="M11" s="30" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N11" s="30"/>
       <c r="O11" s="30"/>
@@ -3164,28 +3156,28 @@
     </row>
     <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="F13" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="F13" s="22" t="s">
+      <c r="H13" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="G13" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>228</v>
-      </c>
       <c r="I13" s="25" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3208,77 +3200,77 @@
   <sheetData>
     <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B1" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="G1" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="H1" s="32" t="s">
         <v>231</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -3298,31 +3290,31 @@
   <sheetData>
     <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B1" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="F1" s="44" t="s">
         <v>302</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="G1" s="44" t="s">
         <v>303</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="E1" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="F1" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="G1" s="44" t="s">
-        <v>307</v>
       </c>
       <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -3341,48 +3333,48 @@
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>480</v>
+        <v>551</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3390,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C3" s="64"/>
       <c r="D3" s="64"/>
@@ -3400,7 +3392,7 @@
       <c r="H3" s="64"/>
       <c r="I3" s="64"/>
       <c r="J3" s="7" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3408,14 +3400,14 @@
         <v>1</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H4" s="46"/>
       <c r="K4" s="7" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3423,16 +3415,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3440,19 +3429,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3460,22 +3449,22 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>354</v>
+        <v>556</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3483,10 +3472,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3494,16 +3483,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>356</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3511,13 +3500,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3610,77 +3599,77 @@
   <sheetData>
     <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="I1" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="F2" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C3" s="64"/>
       <c r="D3" s="64"/>
@@ -3689,26 +3678,26 @@
       <c r="G3" s="64"/>
       <c r="H3" s="64"/>
       <c r="I3" s="7" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3716,30 +3705,30 @@
         <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3747,7 +3736,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C8" s="64"/>
       <c r="D8" s="64"/>
@@ -3758,288 +3747,288 @@
     </row>
     <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -4059,36 +4048,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="51"/>
       <c r="B2" s="51" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D2" s="51"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B3" s="51"/>
       <c r="C3" s="51" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D3" s="51"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="51"/>
       <c r="B4" s="51" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D4" s="51"/>
     </row>
@@ -4096,152 +4085,152 @@
       <c r="A5" s="51"/>
       <c r="B5" s="51"/>
       <c r="C5" s="51" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D5" s="51"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52"/>
       <c r="B6" s="52" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E6" s="52"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52"/>
       <c r="B8" s="52" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E8" s="52"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52"/>
       <c r="B9" s="52" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E9" s="52"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="52"/>
       <c r="B10" s="52" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E10" s="52"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="52"/>
       <c r="B11" s="52" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E11" s="52"/>
     </row>
     <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="53"/>
       <c r="B13" s="53" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D13" s="53"/>
       <c r="E13" s="53"/>
     </row>
     <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="53" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D14" s="53" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E14" s="53"/>
     </row>
     <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="53"/>
       <c r="B15" s="53" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C16" s="53"/>
       <c r="D16" s="53"/>
@@ -4250,20 +4239,20 @@
     <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="53"/>
       <c r="B17" s="53" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
+        <v>430</v>
+      </c>
+      <c r="B18" s="53" t="s">
         <v>436</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>442</v>
       </c>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
@@ -4272,53 +4261,53 @@
     <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="53"/>
       <c r="B19" s="53" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="53"/>
       <c r="B20" s="53" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E21" s="53"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
@@ -4326,31 +4315,31 @@
     <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="53"/>
       <c r="B23" s="53" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="E23" s="53"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="53" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -4369,11 +4358,11 @@
         <v>12</v>
       </c>
       <c r="B1" s="65" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C1" s="65"/>
       <c r="D1" s="65" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E1" s="65"/>
       <c r="F1" s="65"/>
@@ -4382,13 +4371,13 @@
       <c r="I1" s="65"/>
       <c r="J1" s="65"/>
       <c r="K1" s="65" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L1" s="65"/>
       <c r="M1" s="65"/>
       <c r="N1" s="65"/>
       <c r="O1" s="65" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P1" s="65"/>
       <c r="Q1" s="65"/>
@@ -4396,304 +4385,304 @@
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="E2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="41" t="s">
         <v>68</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="41" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="K3" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>387</v>
-      </c>
       <c r="M4" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="I5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="K5" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>174</v>
-      </c>
       <c r="H7" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>179</v>
-      </c>
       <c r="J7" s="6" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -4705,6 +4694,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4718,31 +4708,31 @@
   <sheetData>
     <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="57" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>459</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>460</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>461</v>
+      </c>
+      <c r="G1" s="56" t="s">
         <v>462</v>
       </c>
-      <c r="C1" s="57" t="s">
-        <v>464</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>465</v>
-      </c>
-      <c r="E1" s="56" t="s">
-        <v>466</v>
-      </c>
-      <c r="F1" s="56" t="s">
-        <v>467</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>468</v>
-      </c>
       <c r="H1" s="56" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="I1" s="56" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="J1" s="56" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="K1" s="56"/>
       <c r="L1" s="56"/>
@@ -4751,121 +4741,121 @@
     </row>
     <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E2" s="55" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F2" s="55" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="H2" s="55" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J2" s="55" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E3" s="55" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F3" s="55" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="55" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J3" s="55" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="J4" s="55" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F5" s="55" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="H5" s="55" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="I5" s="55" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="J5" s="55" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -4882,69 +4872,69 @@
     <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60"/>
       <c r="B1" s="31" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="H1" s="31" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="J1" s="31" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D2" s="60" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E2" s="60" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F2" s="60" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="H2" s="60" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="I2" s="60" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="J2" s="60" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="K2" s="60"/>
     </row>
     <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="60" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C3" s="60" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D3" s="60"/>
       <c r="E3" s="60"/>
@@ -4960,11 +4950,11 @@
       <c r="D4" s="60"/>
       <c r="E4" s="60"/>
       <c r="F4" s="59" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="G4" s="60"/>
       <c r="H4" s="59" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="I4" s="60"/>
       <c r="J4" s="60"/>
@@ -4986,25 +4976,25 @@
     <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="60"/>
       <c r="B6" s="62" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="F6" s="62" t="s">
+        <v>528</v>
+      </c>
+      <c r="G6" s="61" t="s">
         <v>535</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="H6" s="62" t="s">
+        <v>529</v>
+      </c>
+      <c r="I6" s="62" t="s">
         <v>542</v>
-      </c>
-      <c r="H6" s="62" t="s">
-        <v>536</v>
-      </c>
-      <c r="I6" s="62" t="s">
-        <v>549</v>
       </c>
       <c r="J6" s="60"/>
       <c r="K6" s="60"/>
@@ -5012,32 +5002,32 @@
     <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="60"/>
       <c r="B7" s="59" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="D7" s="59" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="F7" s="60" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="G7" s="60" t="s">
+        <v>536</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>534</v>
+      </c>
+      <c r="I7" s="59" t="s">
         <v>543</v>
-      </c>
-      <c r="H7" s="60" t="s">
-        <v>541</v>
-      </c>
-      <c r="I7" s="59" t="s">
-        <v>550</v>
       </c>
       <c r="J7" s="60"/>
       <c r="K7" s="60"/>
     </row>
     <row r="9" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="61" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -5058,266 +5048,266 @@
   <sheetData>
     <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E1" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="H1" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="H1" s="31" t="s">
-        <v>136</v>
-      </c>
       <c r="I1" s="31" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" t="s">
         <v>138</v>
       </c>
-      <c r="G2" t="s">
-        <v>141</v>
-      </c>
       <c r="H2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D5" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E5" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="F5" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G5" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="H5" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="I5" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="31" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C11" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D11" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E11" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D14" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C17" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D17" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -5333,140 +5323,140 @@
   <sheetData>
     <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
     </row>
     <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E2" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>488</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>485</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>506</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="L4" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="M4" s="31" t="s">
         <v>491</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>495</v>
-      </c>
-      <c r="D4" s="31" t="s">
+      <c r="N4" s="31" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="O4" s="31" t="s">
         <v>493</v>
       </c>
-      <c r="F4" s="31" t="s">
-        <v>513</v>
-      </c>
-      <c r="G4" s="31" t="s">
+      <c r="P4" s="31" t="s">
         <v>494</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>505</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>497</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>504</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>502</v>
-      </c>
-      <c r="L4" s="31" t="s">
-        <v>503</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>498</v>
-      </c>
-      <c r="N4" s="31" t="s">
-        <v>499</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>500</v>
-      </c>
-      <c r="P4" s="31" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B5" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="C5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G5" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J5" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="K5" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="L5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="N5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="O5" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="P5" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="58" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67067A1-2E7A-496E-A5BB-7514A02D4E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55F38C9-2378-44F7-9A8B-68448B6400AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="3870" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -1954,16 +1954,17 @@
     <t>Fishing</t>
   </si>
   <si>
+    <t>Basic Structure</t>
+  </si>
+  <si>
+    <t>Back to the Job</t>
+  </si>
+  <si>
+    <t>Intergration/Special Political Buildings</t>
+  </si>
+  <si>
     <t>Search Party</t>
-  </si>
-  <si>
-    <t>Basic Structure</t>
-  </si>
-  <si>
-    <t>Back to the Job</t>
-  </si>
-  <si>
-    <t>Intergration/Special Political Buildings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2465,9 +2466,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2505,7 +2506,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2611,7 +2612,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2753,7 +2754,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2762,12 +2763,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="19.6640625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.625" defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="19.6640625" style="16"/>
+    <col min="1" max="16384" width="19.625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>12</v>
       </c>
@@ -2796,7 +2797,7 @@
       <c r="P1" s="63"/>
       <c r="Q1" s="63"/>
     </row>
-    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
         <v>93</v>
       </c>
@@ -2849,7 +2850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -2876,7 +2877,7 @@
       <c r="P3" s="26"/>
       <c r="Q3" s="35"/>
     </row>
-    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -2885,13 +2886,13 @@
       </c>
       <c r="C4" s="34"/>
       <c r="D4" s="34" t="s">
+        <v>556</v>
+      </c>
+      <c r="E4" s="34" t="s">
         <v>553</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="F4" s="34" t="s">
         <v>554</v>
-      </c>
-      <c r="F4" s="34" t="s">
-        <v>555</v>
       </c>
       <c r="G4" s="34"/>
       <c r="H4" s="49" t="s">
@@ -2915,7 +2916,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
     </row>
-    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -2952,7 +2953,7 @@
       </c>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -2985,7 +2986,7 @@
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
     </row>
-    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>212</v>
       </c>
@@ -3022,7 +3023,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -3057,7 +3058,7 @@
       </c>
       <c r="Q8" s="35"/>
     </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -3090,7 +3091,7 @@
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
     </row>
-    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33">
         <v>10</v>
       </c>
@@ -3125,7 +3126,7 @@
       </c>
       <c r="Q10" s="35"/>
     </row>
-    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -3154,7 +3155,7 @@
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
     </row>
-    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="27" t="s">
         <v>218</v>
       </c>
@@ -3196,9 +3197,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="43" t="s">
         <v>280</v>
       </c>
@@ -3224,7 +3225,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>281</v>
       </c>
@@ -3250,7 +3251,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>282</v>
       </c>
@@ -3268,7 +3269,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>279</v>
       </c>
@@ -3283,12 +3284,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>288</v>
       </c>
@@ -3312,7 +3313,7 @@
       </c>
       <c r="H1" s="44"/>
     </row>
-    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
         <v>289</v>
       </c>
@@ -3326,12 +3327,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65E430D-86E9-43E2-AFAF-E995519B62A8}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="23.109375" style="7"/>
+    <col min="1" max="16384" width="23.125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="7" t="s">
         <v>473</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
         <v>93</v>
       </c>
@@ -3377,7 +3378,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
         <v>0</v>
       </c>
@@ -3395,7 +3396,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
@@ -3410,7 +3411,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
@@ -3424,7 +3425,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="33" t="s">
         <v>3</v>
       </c>
@@ -3444,7 +3445,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>4</v>
       </c>
@@ -3458,7 +3459,7 @@
         <v>321</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>341</v>
@@ -3467,7 +3468,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
         <v>5</v>
       </c>
@@ -3478,7 +3479,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
         <v>6</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
         <v>7</v>
       </c>
@@ -3509,74 +3510,74 @@
         <v>355</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="33"/>
     </row>
-    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="33"/>
     </row>
-    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="33"/>
     </row>
-    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="33"/>
     </row>
-    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="33"/>
     </row>
-    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="47"/>
     </row>
-    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="47"/>
     </row>
-    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="47"/>
     </row>
-    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="47"/>
     </row>
-    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="47"/>
     </row>
   </sheetData>
@@ -3591,13 +3592,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="19.88671875" style="7"/>
+    <col min="1" max="1" width="19.875" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="19.875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="7" t="s">
         <v>216</v>
       </c>
@@ -3635,7 +3636,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>110</v>
       </c>
@@ -3664,7 +3665,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>550</v>
       </c>
@@ -3684,7 +3685,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>95</v>
       </c>
@@ -3692,7 +3693,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>29</v>
       </c>
@@ -3700,7 +3701,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
@@ -3714,7 +3715,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>96</v>
       </c>
@@ -3731,7 +3732,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -3745,7 +3746,7 @@
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
     </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>97</v>
       </c>
@@ -3765,7 +3766,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>98</v>
       </c>
@@ -3776,7 +3777,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>32</v>
       </c>
@@ -3793,7 +3794,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>102</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
         <v>38</v>
       </c>
@@ -3835,7 +3836,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>99</v>
       </c>
@@ -3843,7 +3844,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>50</v>
       </c>
@@ -3857,7 +3858,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>100</v>
       </c>
@@ -3871,7 +3872,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>54</v>
       </c>
@@ -3900,7 +3901,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>101</v>
       </c>
@@ -3914,7 +3915,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>103</v>
       </c>
@@ -3925,7 +3926,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>55</v>
       </c>
@@ -3942,7 +3943,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>51</v>
       </c>
@@ -3956,7 +3957,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>104</v>
       </c>
@@ -3973,7 +3974,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>105</v>
       </c>
@@ -3984,7 +3985,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
         <v>106</v>
       </c>
@@ -4001,7 +4002,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>86</v>
       </c>
@@ -4009,7 +4010,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>107</v>
       </c>
@@ -4023,7 +4024,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>87</v>
       </c>
@@ -4044,14 +4045,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="54" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="51"/>
       <c r="B2" s="51" t="s">
         <v>390</v>
@@ -4061,7 +4062,7 @@
       </c>
       <c r="D2" s="51"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="51" t="s">
         <v>389</v>
       </c>
@@ -4071,7 +4072,7 @@
       </c>
       <c r="D3" s="51"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="51" t="s">
         <v>393</v>
@@ -4081,7 +4082,7 @@
       </c>
       <c r="D4" s="51"/>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="51"/>
       <c r="B5" s="51"/>
       <c r="C5" s="51" t="s">
@@ -4089,7 +4090,7 @@
       </c>
       <c r="D5" s="51"/>
     </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="52"/>
       <c r="B6" s="52" t="s">
         <v>396</v>
@@ -4102,7 +4103,7 @@
       </c>
       <c r="E6" s="52"/>
     </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="52" t="s">
         <v>399</v>
       </c>
@@ -4119,7 +4120,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="52"/>
       <c r="B8" s="52" t="s">
         <v>404</v>
@@ -4132,7 +4133,7 @@
       </c>
       <c r="E8" s="52"/>
     </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="52"/>
       <c r="B9" s="52" t="s">
         <v>407</v>
@@ -4145,7 +4146,7 @@
       </c>
       <c r="E9" s="52"/>
     </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="52"/>
       <c r="B10" s="52" t="s">
         <v>410</v>
@@ -4158,7 +4159,7 @@
       </c>
       <c r="E10" s="52"/>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="52"/>
       <c r="B11" s="52" t="s">
         <v>413</v>
@@ -4171,7 +4172,7 @@
       </c>
       <c r="E11" s="52"/>
     </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="53" t="s">
         <v>416</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="53"/>
       <c r="B13" s="53" t="s">
         <v>421</v>
@@ -4199,7 +4200,7 @@
       <c r="D13" s="53"/>
       <c r="E13" s="53"/>
     </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="53" t="s">
         <v>423</v>
       </c>
@@ -4214,7 +4215,7 @@
       </c>
       <c r="E14" s="53"/>
     </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="53"/>
       <c r="B15" s="53" t="s">
         <v>427</v>
@@ -4225,7 +4226,7 @@
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
     </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="53" t="s">
         <v>429</v>
       </c>
@@ -4236,7 +4237,7 @@
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
     </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="53"/>
       <c r="B17" s="53" t="s">
         <v>435</v>
@@ -4247,7 +4248,7 @@
       <c r="D17" s="53"/>
       <c r="E17" s="53"/>
     </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="53" t="s">
         <v>430</v>
       </c>
@@ -4258,7 +4259,7 @@
       <c r="D18" s="53"/>
       <c r="E18" s="53"/>
     </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="53"/>
       <c r="B19" s="53" t="s">
         <v>437</v>
@@ -4273,7 +4274,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="53"/>
       <c r="B20" s="53" t="s">
         <v>438</v>
@@ -4284,7 +4285,7 @@
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
     </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="53" t="s">
         <v>431</v>
       </c>
@@ -4299,7 +4300,7 @@
       </c>
       <c r="E21" s="53"/>
     </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="53" t="s">
         <v>432</v>
       </c>
@@ -4312,7 +4313,7 @@
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
     </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="53"/>
       <c r="B23" s="53" t="s">
         <v>441</v>
@@ -4325,7 +4326,7 @@
       </c>
       <c r="E23" s="53"/>
     </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="53" t="s">
         <v>433</v>
       </c>
@@ -4351,9 +4352,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
@@ -4382,7 +4383,7 @@
       <c r="P1" s="65"/>
       <c r="Q1" s="65"/>
     </row>
-    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="39" t="s">
         <v>62</v>
@@ -4433,7 +4434,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
         <v>78</v>
       </c>
@@ -4486,7 +4487,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>79</v>
       </c>
@@ -4539,7 +4540,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>80</v>
       </c>
@@ -4592,7 +4593,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42" t="s">
         <v>71</v>
       </c>
@@ -4645,7 +4646,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="41" t="s">
         <v>81</v>
       </c>
@@ -4701,12 +4702,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="20.77734375" style="55"/>
+    <col min="1" max="16384" width="20.75" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="57" t="s">
         <v>456</v>
       </c>
@@ -4739,7 +4740,7 @@
       <c r="M1" s="56"/>
       <c r="N1" s="56"/>
     </row>
-    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
         <v>233</v>
       </c>
@@ -4771,7 +4772,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55" t="s">
         <v>146</v>
       </c>
@@ -4794,7 +4795,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
         <v>140</v>
       </c>
@@ -4826,7 +4827,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55" t="s">
         <v>363</v>
       </c>
@@ -4867,9 +4868,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDA60A-2197-46FF-A1E9-DE6B49F4104C}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="60"/>
       <c r="B1" s="31" t="s">
         <v>521</v>
@@ -4896,7 +4897,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="60" t="s">
         <v>233</v>
       </c>
@@ -4926,7 +4927,7 @@
       </c>
       <c r="K2" s="60"/>
     </row>
-    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
         <v>146</v>
       </c>
@@ -4945,7 +4946,7 @@
       <c r="J3" s="60"/>
       <c r="K3" s="60"/>
     </row>
-    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="60"/>
       <c r="D4" s="60"/>
       <c r="E4" s="60"/>
@@ -4960,7 +4961,7 @@
       <c r="J4" s="60"/>
       <c r="K4" s="60"/>
     </row>
-    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="60"/>
       <c r="B5" s="60"/>
       <c r="C5" s="60"/>
@@ -4973,7 +4974,7 @@
       <c r="J5" s="60"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="60"/>
       <c r="B6" s="62" t="s">
         <v>537</v>
@@ -4999,7 +5000,7 @@
       <c r="J6" s="60"/>
       <c r="K6" s="60"/>
     </row>
-    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="60"/>
       <c r="B7" s="59" t="s">
         <v>538</v>
@@ -5025,12 +5026,12 @@
       <c r="J7" s="60"/>
       <c r="K7" s="60"/>
     </row>
-    <row r="9" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="61" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
@@ -5044,9 +5045,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>517</v>
       </c>
@@ -5075,7 +5076,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -5104,7 +5105,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>146</v>
       </c>
@@ -5124,7 +5125,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>140</v>
       </c>
@@ -5153,7 +5154,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>363</v>
       </c>
@@ -5182,7 +5183,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="31" t="s">
         <v>283</v>
       </c>
@@ -5199,7 +5200,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>518</v>
       </c>
@@ -5216,7 +5217,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>284</v>
       </c>
@@ -5230,7 +5231,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>141</v>
       </c>
@@ -5244,7 +5245,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>365</v>
       </c>
@@ -5258,7 +5259,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>519</v>
       </c>
@@ -5272,7 +5273,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>135</v>
       </c>
@@ -5283,12 +5284,12 @@
         <v>513</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>142</v>
       </c>
@@ -5299,7 +5300,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>364</v>
       </c>
@@ -5319,9 +5320,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>499</v>
       </c>
@@ -5343,7 +5344,7 @@
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
     </row>
-    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -5360,7 +5361,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>500</v>
       </c>
@@ -5410,7 +5411,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>233</v>
       </c>
@@ -5451,7 +5452,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="58" t="s">
         <v>505</v>
       </c>
@@ -5459,7 +5460,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
     </row>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55F38C9-2378-44F7-9A8B-68448B6400AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BA9D54-CDE8-4C97-A18C-65BD1C274A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{61AE6E18-C22B-4585-94FB-314F1C6D5659}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -4896,6 +4896,9 @@
       <c r="J1" s="31" t="s">
         <v>548</v>
       </c>
+      <c r="K1" s="61" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="60" t="s">
@@ -5025,11 +5028,6 @@
       </c>
       <c r="J7" s="60"/>
       <c r="K7" s="60"/>
-    </row>
-    <row r="9" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="61" t="s">
-        <v>527</v>
-      </c>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="31"/>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\OneDrive\桌面\Unciv-Windows64\mods\Zombie-Apocalypse-DEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D12EBE8-F79E-45A4-B5AC-BEECCB978161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47C9D52-624C-4003-9B84-246505076069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="594" activeTab="4" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="566">
   <si>
     <t>Line1</t>
   </si>
@@ -166,38 +166,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>River Patrol</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Generator</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Permanent Structure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vehicle Patrol</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Grid Rebuild</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Construction Vehicle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tool Smithing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Water Pump</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -234,10 +210,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Horde Killing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Chemistry</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -254,10 +226,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Makeshift Weapons</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Escape and Hide</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -342,10 +310,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Reforging</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Mass Production</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -618,10 +582,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Commisars</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Retreat from the Horde</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -674,10 +634,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Industrial Plans</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>National Guards</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -694,10 +650,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cleansing the World</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Missionary Works</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -706,10 +658,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>New Nobilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Royal Guards</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -782,10 +730,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Strict Border Control</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Inpeccable Defence</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -826,22 +770,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Restore Power</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Restore Water</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Restore Agriculture</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Out of the hell</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>New Federation</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1042,9 +974,6 @@
     <t>Contaminator</t>
   </si>
   <si>
-    <t>Nothing Against the Unity</t>
-  </si>
-  <si>
     <t>less settlements more work range</t>
   </si>
   <si>
@@ -1306,15 +1235,9 @@
     <t>Crusade against the unholy</t>
   </si>
   <si>
-    <t>Preparation</t>
-  </si>
-  <si>
     <t>First Conference</t>
   </si>
   <si>
-    <t>Revitalised Party System</t>
-  </si>
-  <si>
     <t>Trap Engineering</t>
   </si>
   <si>
@@ -1327,27 +1250,12 @@
     <t>Freedom and Sufferage</t>
   </si>
   <si>
-    <t>Base Line Rights</t>
-  </si>
-  <si>
     <t>Revolution Overdrive</t>
   </si>
   <si>
     <t>Anti-Hierarchy</t>
   </si>
   <si>
-    <t>Benevolence for the Chosen</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>Immortal Habits</t>
-  </si>
-  <si>
-    <t>Love for Convenience</t>
-  </si>
-  <si>
     <t>Return Trips</t>
   </si>
   <si>
@@ -1525,9 +1433,6 @@
     <t>Land Mine</t>
   </si>
   <si>
-    <t>Potato Cannon</t>
-  </si>
-  <si>
     <t>22 Hunting Rifles</t>
   </si>
   <si>
@@ -1591,23 +1496,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Plane Grave</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Watch tower</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Housing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Reactivation</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Repairshop</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1867,89 +1756,258 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Intergration/Special Political Buildings</t>
+  </si>
+  <si>
+    <t>Bathhouse</t>
+  </si>
+  <si>
+    <t>Windmill/Watermill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Scraping </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean Scavenge </t>
+  </si>
+  <si>
+    <t>Scavenge Expertise</t>
+  </si>
+  <si>
+    <t>Truck Evac Site</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Reconstruction</t>
+  </si>
+  <si>
+    <t>Weldery</t>
+  </si>
+  <si>
+    <t>Total Mobilization</t>
+  </si>
+  <si>
+    <t>Electricity(Generator)</t>
+  </si>
+  <si>
+    <t>The First Founding</t>
+  </si>
+  <si>
+    <t>Seasons</t>
+  </si>
+  <si>
+    <t>Spring is the most normal season due to unciv not being able to simulate work in the field</t>
+  </si>
+  <si>
+    <t>Summer is the best Season for Hunting/Foraging</t>
+  </si>
+  <si>
+    <t>Autumn is the notable food surplus season</t>
+  </si>
+  <si>
+    <t>Winter demands enough stored food and fuel to survive</t>
+  </si>
+  <si>
+    <t>Pacing</t>
+  </si>
+  <si>
+    <t>Early Game: Population Growth seems impossible, but there are free population through events</t>
+  </si>
+  <si>
+    <t>Early Game: Needing to find foundational resources like seeds, books and generators</t>
+  </si>
+  <si>
+    <t>Mid Game: Clean up the zombies, Set up perimeters</t>
+  </si>
+  <si>
+    <t>Armed Militia</t>
+  </si>
+  <si>
+    <t>Dormitory/Houses</t>
+  </si>
+  <si>
     <t>Fishing</t>
-  </si>
-  <si>
-    <t>Intergration/Special Political Buildings</t>
-  </si>
-  <si>
-    <t>Bathhouse</t>
-  </si>
-  <si>
-    <t>Windmill/Watermill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle Scraping </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean Scavenge </t>
-  </si>
-  <si>
-    <t>Scavenge Expertise</t>
-  </si>
-  <si>
-    <t>Truck Evac Site</t>
-  </si>
-  <si>
-    <t>Engineering</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marine Trades</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Concrete</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recycled Materials</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slaying Horde</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commissars</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Development Plans</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human Rights</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Revitalised Democracy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nothing Against the Unity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cleansing the Corruption</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benevolence for the chosen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>War-forged Nobilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modern Convenience</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Reconstruction</t>
-  </si>
-  <si>
-    <t>Weldery</t>
-  </si>
-  <si>
-    <t>Total Mobilization</t>
-  </si>
-  <si>
-    <t>Hunting Party</t>
-  </si>
-  <si>
-    <t>Electricity(Generator)</t>
-  </si>
-  <si>
-    <t>The First Founding</t>
-  </si>
-  <si>
-    <t>Seasons</t>
-  </si>
-  <si>
-    <t>Spring is the most normal season due to unciv not being able to simulate work in the field</t>
-  </si>
-  <si>
-    <t>Summer is the best Season for Hunting/Foraging</t>
-  </si>
-  <si>
-    <t>Autumn is the notable food surplus season</t>
-  </si>
-  <si>
-    <t>Winter demands enough stored food and fuel to survive</t>
-  </si>
-  <si>
-    <t>Pacing</t>
-  </si>
-  <si>
-    <t>Early Game: Population Growth seems impossible, but there are free population through events</t>
-  </si>
-  <si>
-    <t>Early Game: Needing to find foundational resources like seeds, books and generators</t>
-  </si>
-  <si>
-    <t>Mid Game: Clean up the zombies, Set up perimeters</t>
-  </si>
-  <si>
-    <t>Armed Militia</t>
-  </si>
-  <si>
-    <t>Dormitory/Houses</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sharpen the Blade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Down with the Rotten</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore Industry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Restore the Peace</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamping</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reinforced Hull</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zed Siren</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drone Support</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mobile HQ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato Cannon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medicine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Same as farm with more food</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unique Units</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plane Graveyard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Global Water Bonus</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Free Buildings</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drones</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Line17</t>
+  </si>
+  <si>
+    <t>Outward Reclaimation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Telecommunication</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Combined Arms</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Architecture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Improvised Weapons</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vehicle Engineering</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mechanised Construction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internal Monopoly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fight for the deceased</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Information Era</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2219,7 +2277,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2382,9 +2440,6 @@
     <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2406,14 +2461,23 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2729,44 +2793,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A5130F-E574-431A-B02D-D2C6DE486462}">
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="66.599999999999994" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="23.88671875" style="16"/>
+    <col min="1" max="16384" width="23.875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A1" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63" t="s">
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63" t="s">
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63" t="s">
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-    </row>
-    <row r="2" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+    </row>
+    <row r="2" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A2" s="49" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B2" s="49" t="s">
         <v>0</v>
@@ -2789,9 +2854,7 @@
       <c r="H2" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="49" t="s">
-        <v>7</v>
-      </c>
+      <c r="I2" s="49"/>
       <c r="J2" s="49" t="s">
         <v>8</v>
       </c>
@@ -2816,35 +2879,41 @@
       <c r="Q2" s="49" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R2" s="49" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A3" s="49">
         <v>3</v>
       </c>
       <c r="B3" s="50"/>
       <c r="C3" s="50" t="s">
-        <v>532</v>
+        <v>501</v>
       </c>
       <c r="D3" s="50"/>
       <c r="E3" s="50"/>
       <c r="F3" s="50"/>
       <c r="G3" s="50" t="s">
-        <v>538</v>
+        <v>507</v>
       </c>
       <c r="H3" s="50"/>
       <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="51"/>
+      <c r="J3" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="51"/>
+      <c r="L3" s="56"/>
       <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
+      <c r="N3" s="51" t="s">
+        <v>71</v>
+      </c>
       <c r="O3" s="51"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="53"/>
-    </row>
-    <row r="4" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R3" s="53"/>
+    </row>
+    <row r="4" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -2853,307 +2922,321 @@
       </c>
       <c r="C4" s="50"/>
       <c r="D4" s="50" t="s">
-        <v>534</v>
+        <v>503</v>
       </c>
       <c r="E4" s="50" t="s">
-        <v>536</v>
+        <v>505</v>
       </c>
       <c r="F4" s="50" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="G4" s="50"/>
       <c r="H4" s="50" t="s">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="I4" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="O4" s="51" t="s">
-        <v>55</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J4" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="56"/>
+      <c r="M4" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
       <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-    </row>
-    <row r="5" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="52" t="s">
+        <v>556</v>
+      </c>
+      <c r="R4" s="53"/>
+    </row>
+    <row r="5" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A5" s="49">
         <v>5</v>
       </c>
       <c r="B5" s="50"/>
       <c r="C5" s="50" t="s">
-        <v>533</v>
+        <v>502</v>
       </c>
       <c r="D5" s="50"/>
       <c r="E5" s="50"/>
       <c r="F5" s="50"/>
       <c r="G5" s="50" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="H5" s="50"/>
       <c r="I5" s="50"/>
       <c r="J5" s="51" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K5" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="51" t="s">
+        <v>525</v>
+      </c>
+      <c r="L5" s="56"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51" t="s">
-        <v>80</v>
-      </c>
       <c r="P5" s="52" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="Q5" s="53"/>
-    </row>
-    <row r="6" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R5" s="53"/>
+    </row>
+    <row r="6" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A6" s="49">
         <v>6</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55" t="s">
-        <v>528</v>
-      </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54" t="s">
+        <v>522</v>
+      </c>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="55"/>
-      <c r="H6" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="56"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51" t="s">
-        <v>54</v>
-      </c>
+      <c r="G6" s="54"/>
+      <c r="H6" s="55" t="s">
+        <v>524</v>
+      </c>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>562</v>
+      </c>
+      <c r="L6" s="64"/>
+      <c r="M6" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="51"/>
       <c r="O6" s="51"/>
       <c r="P6" s="53"/>
       <c r="Q6" s="53"/>
-    </row>
-    <row r="7" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="53"/>
+    </row>
+    <row r="7" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A7" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="B7" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55" t="s">
-        <v>329</v>
-      </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="57" t="s">
-        <v>212</v>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54" t="s">
+        <v>523</v>
+      </c>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55" t="s">
+        <v>559</v>
+      </c>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56" t="s">
+        <v>195</v>
       </c>
       <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="P7" s="53"/>
+      <c r="N7" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="51"/>
+      <c r="P7" s="52" t="s">
+        <v>554</v>
+      </c>
       <c r="Q7" s="52" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+      <c r="R7" s="52" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A8" s="49">
         <v>8</v>
       </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55" t="s">
-        <v>540</v>
-      </c>
-      <c r="E8" s="55"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="54"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="58"/>
-      <c r="J8" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="52" t="s">
-        <v>84</v>
-      </c>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="K8" s="59"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="59"/>
+      <c r="O8" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="53"/>
       <c r="Q8" s="53"/>
-    </row>
-    <row r="9" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R8" s="53"/>
+    </row>
+    <row r="9" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A9" s="49">
         <v>9</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58" t="s">
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57" t="s">
+        <v>560</v>
+      </c>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58" t="s">
+      <c r="H9" s="57"/>
+      <c r="I9" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="P9" s="53"/>
+      <c r="J9" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="56"/>
+      <c r="M9" s="59"/>
+      <c r="N9" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="59"/>
+      <c r="P9" s="52" t="s">
+        <v>73</v>
+      </c>
       <c r="Q9" s="53"/>
-    </row>
-    <row r="10" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R9" s="53"/>
+    </row>
+    <row r="10" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A10" s="49">
         <v>10</v>
       </c>
-      <c r="B10" s="58" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>539</v>
-      </c>
-      <c r="D10" s="58" t="s">
+      <c r="B10" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>508</v>
+      </c>
+      <c r="D10" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58" t="s">
-        <v>542</v>
-      </c>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58" t="s">
+      <c r="E10" s="57"/>
+      <c r="F10" s="57" t="s">
+        <v>510</v>
+      </c>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="58"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q10" s="53"/>
-    </row>
-    <row r="11" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="57"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="59" t="s">
+        <v>561</v>
+      </c>
+      <c r="L10" s="56"/>
+      <c r="M10" s="59" t="s">
+        <v>526</v>
+      </c>
+      <c r="N10" s="59"/>
+      <c r="O10" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="52" t="s">
+        <v>558</v>
+      </c>
+      <c r="R10" s="53"/>
+    </row>
+    <row r="11" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="A11" s="49">
         <v>11</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="59" t="s">
+        <v>553</v>
+      </c>
+      <c r="K11" s="59"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
       <c r="P11" s="53"/>
       <c r="Q11" s="53"/>
-    </row>
-    <row r="13" spans="1:17" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R11" s="53"/>
+    </row>
+    <row r="13" spans="1:18" ht="66.599999999999994" customHeight="1">
       <c r="B13" s="22" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="I13" s="48" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="N1:R1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3164,73 +3247,73 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1">
       <c r="A1" s="31" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>548</v>
+        <v>516</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -3243,38 +3326,38 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="31.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1"/>
   <cols>
-    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="51.6" customHeight="1">
       <c r="A1" s="32" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="H1" s="32"/>
     </row>
-    <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="51.6" customHeight="1">
       <c r="A2" s="33" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -3286,63 +3369,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65E430D-86E9-43E2-AFAF-E995519B62A8}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="23.109375" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="23.109375" style="7"/>
+    <col min="1" max="16384" width="23.125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="60" customHeight="1">
       <c r="B1" s="7" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>527</v>
+        <v>497</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" customHeight="1">
       <c r="A2" s="26" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" customHeight="1">
       <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="62"/>
@@ -3352,197 +3435,197 @@
       <c r="H3" s="62"/>
       <c r="I3" s="62"/>
       <c r="J3" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" customHeight="1">
       <c r="A4" s="26" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="H4" s="34"/>
       <c r="K4" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="60" customHeight="1">
       <c r="A5" s="26" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="60" customHeight="1">
       <c r="A6" s="26" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60" customHeight="1">
       <c r="A7" s="26" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" customHeight="1">
       <c r="A8" s="26" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60" customHeight="1">
       <c r="A9" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="60" customHeight="1">
       <c r="A10" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>553</v>
+        <v>521</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" customHeight="1">
       <c r="A11" s="26" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="60" customHeight="1">
       <c r="A12" s="26" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="60" customHeight="1">
       <c r="A13" s="26" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="60" customHeight="1">
       <c r="A14" s="26" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="60" customHeight="1">
       <c r="A15" s="26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="60" customHeight="1">
       <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="60" customHeight="1">
       <c r="A17" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="60" customHeight="1">
       <c r="A18" s="26" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="60" customHeight="1">
       <c r="A19" s="26"/>
     </row>
-    <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="60" customHeight="1">
       <c r="A20" s="26"/>
     </row>
-    <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="60" customHeight="1">
       <c r="A21" s="26"/>
     </row>
-    <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" ht="60" customHeight="1">
       <c r="A22" s="26"/>
     </row>
-    <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" ht="60" customHeight="1">
       <c r="A23" s="26"/>
     </row>
-    <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" ht="60" customHeight="1">
       <c r="A24" s="35"/>
     </row>
-    <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" ht="60" customHeight="1">
       <c r="A25" s="35"/>
     </row>
-    <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" ht="60" customHeight="1">
       <c r="A26" s="35"/>
     </row>
-    <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" ht="60" customHeight="1">
       <c r="A27" s="35"/>
     </row>
-    <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" ht="60" customHeight="1">
       <c r="A28" s="35"/>
     </row>
   </sheetData>
@@ -3558,85 +3641,85 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9525DAE-B4B3-486C-A4F4-FDA26BC38E74}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="19.88671875" defaultRowHeight="54.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="54.6" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="19.88671875" style="7"/>
+    <col min="1" max="1" width="19.875" style="7" customWidth="1"/>
+    <col min="2" max="16384" width="19.875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="54.6" customHeight="1">
       <c r="B1" s="7" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="54" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>118</v>
-      </c>
       <c r="I2" s="7" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="54.6" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>526</v>
+        <v>496</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="62"/>
@@ -3645,68 +3728,68 @@
       <c r="G3" s="62"/>
       <c r="H3" s="62"/>
       <c r="I3" s="7" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="54.6" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="54.6" customHeight="1">
       <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="54.6" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>552</v>
+        <v>520</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54.6" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="54.6" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="62" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="C8" s="62"/>
       <c r="D8" s="62"/>
@@ -3715,290 +3798,290 @@
       <c r="G8" s="62"/>
       <c r="H8" s="62"/>
     </row>
-    <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="54.6" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="54.6" customHeight="1">
       <c r="A10" s="13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="54.6" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>252</v>
-      </c>
       <c r="M11" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="54.6" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="54.6" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="54.6" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G14" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>249</v>
-      </c>
       <c r="L14" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="54.6" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="54.6" customHeight="1">
       <c r="A16" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="54.6" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="54.6" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="54.6" customHeight="1">
+      <c r="A19" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="54.6" customHeight="1">
+      <c r="A20" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="54.6" customHeight="1">
+      <c r="A21" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="54.6" customHeight="1">
+      <c r="A22" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="54.6" customHeight="1">
+      <c r="A23" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="M23" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:13" ht="54.6" customHeight="1">
       <c r="A24" s="10" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="54.6" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="54.6" customHeight="1">
       <c r="A26" s="10" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="54.6" customHeight="1">
       <c r="A27" s="15" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="54.6" customHeight="1">
       <c r="A28" s="15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -4013,304 +4096,405 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57FA41E-923B-4197-8F1B-833786480AFE}">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="20.6640625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" customHeight="1">
       <c r="A1" s="39" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.6" customHeight="1">
       <c r="A2" s="36"/>
       <c r="B2" s="36" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="D2" s="36"/>
     </row>
-    <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.6" customHeight="1">
       <c r="A3" s="36" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="B3" s="36"/>
       <c r="C3" s="36" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="D3" s="36"/>
     </row>
-    <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.6" customHeight="1">
       <c r="A4" s="36"/>
       <c r="B4" s="36" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="D4" s="36"/>
     </row>
-    <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.6" customHeight="1">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="D5" s="36"/>
     </row>
-    <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15.6" customHeight="1">
       <c r="A6" s="37"/>
       <c r="B6" s="37" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="E6" s="37"/>
     </row>
-    <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15.6" customHeight="1">
       <c r="A7" s="37" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.6" customHeight="1">
       <c r="A8" s="37"/>
       <c r="B8" s="37" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="E8" s="37"/>
     </row>
-    <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="15.6" customHeight="1">
       <c r="A9" s="37"/>
       <c r="B9" s="37" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="E9" s="37"/>
     </row>
-    <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.6" customHeight="1">
       <c r="A10" s="37"/>
       <c r="B10" s="37" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="E10" s="37"/>
     </row>
-    <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15.6" customHeight="1">
       <c r="A11" s="37"/>
       <c r="B11" s="37" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="E11" s="37"/>
     </row>
-    <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15.6" customHeight="1">
       <c r="A12" s="38" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" customHeight="1">
       <c r="A13" s="38"/>
       <c r="B13" s="38" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
     </row>
-    <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15.6" customHeight="1">
       <c r="A14" s="38" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="E14" s="38"/>
     </row>
-    <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="15.6" customHeight="1">
       <c r="A15" s="38"/>
       <c r="B15" s="38" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
     </row>
-    <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="15.6" customHeight="1">
       <c r="A16" s="38" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
     </row>
-    <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15.6" customHeight="1">
       <c r="A17" s="38"/>
       <c r="B17" s="38" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
     </row>
-    <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15.6" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
       <c r="E18" s="38"/>
     </row>
-    <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="15.6" customHeight="1">
       <c r="A19" s="38"/>
       <c r="B19" s="38" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.6" customHeight="1">
       <c r="A20" s="38"/>
       <c r="B20" s="38" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="D20" s="38"/>
       <c r="E20" s="38"/>
     </row>
-    <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15.6" customHeight="1">
       <c r="A21" s="38" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="E21" s="38"/>
     </row>
-    <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="15.6" customHeight="1">
       <c r="A22" s="38" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
     </row>
-    <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15.6" customHeight="1">
       <c r="A23" s="38"/>
       <c r="B23" s="38" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="E23" s="38"/>
     </row>
-    <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15.6" customHeight="1">
       <c r="A24" s="38" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>425</v>
+        <v>546</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>437</v>
-      </c>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A25" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>542</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>543</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>544</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A28" s="65"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A29" s="65"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A30" s="65"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A31" s="65"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A32" s="65"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+    </row>
+    <row r="33" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A33" s="65"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A34" s="65"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A35" s="65"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+    </row>
+    <row r="36" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A36" s="65"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+    </row>
+    <row r="37" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A37" s="65"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A38" s="65"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4320,339 +4504,341 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01988B0-73BA-4CA6-BE31-7ADFE60DCE4E}">
-  <dimension ref="A1:Q7"/>
-  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="51" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64" t="s">
+        <v>565</v>
+      </c>
+      <c r="B1" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-    </row>
-    <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+    </row>
+    <row r="2" spans="1:17" ht="51" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="L2" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q2" s="29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="51" customHeight="1">
+      <c r="B3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="D3" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="51" customHeight="1">
+      <c r="B4" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="51" customHeight="1">
+      <c r="B5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="51" customHeight="1">
+      <c r="B6" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="D6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="O2" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="P2" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="29" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="O6" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P6" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>201</v>
-      </c>
       <c r="Q6" s="6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>76</v>
-      </c>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="51" customHeight="1">
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>166</v>
+        <v>532</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>202</v>
+        <v>540</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>206</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="51" customHeight="1">
+      <c r="B9" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4671,137 +4857,134 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD73BA7-6743-4814-9106-0092E73F08DA}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="20.77734375" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="20.77734375" style="40"/>
+    <col min="1" max="16384" width="20.75" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="67.5" customHeight="1">
       <c r="B1" s="42" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>441</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="E1" s="41" t="s">
-        <v>443</v>
+        <v>459</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>415</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>416</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>535</v>
+        <v>418</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>489</v>
-      </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
+        <v>504</v>
+      </c>
       <c r="N1" s="41"/>
     </row>
-    <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="67.5" customHeight="1">
       <c r="A2" s="40" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="C2" s="40" t="s">
+        <v>462</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>420</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>422</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="67.5" customHeight="1">
+      <c r="A3" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="40" t="s">
-        <v>451</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>450</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>452</v>
-      </c>
-      <c r="G2" s="40" t="s">
-        <v>493</v>
-      </c>
-      <c r="H2" s="40" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
-        <v>141</v>
-      </c>
       <c r="B3" s="40" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>139</v>
+        <v>130</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>130</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="67.5" customHeight="1">
       <c r="A4" s="40" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="67.5" customHeight="1">
       <c r="A5" s="40" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>446</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>446</v>
+        <v>552</v>
+      </c>
+      <c r="E5" s="66" t="s">
+        <v>551</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="G5" s="40" t="s">
-        <v>449</v>
+        <v>550</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>448</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -4813,103 +4996,105 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52BDA60A-2197-46FF-A1E9-DE6B49F4104C}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="21.6640625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="54" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="54" customHeight="1">
       <c r="A1" s="45"/>
       <c r="B1" s="24" t="s">
-        <v>498</v>
+        <v>468</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>522</v>
+        <v>492</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>502</v>
+        <v>472</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>471</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>503</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>525</v>
-      </c>
-      <c r="K1" s="46" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="54" customHeight="1">
       <c r="A2" s="45" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D2" s="45" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="E2" s="45" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="F2" s="45" t="s">
-        <v>482</v>
+        <v>452</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>478</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="I2" s="45" t="s">
-        <v>509</v>
-      </c>
-      <c r="J2" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="54" customHeight="1">
+      <c r="A3" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="C3" s="45" t="s">
         <v>272</v>
-      </c>
-      <c r="K2" s="45"/>
-    </row>
-    <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>507</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>290</v>
       </c>
       <c r="D3" s="45"/>
       <c r="E3" s="45"/>
       <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
+      <c r="G3" s="45" t="s">
+        <v>547</v>
+      </c>
       <c r="H3" s="45"/>
       <c r="I3" s="45"/>
       <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-    </row>
-    <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" ht="54" customHeight="1">
       <c r="A4" s="45"/>
       <c r="D4" s="45"/>
       <c r="E4" s="45"/>
       <c r="F4" s="44" t="s">
-        <v>523</v>
-      </c>
-      <c r="G4" s="45"/>
-      <c r="H4" s="44" t="s">
-        <v>524</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>494</v>
+      </c>
+      <c r="H4" s="45"/>
       <c r="I4" s="45"/>
       <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-    </row>
-    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" ht="54" customHeight="1">
       <c r="A5" s="45"/>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
@@ -4922,59 +5107,61 @@
       <c r="J5" s="45"/>
       <c r="K5" s="45"/>
     </row>
-    <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="54" customHeight="1">
       <c r="A6" s="45"/>
-      <c r="B6" s="47" t="s">
-        <v>514</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>438</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>517</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>505</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>512</v>
-      </c>
-      <c r="H6" s="47" t="s">
-        <v>506</v>
-      </c>
-      <c r="I6" s="47" t="s">
-        <v>519</v>
-      </c>
       <c r="J6" s="45"/>
       <c r="K6" s="45"/>
     </row>
-    <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="54" customHeight="1">
       <c r="A7" s="45"/>
-      <c r="B7" s="44" t="s">
-        <v>515</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>516</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>518</v>
-      </c>
-      <c r="F7" s="45" t="s">
-        <v>510</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>513</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>511</v>
-      </c>
-      <c r="I7" s="44" t="s">
-        <v>520</v>
+      <c r="B7" s="47" t="s">
+        <v>484</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>487</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>475</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>482</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>476</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>489</v>
       </c>
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
     </row>
-    <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="54" customHeight="1">
+      <c r="B8" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>480</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="54" customHeight="1">
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
       <c r="D13" s="24"/>
@@ -4988,270 +5175,270 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="38.25" customHeight="1">
       <c r="A1" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="B1" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="38.25" customHeight="1">
+      <c r="A2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="38.25" customHeight="1">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>461</v>
+      </c>
+      <c r="E3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="38.25" customHeight="1">
+      <c r="A4" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="B4" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" s="24" t="s">
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="38.25" customHeight="1">
+      <c r="A5" t="s">
+        <v>328</v>
+      </c>
+      <c r="B5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E5" t="s">
+        <v>329</v>
+      </c>
+      <c r="F5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H5" t="s">
+        <v>330</v>
+      </c>
+      <c r="I5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="38.25" customHeight="1">
+      <c r="B7" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="38.25" customHeight="1">
+      <c r="A8" t="s">
+        <v>465</v>
+      </c>
+      <c r="B8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="38.25" customHeight="1">
+      <c r="B9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
         <v>125</v>
       </c>
-      <c r="F1" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="38.25" customHeight="1">
+      <c r="B10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="38.25" customHeight="1">
+      <c r="B11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D11" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="38.25" customHeight="1">
+      <c r="A13" t="s">
+        <v>466</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="38.25" customHeight="1">
+      <c r="B14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" t="s">
+        <v>427</v>
+      </c>
+      <c r="D14" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="38.25" customHeight="1">
+      <c r="D15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="38.25" customHeight="1">
+      <c r="B16" t="s">
         <v>128</v>
       </c>
-      <c r="I1" s="24" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" t="s">
-        <v>491</v>
-      </c>
-      <c r="E3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>346</v>
-      </c>
-      <c r="B5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D5" t="s">
-        <v>348</v>
-      </c>
-      <c r="E5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H5" t="s">
-        <v>348</v>
-      </c>
-      <c r="I5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>458</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>495</v>
-      </c>
-      <c r="B8" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>348</v>
-      </c>
-      <c r="C11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D11" t="s">
-        <v>348</v>
-      </c>
-      <c r="E11" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>496</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" t="s">
-        <v>457</v>
-      </c>
-      <c r="D14" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>137</v>
-      </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="38.25" customHeight="1">
       <c r="B17" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C17" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="D17" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -5263,147 +5450,147 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="15.88671875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="38.25" customHeight="1">
       <c r="A1" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>463</v>
+        <v>433</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>461</v>
+        <v>431</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="I1" s="24"/>
       <c r="J1" s="24"/>
     </row>
-    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="38.25" customHeight="1">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="D2" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="38.25" customHeight="1">
       <c r="A4" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>464</v>
+        <v>434</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="M4" s="24" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="38.25" customHeight="1">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="C5" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="E5" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="G5" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="H5" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="J5" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="K5" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="L5" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="M5" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="N5" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="O5" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="P5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="38.25" customHeight="1">
       <c r="B7" s="43" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="38.25" customHeight="1">
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
     </row>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chenx\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F81F60-5218-4C5F-B38D-4E1AF94D4502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2954B286-7784-4DCF-8A9C-C24C7337216F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="594" firstSheet="1" activeTab="8" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="594" firstSheet="2" activeTab="9" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -1506,11 +1506,11 @@
   </si>
   <si>
     <t>Housing</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Industry</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Bar</t>
@@ -2012,7 +2012,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2045,31 +2045,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2123,29 +2100,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
@@ -2175,6 +2129,76 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -2281,7 +2305,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2291,194 +2315,197 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2797,442 +2824,472 @@
   <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="23.875" style="11"/>
+    <col min="1" max="16384" width="23.875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54" t="s">
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30" t="s">
         <v>562</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54" t="s">
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
     </row>
     <row r="2" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="H2" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="I2" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="N2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="39" t="s">
+      <c r="P2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="39" t="s">
+      <c r="Q2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="39" t="s">
+      <c r="R2" s="29" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39">
+      <c r="A3" s="29">
         <v>3</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31" t="s">
         <v>556</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40" t="s">
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31" t="s">
         <v>561</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="41" t="s">
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="41"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41" t="s">
+      <c r="K3" s="32"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
     </row>
     <row r="4" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39">
+      <c r="A4" s="29">
         <v>4</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31" t="s">
         <v>558</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="31" t="s">
         <v>559</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="31" t="s">
         <v>526</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="31" t="s">
         <v>563</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="46"/>
-      <c r="M4" s="41" t="s">
+      <c r="L4" s="33"/>
+      <c r="M4" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="42" t="s">
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="34" t="s">
         <v>546</v>
       </c>
-      <c r="R4" s="43"/>
+      <c r="R4" s="35"/>
     </row>
     <row r="5" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="39">
+      <c r="A5" s="29">
         <v>5</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31" t="s">
         <v>557</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40" t="s">
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="41" t="s">
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="32" t="s">
         <v>515</v>
       </c>
-      <c r="L5" s="46"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41" t="s">
+      <c r="L5" s="33"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="O5" s="41" t="s">
+      <c r="O5" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
     </row>
     <row r="6" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="39">
+      <c r="A6" s="29">
         <v>6</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36" t="s">
         <v>512</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45" t="s">
+      <c r="G6" s="36"/>
+      <c r="H6" s="37" t="s">
         <v>514</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45" t="s">
+      <c r="I6" s="37"/>
+      <c r="J6" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="45" t="s">
+      <c r="K6" s="37" t="s">
         <v>552</v>
       </c>
-      <c r="L6" s="51"/>
-      <c r="M6" s="41" t="s">
+      <c r="L6" s="38"/>
+      <c r="M6" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
     </row>
     <row r="7" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44" t="s">
+      <c r="D7" s="36"/>
+      <c r="E7" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44" t="s">
+      <c r="F7" s="36"/>
+      <c r="G7" s="36" t="s">
         <v>513</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45" t="s">
+      <c r="H7" s="37"/>
+      <c r="I7" s="37" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="46" t="s">
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41" t="s">
+      <c r="M7" s="32"/>
+      <c r="N7" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="O7" s="41"/>
-      <c r="P7" s="42" t="s">
+      <c r="O7" s="32"/>
+      <c r="P7" s="34" t="s">
         <v>544</v>
       </c>
-      <c r="Q7" s="42" t="s">
+      <c r="Q7" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="R7" s="42" t="s">
+      <c r="R7" s="34" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="39">
+      <c r="A8" s="29">
         <v>8</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47" t="s">
+      <c r="E8" s="36"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="47"/>
-      <c r="J8" s="48" t="s">
+      <c r="I8" s="39"/>
+      <c r="J8" s="40" t="s">
         <v>531</v>
       </c>
-      <c r="K8" s="49"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="49" t="s">
+      <c r="K8" s="41"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49" t="s">
+      <c r="N8" s="41"/>
+      <c r="O8" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
     </row>
     <row r="9" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="39">
+      <c r="A9" s="29">
         <v>9</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47" t="s">
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39" t="s">
         <v>550</v>
       </c>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47" t="s">
+      <c r="F9" s="39"/>
+      <c r="G9" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47" t="s">
+      <c r="H9" s="39"/>
+      <c r="I9" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="49" t="s">
+      <c r="J9" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="K9" s="49" t="s">
+      <c r="K9" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="46"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="49" t="s">
+      <c r="L9" s="33"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="49"/>
-      <c r="P9" s="42" t="s">
+      <c r="O9" s="41"/>
+      <c r="P9" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
     </row>
     <row r="10" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="39">
+      <c r="A10" s="29">
         <v>10</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="39" t="s">
         <v>500</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47" t="s">
+      <c r="E10" s="39"/>
+      <c r="F10" s="39" t="s">
         <v>560</v>
       </c>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47" t="s">
+      <c r="G10" s="39"/>
+      <c r="H10" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="47"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="49" t="s">
+      <c r="I10" s="39"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="41" t="s">
         <v>551</v>
       </c>
-      <c r="L10" s="46"/>
-      <c r="M10" s="49" t="s">
+      <c r="L10" s="33"/>
+      <c r="M10" s="41" t="s">
         <v>516</v>
       </c>
-      <c r="N10" s="49"/>
-      <c r="O10" s="49" t="s">
+      <c r="N10" s="41"/>
+      <c r="O10" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="42" t="s">
+      <c r="P10" s="35"/>
+      <c r="Q10" s="34" t="s">
         <v>548</v>
       </c>
-      <c r="R10" s="43"/>
+      <c r="R10" s="35"/>
     </row>
     <row r="11" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="39">
+      <c r="A11" s="29">
         <v>11</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47" t="s">
+      <c r="F11" s="39"/>
+      <c r="G11" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47" t="s">
+      <c r="H11" s="39"/>
+      <c r="I11" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="49" t="s">
+      <c r="J11" s="41" t="s">
         <v>543</v>
       </c>
-      <c r="K11" s="49"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="49"/>
-      <c r="N11" s="49"/>
-      <c r="O11" s="49"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+    </row>
+    <row r="12" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
     </row>
     <row r="13" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="43"/>
+      <c r="B13" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="49" t="s">
         <v>200</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="I13" s="38" t="s">
+      <c r="I13" s="33" t="s">
         <v>194</v>
       </c>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3253,19 +3310,19 @@
   <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="5" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3335,31 +3392,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="H1" s="23"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" ht="51.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="8" t="s">
         <v>256</v>
       </c>
     </row>
@@ -3374,267 +3431,267 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="23.125" style="2"/>
+    <col min="1" max="16384" width="23.125" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="51" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="51" t="s">
         <v>495</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="51" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="51" t="s">
         <v>273</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="51" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="53" t="s">
         <v>282</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="2" t="s">
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="51" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="51" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="51" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="51" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="51" t="s">
         <v>278</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="51" t="s">
         <v>281</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="51" t="s">
         <v>316</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="51" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="51" t="s">
         <v>288</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="51" t="s">
         <v>496</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="51" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="51" t="s">
         <v>498</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="51" t="s">
         <v>279</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="51" t="s">
         <v>497</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="51" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="51" t="s">
         <v>311</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="51" t="s">
         <v>315</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="51" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="51" t="s">
         <v>511</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="51" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="52" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="52" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="52" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="52" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="52" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="52" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="52" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="A19" s="52"/>
     </row>
     <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="A20" s="52"/>
     </row>
     <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
+      <c r="A21" s="52"/>
     </row>
     <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
+      <c r="A22" s="52"/>
     </row>
     <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
+      <c r="A23" s="52"/>
     </row>
     <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="25"/>
+      <c r="A24" s="54"/>
     </row>
     <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
+      <c r="A25" s="54"/>
     </row>
     <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="25"/>
+      <c r="A26" s="54"/>
     </row>
     <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="25"/>
+      <c r="A27" s="54"/>
     </row>
     <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="25"/>
+      <c r="A28" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:I3"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -3650,441 +3707,670 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="51"/>
+      <c r="B1" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="51" t="s">
         <v>341</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="51" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="51"/>
+      <c r="H2" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="51" t="s">
         <v>182</v>
       </c>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="55" t="s">
         <v>494</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="2" t="s">
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="51" t="s">
         <v>301</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51" t="s">
         <v>207</v>
       </c>
+      <c r="M3" s="51"/>
     </row>
     <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="51" t="s">
         <v>103</v>
       </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
     </row>
     <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51" t="s">
         <v>240</v>
       </c>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
     </row>
     <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="51"/>
+      <c r="F6" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51" t="s">
         <v>277</v>
       </c>
+      <c r="M6" s="51"/>
     </row>
     <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="51" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="53" t="s">
         <v>300</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
     </row>
     <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51" t="s">
         <v>302</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="K9" s="51"/>
+      <c r="L9" s="51" t="s">
         <v>209</v>
       </c>
+      <c r="M9" s="51"/>
     </row>
     <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51" t="s">
         <v>304</v>
       </c>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
     </row>
     <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="L11" s="51"/>
+      <c r="M11" s="51" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51" t="s">
         <v>227</v>
       </c>
+      <c r="M12" s="51"/>
     </row>
     <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="J13" s="51"/>
+      <c r="K13" s="51" t="s">
         <v>219</v>
       </c>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
     </row>
     <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51" t="s">
         <v>214</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="K14" s="51"/>
+      <c r="L14" s="51" t="s">
         <v>299</v>
       </c>
+      <c r="M14" s="51"/>
     </row>
     <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51" t="s">
         <v>298</v>
       </c>
+      <c r="M15" s="51"/>
     </row>
     <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51" t="s">
         <v>237</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="F16" s="51"/>
+      <c r="G16" s="51" t="s">
         <v>295</v>
       </c>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
     </row>
     <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="51"/>
+      <c r="C17" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51" t="s">
         <v>235</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="L17" s="51"/>
+      <c r="M17" s="51" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="51"/>
+      <c r="C18" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="L18" s="51"/>
+      <c r="M18" s="51" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="51" t="s">
         <v>241</v>
       </c>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
     </row>
     <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="K20" s="51"/>
+      <c r="L20" s="51" t="s">
         <v>226</v>
       </c>
+      <c r="M20" s="51"/>
     </row>
     <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="51"/>
+      <c r="C21" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51" t="s">
         <v>342</v>
       </c>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
     </row>
     <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="60" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="51" t="s">
         <v>343</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="L23" s="51"/>
+      <c r="M23" s="51" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51" t="s">
         <v>294</v>
       </c>
+      <c r="M24" s="51"/>
     </row>
     <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="B25" s="51"/>
+      <c r="C25" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51" t="s">
         <v>293</v>
       </c>
+      <c r="M25" s="51"/>
     </row>
     <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="B26" s="51"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="51"/>
+      <c r="C27" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51" t="s">
         <v>307</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="L27" s="51"/>
+      <c r="M27" s="51" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51" t="s">
         <v>292</v>
       </c>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4102,401 +4388,409 @@
   <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="63" t="s">
         <v>344</v>
       </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="64"/>
+      <c r="B2" s="64" t="s">
         <v>346</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="64" t="s">
         <v>347</v>
       </c>
-      <c r="D2" s="26"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="64" t="s">
         <v>345</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26" t="s">
+      <c r="B3" s="64"/>
+      <c r="C3" s="64" t="s">
         <v>348</v>
       </c>
-      <c r="D3" s="26"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64" t="s">
         <v>349</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="64" t="s">
         <v>350</v>
       </c>
-      <c r="D4" s="26"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26" t="s">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64" t="s">
         <v>351</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="65" t="s">
         <v>352</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="65" t="s">
         <v>353</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="65" t="s">
         <v>354</v>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="65"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="65" t="s">
         <v>355</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="65" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="65" t="s">
         <v>358</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="65" t="s">
         <v>359</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="65" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="65"/>
+      <c r="B8" s="65" t="s">
         <v>360</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="65" t="s">
         <v>361</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="65" t="s">
         <v>362</v>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="65"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27" t="s">
+      <c r="A9" s="65"/>
+      <c r="B9" s="65" t="s">
         <v>363</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="65" t="s">
         <v>364</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="65" t="s">
         <v>365</v>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="65"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27" t="s">
+      <c r="A10" s="65"/>
+      <c r="B10" s="65" t="s">
         <v>366</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="65" t="s">
         <v>367</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="65" t="s">
         <v>368</v>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="65"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="65" t="s">
         <v>369</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="65" t="s">
         <v>370</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="65" t="s">
         <v>371</v>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="65"/>
     </row>
     <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="66" t="s">
         <v>372</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="66" t="s">
         <v>373</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="66" t="s">
         <v>374</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="66" t="s">
         <v>375</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="66" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="66"/>
+      <c r="B13" s="66" t="s">
         <v>377</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="66" t="s">
         <v>378</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
     </row>
     <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="66" t="s">
         <v>379</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="66" t="s">
         <v>380</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="66" t="s">
         <v>381</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="66" t="s">
         <v>382</v>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="66"/>
     </row>
     <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28" t="s">
+      <c r="A15" s="66"/>
+      <c r="B15" s="66" t="s">
         <v>383</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="66" t="s">
         <v>384</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="66" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="66" t="s">
         <v>390</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28" t="s">
+      <c r="A17" s="66"/>
+      <c r="B17" s="66" t="s">
         <v>391</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="66" t="s">
         <v>398</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="66" t="s">
         <v>392</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28" t="s">
+      <c r="A19" s="66"/>
+      <c r="B19" s="66" t="s">
         <v>393</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="66" t="s">
         <v>399</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="66" t="s">
         <v>400</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="66" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28" t="s">
+      <c r="A20" s="66"/>
+      <c r="B20" s="66" t="s">
         <v>394</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="66" t="s">
         <v>402</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="66" t="s">
         <v>387</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="66" t="s">
         <v>395</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="66" t="s">
         <v>403</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="66" t="s">
         <v>404</v>
       </c>
-      <c r="E21" s="28"/>
+      <c r="E21" s="66"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="66" t="s">
         <v>388</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="66" t="s">
         <v>396</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="66" t="s">
         <v>405</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
     </row>
     <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28" t="s">
+      <c r="A23" s="66"/>
+      <c r="B23" s="66" t="s">
         <v>397</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="66" t="s">
         <v>406</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="66" t="s">
         <v>410</v>
       </c>
-      <c r="E23" s="28"/>
+      <c r="E23" s="66"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="66" t="s">
         <v>389</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="66" t="s">
         <v>536</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="66" t="s">
         <v>407</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="66" t="s">
         <v>408</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="66" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="66" t="s">
         <v>532</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="66" t="s">
         <v>533</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="66" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="52"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="52"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="52"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="52"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="52"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="52"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="34" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="52"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
     </row>
     <row r="35" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="52"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
     </row>
     <row r="36" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="52"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
     </row>
     <row r="38" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4509,379 +4803,379 @@
   <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultColWidth="16" defaultRowHeight="51" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="16" style="58"/>
+    <col min="1" max="16384" width="16" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="19" t="s">
         <v>555</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57" t="s">
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="56"/>
-      <c r="B2" s="59" t="s">
+      <c r="A2" s="19"/>
+      <c r="B2" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="K2" s="61" t="s">
+      <c r="K2" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="61" t="s">
+      <c r="L2" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="M2" s="62" t="s">
+      <c r="M2" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="62" t="s">
+      <c r="N2" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="63" t="s">
+      <c r="O2" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="P2" s="63" t="s">
+      <c r="P2" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="63" t="s">
+      <c r="Q2" s="25" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="64"/>
-      <c r="B3" s="56" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="D3" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="19" t="s">
         <v>520</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="19" t="s">
         <v>521</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="K3" s="56" t="s">
+      <c r="K3" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="L3" s="56" t="s">
+      <c r="L3" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="N3" s="56" t="s">
+      <c r="N3" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="O3" s="56" t="s">
+      <c r="O3" s="19" t="s">
         <v>527</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="Q3" s="56" t="s">
+      <c r="Q3" s="19" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="64"/>
-      <c r="B4" s="56" t="s">
+      <c r="A4" s="26"/>
+      <c r="B4" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="19" t="s">
         <v>564</v>
       </c>
-      <c r="G4" s="56" t="s">
+      <c r="G4" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="H4" s="56" t="s">
+      <c r="H4" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="J4" s="56" t="s">
+      <c r="J4" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="K4" s="56" t="s">
+      <c r="K4" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="L4" s="56" t="s">
+      <c r="L4" s="19" t="s">
         <v>554</v>
       </c>
-      <c r="M4" s="56" t="s">
+      <c r="M4" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="N4" s="56" t="s">
+      <c r="N4" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="O4" s="56" t="s">
+      <c r="O4" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="P4" s="56" t="s">
+      <c r="P4" s="19" t="s">
         <v>528</v>
       </c>
-      <c r="Q4" s="56" t="s">
+      <c r="Q4" s="19" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="64"/>
-      <c r="B5" s="56" t="s">
+      <c r="A5" s="26"/>
+      <c r="B5" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="D5" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="E5" s="56" t="s">
+      <c r="E5" s="19" t="s">
         <v>517</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G5" s="56" t="s">
+      <c r="G5" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="H5" s="56" t="s">
+      <c r="H5" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="I5" s="56" t="s">
+      <c r="I5" s="19" t="s">
         <v>524</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="K5" s="56" t="s">
+      <c r="K5" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="L5" s="56" t="s">
+      <c r="L5" s="19" t="s">
         <v>525</v>
       </c>
-      <c r="M5" s="56" t="s">
+      <c r="M5" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="N5" s="56" t="s">
+      <c r="N5" s="19" t="s">
         <v>553</v>
       </c>
-      <c r="O5" s="56" t="s">
+      <c r="O5" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="P5" s="56" t="s">
+      <c r="P5" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="Q5" s="56" t="s">
+      <c r="Q5" s="19" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="64"/>
-      <c r="B6" s="56" t="s">
+      <c r="A6" s="26"/>
+      <c r="B6" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="19" t="s">
         <v>518</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="19" t="s">
         <v>519</v>
       </c>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="19" t="s">
         <v>523</v>
       </c>
-      <c r="I6" s="56" t="s">
+      <c r="I6" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="J6" s="56" t="s">
+      <c r="J6" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="K6" s="56" t="s">
+      <c r="K6" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="L6" s="56" t="s">
+      <c r="L6" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="M6" s="56" t="s">
+      <c r="M6" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="N6" s="56" t="s">
+      <c r="N6" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="O6" s="56" t="s">
+      <c r="O6" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="P6" s="56" t="s">
+      <c r="P6" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="Q6" s="56" t="s">
+      <c r="Q6" s="19" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="64"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="E7" s="56" t="s">
+      <c r="E7" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F7" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G7" s="56" t="s">
+      <c r="G7" s="19" t="s">
         <v>522</v>
       </c>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="I7" s="56" t="s">
+      <c r="I7" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="J7" s="56" t="s">
+      <c r="J7" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="K7" s="64"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56" t="s">
+      <c r="K7" s="26"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="P7" s="56" t="s">
+      <c r="P7" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="Q7" s="56" t="s">
+      <c r="Q7" s="19" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
     </row>
     <row r="9" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="64"/>
-      <c r="B9" s="59" t="s">
+      <c r="A9" s="26"/>
+      <c r="B9" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="65" t="s">
+      <c r="E9" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="64"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="64"/>
-      <c r="Q9" s="64"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4901,131 +5195,131 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="20.75" defaultRowHeight="67.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="20.75" style="30"/>
+    <col min="1" max="16384" width="20.75" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="N1" s="31"/>
+      <c r="N1" s="10"/>
     </row>
     <row r="2" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="9" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="9" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="18" t="s">
         <v>541</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="9" t="s">
         <v>539</v>
       </c>
     </row>
@@ -5041,172 +5335,172 @@
   <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="54" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35"/>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="15" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="13" t="s">
         <v>489</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="13" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="14" t="s">
         <v>475</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
         <v>537</v>
       </c>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="34" t="s">
+      <c r="A4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
+      <c r="A6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35"/>
-      <c r="B7" s="37" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="16" t="s">
         <v>473</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="16" t="s">
         <v>474</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="16" t="s">
         <v>487</v>
       </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="13" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5223,28 +5517,28 @@
       <c r="A1" t="s">
         <v>462</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="4" t="s">
         <v>465</v>
       </c>
     </row>
@@ -5356,19 +5650,19 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="4" t="s">
         <v>427</v>
       </c>
     </row>
@@ -5435,13 +5729,13 @@
       <c r="A13" t="s">
         <v>464</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="4" t="s">
         <v>308</v>
       </c>
     </row>
@@ -5498,23 +5792,23 @@
       <c r="A1" t="s">
         <v>447</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -5537,49 +5831,49 @@
       <c r="A4" t="s">
         <v>448</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="M4" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="N4" s="19" t="s">
+      <c r="N4" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="4" t="s">
         <v>442</v>
       </c>
     </row>
@@ -5625,16 +5919,16 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="5" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Silly zombie game.xlsx
+++ b/Silly zombie game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\unciv-windows64\mods\Zombie-Apocalypse-DEMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2954B286-7784-4DCF-8A9C-C24C7337216F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6005FD0-53D4-4DA3-82CA-96B2D2F6BF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" tabRatio="594" firstSheet="2" activeTab="9" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="594" firstSheet="3" activeTab="7" xr2:uid="{8A136F01-EAE7-4255-A1EA-2D260870475D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tech Tree" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,11 @@
     <sheet name="Policy Tree" sheetId="3" r:id="rId5"/>
     <sheet name="Locations(Wonder)" sheetId="11" r:id="rId6"/>
     <sheet name="Improvements" sheetId="14" r:id="rId7"/>
-    <sheet name="Locations(RES)" sheetId="5" r:id="rId8"/>
-    <sheet name="Terrain" sheetId="13" r:id="rId9"/>
-    <sheet name="C.Mechanics" sheetId="6" r:id="rId10"/>
-    <sheet name="U.Mechanics" sheetId="8" r:id="rId11"/>
+    <sheet name="Locations(RES) (2)" sheetId="15" r:id="rId8"/>
+    <sheet name="Locations(RES)" sheetId="5" r:id="rId9"/>
+    <sheet name="Terrain" sheetId="13" r:id="rId10"/>
+    <sheet name="C.Mechanics" sheetId="6" r:id="rId11"/>
+    <sheet name="U.Mechanics" sheetId="8" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="606">
   <si>
     <t>Line1</t>
   </si>
@@ -2005,6 +2006,170 @@
   </si>
   <si>
     <t>Freedom and Suffrage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Terrain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lake</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plains</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Street</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Highrise</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Barns</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gas Station</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Office</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warehouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harbour</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medicines</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weaponry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fuel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Single Story Building</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Multi Story Building</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TF\Resources:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Community Garden</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Military Surplus Store</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Industrial Warehouse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Commercial Zone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parking Lot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Granary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aquaculture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Abandoned Evac Site</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Church</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hunts</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cabin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Medicinal Herbs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Books</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Library</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bookstore</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Watertower</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water Purification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Perishable Food</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recreation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Materials</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2205,7 +2370,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2290,8 +2455,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2299,13 +2482,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2390,122 +2586,149 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2828,468 +3051,468 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30" t="s">
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30" t="s">
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65" t="s">
         <v>562</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30" t="s">
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
     </row>
     <row r="2" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="P2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="Q2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="29" t="s">
+      <c r="R2" s="28" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29">
+      <c r="A3" s="28">
         <v>3</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="30" t="s">
         <v>556</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30" t="s">
         <v>561</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="32" t="s">
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32" t="s">
+      <c r="K3" s="31"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
     </row>
     <row r="4" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29">
+      <c r="A4" s="28">
         <v>4</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31" t="s">
+      <c r="C4" s="30"/>
+      <c r="D4" s="30" t="s">
         <v>558</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="30" t="s">
         <v>559</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="30" t="s">
         <v>526</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31" t="s">
+      <c r="G4" s="30"/>
+      <c r="H4" s="30" t="s">
         <v>563</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="33"/>
-      <c r="M4" s="32" t="s">
+      <c r="L4" s="32"/>
+      <c r="M4" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="34" t="s">
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="33" t="s">
         <v>546</v>
       </c>
-      <c r="R4" s="35"/>
+      <c r="R4" s="34"/>
     </row>
     <row r="5" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="29">
+      <c r="A5" s="28">
         <v>5</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="30" t="s">
         <v>557</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31" t="s">
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="32" t="s">
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="31" t="s">
         <v>515</v>
       </c>
-      <c r="L5" s="33"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32" t="s">
+      <c r="L5" s="32"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="O5" s="32" t="s">
+      <c r="O5" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="34" t="s">
+      <c r="P5" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
     </row>
     <row r="6" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="29">
+      <c r="A6" s="28">
         <v>6</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36" t="s">
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35" t="s">
         <v>512</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36" t="s">
+      <c r="E6" s="35"/>
+      <c r="F6" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37" t="s">
+      <c r="G6" s="35"/>
+      <c r="H6" s="36" t="s">
         <v>514</v>
       </c>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37" t="s">
+      <c r="I6" s="36"/>
+      <c r="J6" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="36" t="s">
         <v>552</v>
       </c>
-      <c r="L6" s="38"/>
-      <c r="M6" s="32" t="s">
+      <c r="L6" s="37"/>
+      <c r="M6" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
     </row>
     <row r="7" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36" t="s">
+      <c r="D7" s="35"/>
+      <c r="E7" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36" t="s">
+      <c r="F7" s="35"/>
+      <c r="G7" s="35" t="s">
         <v>513</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37" t="s">
+      <c r="H7" s="36"/>
+      <c r="I7" s="36" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="33" t="s">
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32" t="s">
+      <c r="M7" s="31"/>
+      <c r="N7" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="O7" s="32"/>
-      <c r="P7" s="34" t="s">
+      <c r="O7" s="31"/>
+      <c r="P7" s="33" t="s">
         <v>544</v>
       </c>
-      <c r="Q7" s="34" t="s">
+      <c r="Q7" s="33" t="s">
         <v>547</v>
       </c>
-      <c r="R7" s="34" t="s">
+      <c r="R7" s="33" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29">
+      <c r="A8" s="28">
         <v>8</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39" t="s">
+      <c r="E8" s="35"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40" t="s">
+      <c r="I8" s="38"/>
+      <c r="J8" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="K8" s="41"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="41" t="s">
+      <c r="K8" s="40"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41" t="s">
+      <c r="N8" s="40"/>
+      <c r="O8" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
     </row>
     <row r="9" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>9</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38" t="s">
         <v>550</v>
       </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39" t="s">
+      <c r="F9" s="38"/>
+      <c r="G9" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39" t="s">
+      <c r="H9" s="38"/>
+      <c r="I9" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="33"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41" t="s">
+      <c r="L9" s="32"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="41"/>
-      <c r="P9" s="34" t="s">
+      <c r="O9" s="40"/>
+      <c r="P9" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
     </row>
     <row r="10" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29">
+      <c r="A10" s="28">
         <v>10</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="38" t="s">
         <v>500</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39" t="s">
+      <c r="E10" s="38"/>
+      <c r="F10" s="38" t="s">
         <v>560</v>
       </c>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39" t="s">
+      <c r="G10" s="38"/>
+      <c r="H10" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="39"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="41" t="s">
+      <c r="I10" s="38"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="40" t="s">
         <v>551</v>
       </c>
-      <c r="L10" s="33"/>
-      <c r="M10" s="41" t="s">
+      <c r="L10" s="32"/>
+      <c r="M10" s="40" t="s">
         <v>516</v>
       </c>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41" t="s">
+      <c r="N10" s="40"/>
+      <c r="O10" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="34" t="s">
+      <c r="P10" s="34"/>
+      <c r="Q10" s="33" t="s">
         <v>548</v>
       </c>
-      <c r="R10" s="35"/>
+      <c r="R10" s="34"/>
     </row>
     <row r="11" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="29">
+      <c r="A11" s="28">
         <v>11</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39" t="s">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39" t="s">
+      <c r="F11" s="38"/>
+      <c r="G11" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39" t="s">
+      <c r="H11" s="38"/>
+      <c r="I11" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="41" t="s">
+      <c r="J11" s="40" t="s">
         <v>543</v>
       </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
     </row>
     <row r="12" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="43"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
+      <c r="A12" s="42"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
     </row>
     <row r="13" spans="1:18" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44" t="s">
+      <c r="A13" s="42"/>
+      <c r="B13" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="47" t="s">
         <v>197</v>
       </c>
-      <c r="G13" s="49" t="s">
+      <c r="G13" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="H13" s="50" t="s">
+      <c r="H13" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3305,76 +3528,151 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="1" t="s">
-        <v>505</v>
-      </c>
+    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" t="s">
+        <v>451</v>
+      </c>
+      <c r="H5" t="s">
+        <v>253</v>
+      </c>
+      <c r="J5" t="s">
+        <v>450</v>
+      </c>
+      <c r="K5" t="s">
+        <v>450</v>
+      </c>
+      <c r="L5" t="s">
+        <v>253</v>
+      </c>
+      <c r="M5" t="s">
+        <v>204</v>
+      </c>
+      <c r="N5" t="s">
+        <v>254</v>
+      </c>
+      <c r="O5" t="s">
+        <v>452</v>
+      </c>
+      <c r="P5" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3384,6 +3682,85 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2675AC5-9914-48B9-9ACA-4BDCD651E70E}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="27.875" defaultRowHeight="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BAE26F-C7CF-476B-A8FD-762F3F557460}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="31.75" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3431,261 +3808,261 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="23.125" defaultRowHeight="60" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="23.125" style="51"/>
+    <col min="1" max="16384" width="23.125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="50" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="50" t="s">
         <v>495</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="50" t="s">
         <v>257</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="50" t="s">
         <v>259</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="50" t="s">
         <v>261</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="50" t="s">
         <v>262</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="50" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>272</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="50" t="s">
         <v>273</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="50" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="66" t="s">
         <v>282</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="51" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="50" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="50" t="s">
         <v>275</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="50" t="s">
         <v>276</v>
       </c>
-      <c r="K4" s="51" t="s">
+      <c r="K4" s="50" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="50" t="s">
         <v>280</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="50" t="s">
         <v>286</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="K5" s="50" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="50" t="s">
         <v>313</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="50" t="s">
         <v>278</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="50" t="s">
         <v>281</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="K6" s="51" t="s">
+      <c r="K6" s="50" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="50" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="50" t="s">
         <v>285</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="50" t="s">
         <v>496</v>
       </c>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="50" t="s">
         <v>308</v>
       </c>
-      <c r="J7" s="51" t="s">
+      <c r="J7" s="50" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="50" t="s">
         <v>498</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="50" t="s">
         <v>279</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="50" t="s">
         <v>497</v>
       </c>
-      <c r="I8" s="51" t="s">
+      <c r="I8" s="50" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="50" t="s">
         <v>312</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="50" t="s">
         <v>311</v>
       </c>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="50" t="s">
         <v>315</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F9" s="50" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="50" t="s">
         <v>511</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="50" t="s">
         <v>309</v>
       </c>
-      <c r="K10" s="51" t="s">
+      <c r="K10" s="50" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="51" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="51" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="51" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="51" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="51" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="51" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="51" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="51" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52"/>
+      <c r="A19" s="51"/>
     </row>
     <row r="20" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52"/>
+      <c r="A20" s="51"/>
     </row>
     <row r="21" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52"/>
+      <c r="A21" s="51"/>
     </row>
     <row r="22" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52"/>
+      <c r="A22" s="51"/>
     </row>
     <row r="23" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52"/>
+      <c r="A23" s="51"/>
     </row>
     <row r="24" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="54"/>
+      <c r="A24" s="52"/>
     </row>
     <row r="25" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="54"/>
+      <c r="A25" s="52"/>
     </row>
     <row r="26" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="54"/>
+      <c r="A26" s="52"/>
     </row>
     <row r="27" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="54"/>
+      <c r="A27" s="52"/>
     </row>
     <row r="28" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="54"/>
+      <c r="A28" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3707,670 +4084,670 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51"/>
-      <c r="B1" s="51" t="s">
+      <c r="A1" s="50"/>
+      <c r="B1" s="50" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="50" t="s">
         <v>341</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="50" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="53" t="s">
         <v>494</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="66" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="51" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="50" t="s">
         <v>301</v>
       </c>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51" t="s">
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="51"/>
+      <c r="M3" s="50"/>
     </row>
     <row r="4" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
     </row>
     <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
     </row>
     <row r="6" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="50" t="s">
         <v>510</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51" t="s">
+      <c r="E6" s="50"/>
+      <c r="F6" s="50" t="s">
         <v>243</v>
       </c>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51" t="s">
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50" t="s">
         <v>277</v>
       </c>
-      <c r="M6" s="51"/>
+      <c r="M6" s="50"/>
     </row>
     <row r="7" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51" t="s">
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="L7" s="51" t="s">
+      <c r="L7" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="51" t="s">
+      <c r="M7" s="50" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="66" t="s">
         <v>300</v>
       </c>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
     </row>
     <row r="9" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="50" t="s">
         <v>239</v>
       </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51" t="s">
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50" t="s">
         <v>302</v>
       </c>
-      <c r="J9" s="51" t="s">
+      <c r="J9" s="50" t="s">
         <v>303</v>
       </c>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51" t="s">
+      <c r="K9" s="50"/>
+      <c r="L9" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="M9" s="51"/>
+      <c r="M9" s="50"/>
     </row>
     <row r="10" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51" t="s">
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51" t="s">
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50" t="s">
         <v>304</v>
       </c>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
     </row>
     <row r="11" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51" t="s">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51" t="s">
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51" t="s">
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50" t="s">
         <v>234</v>
       </c>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51" t="s">
+      <c r="L11" s="50"/>
+      <c r="M11" s="50" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51" t="s">
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51" t="s">
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50" t="s">
         <v>227</v>
       </c>
-      <c r="M12" s="51"/>
+      <c r="M12" s="50"/>
     </row>
     <row r="13" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51" t="s">
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51" t="s">
+      <c r="J13" s="50"/>
+      <c r="K13" s="50" t="s">
         <v>219</v>
       </c>
-      <c r="L13" s="51"/>
-      <c r="M13" s="51"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
     </row>
     <row r="14" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51" t="s">
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51" t="s">
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50" t="s">
         <v>231</v>
       </c>
-      <c r="K14" s="51"/>
-      <c r="L14" s="51" t="s">
+      <c r="K14" s="50"/>
+      <c r="L14" s="50" t="s">
         <v>299</v>
       </c>
-      <c r="M14" s="51"/>
+      <c r="M14" s="50"/>
     </row>
     <row r="15" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="59" t="s">
+      <c r="A15" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51" t="s">
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50" t="s">
         <v>298</v>
       </c>
-      <c r="M15" s="51"/>
+      <c r="M15" s="50"/>
     </row>
     <row r="16" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51" t="s">
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50" t="s">
         <v>237</v>
       </c>
-      <c r="E16" s="51" t="s">
+      <c r="E16" s="50" t="s">
         <v>212</v>
       </c>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51" t="s">
+      <c r="F16" s="50"/>
+      <c r="G16" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
     </row>
     <row r="17" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51" t="s">
+      <c r="B17" s="50"/>
+      <c r="C17" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51" t="s">
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50" t="s">
         <v>235</v>
       </c>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51" t="s">
+      <c r="L17" s="50"/>
+      <c r="M17" s="50" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51" t="s">
+      <c r="B18" s="50"/>
+      <c r="C18" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="50" t="s">
         <v>223</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51" t="s">
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50" t="s">
         <v>305</v>
       </c>
-      <c r="J18" s="51" t="s">
+      <c r="J18" s="50" t="s">
         <v>306</v>
       </c>
-      <c r="K18" s="51" t="s">
+      <c r="K18" s="50" t="s">
         <v>340</v>
       </c>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51" t="s">
+      <c r="L18" s="50"/>
+      <c r="M18" s="50" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51" t="s">
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50" t="s">
         <v>290</v>
       </c>
-      <c r="H19" s="51" t="s">
+      <c r="H19" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
     </row>
     <row r="20" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51" t="s">
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51" t="s">
+      <c r="K20" s="50"/>
+      <c r="L20" s="50" t="s">
         <v>226</v>
       </c>
-      <c r="M20" s="51"/>
+      <c r="M20" s="50"/>
     </row>
     <row r="21" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51" t="s">
+      <c r="B21" s="50"/>
+      <c r="C21" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="50" t="s">
         <v>222</v>
       </c>
-      <c r="E21" s="51" t="s">
+      <c r="E21" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51" t="s">
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50" t="s">
         <v>342</v>
       </c>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
     </row>
     <row r="22" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="50" t="s">
         <v>221</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51" t="s">
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51" t="s">
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51" t="s">
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="J23" s="51" t="s">
+      <c r="J23" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="K23" s="51" t="s">
+      <c r="K23" s="50" t="s">
         <v>343</v>
       </c>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51" t="s">
+      <c r="L23" s="50"/>
+      <c r="M23" s="50" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51" t="s">
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50" t="s">
         <v>291</v>
       </c>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51" t="s">
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="M24" s="51"/>
+      <c r="M24" s="50"/>
     </row>
     <row r="25" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51" t="s">
+      <c r="B25" s="50"/>
+      <c r="C25" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51" t="s">
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50" t="s">
         <v>225</v>
       </c>
-      <c r="H25" s="51" t="s">
+      <c r="H25" s="50" t="s">
         <v>225</v>
       </c>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="51" t="s">
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="M25" s="51"/>
+      <c r="M25" s="50"/>
     </row>
     <row r="26" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="51" t="s">
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51" t="s">
+      <c r="B27" s="50"/>
+      <c r="C27" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="51" t="s">
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50" t="s">
         <v>307</v>
       </c>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51" t="s">
+      <c r="L27" s="50"/>
+      <c r="M27" s="50" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="62" t="s">
+      <c r="A28" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51" t="s">
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50" t="s">
         <v>292</v>
       </c>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="51"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4388,7 +4765,7 @@
   <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="61" t="s">
         <v>344</v>
       </c>
       <c r="B1" s="20"/>
@@ -4397,314 +4774,314 @@
       <c r="E1" s="20"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="64"/>
-      <c r="B2" s="64" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="62" t="s">
         <v>346</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="62" t="s">
         <v>347</v>
       </c>
-      <c r="D2" s="64"/>
+      <c r="D2" s="62"/>
       <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="62" t="s">
         <v>345</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64" t="s">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62" t="s">
         <v>348</v>
       </c>
-      <c r="D3" s="64"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="20"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64" t="s">
+      <c r="A4" s="62"/>
+      <c r="B4" s="62" t="s">
         <v>349</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="62" t="s">
         <v>350</v>
       </c>
-      <c r="D4" s="64"/>
+      <c r="D4" s="62"/>
       <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64" t="s">
+      <c r="A5" s="62"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62" t="s">
         <v>351</v>
       </c>
-      <c r="D5" s="64"/>
+      <c r="D5" s="62"/>
       <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65" t="s">
+      <c r="A6" s="63"/>
+      <c r="B6" s="63" t="s">
         <v>352</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="63" t="s">
         <v>353</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="D6" s="63" t="s">
         <v>354</v>
       </c>
-      <c r="E6" s="65"/>
+      <c r="E6" s="63"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="63" t="s">
         <v>355</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="63" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="63" t="s">
         <v>358</v>
       </c>
-      <c r="D7" s="65" t="s">
+      <c r="D7" s="63" t="s">
         <v>359</v>
       </c>
-      <c r="E7" s="65" t="s">
+      <c r="E7" s="63" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65" t="s">
+      <c r="A8" s="63"/>
+      <c r="B8" s="63" t="s">
         <v>360</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="63" t="s">
         <v>361</v>
       </c>
-      <c r="D8" s="65" t="s">
+      <c r="D8" s="63" t="s">
         <v>362</v>
       </c>
-      <c r="E8" s="65"/>
+      <c r="E8" s="63"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="65"/>
-      <c r="B9" s="65" t="s">
+      <c r="A9" s="63"/>
+      <c r="B9" s="63" t="s">
         <v>363</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="63" t="s">
         <v>364</v>
       </c>
-      <c r="D9" s="65" t="s">
+      <c r="D9" s="63" t="s">
         <v>365</v>
       </c>
-      <c r="E9" s="65"/>
+      <c r="E9" s="63"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65" t="s">
+      <c r="A10" s="63"/>
+      <c r="B10" s="63" t="s">
         <v>366</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="63" t="s">
         <v>367</v>
       </c>
-      <c r="D10" s="65" t="s">
+      <c r="D10" s="63" t="s">
         <v>368</v>
       </c>
-      <c r="E10" s="65"/>
+      <c r="E10" s="63"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="65"/>
-      <c r="B11" s="65" t="s">
+      <c r="A11" s="63"/>
+      <c r="B11" s="63" t="s">
         <v>369</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="63" t="s">
         <v>370</v>
       </c>
-      <c r="D11" s="65" t="s">
+      <c r="D11" s="63" t="s">
         <v>371</v>
       </c>
-      <c r="E11" s="65"/>
+      <c r="E11" s="63"/>
     </row>
     <row r="12" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="64" t="s">
         <v>372</v>
       </c>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="64" t="s">
         <v>373</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>374</v>
       </c>
-      <c r="D12" s="66" t="s">
+      <c r="D12" s="64" t="s">
         <v>375</v>
       </c>
-      <c r="E12" s="66" t="s">
+      <c r="E12" s="64" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="66"/>
-      <c r="B13" s="66" t="s">
+      <c r="A13" s="64"/>
+      <c r="B13" s="64" t="s">
         <v>377</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="64" t="s">
         <v>378</v>
       </c>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
     </row>
     <row r="14" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="64" t="s">
         <v>379</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="64" t="s">
         <v>380</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="64" t="s">
         <v>381</v>
       </c>
-      <c r="D14" s="66" t="s">
+      <c r="D14" s="64" t="s">
         <v>382</v>
       </c>
-      <c r="E14" s="66"/>
+      <c r="E14" s="64"/>
     </row>
     <row r="15" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="66"/>
-      <c r="B15" s="66" t="s">
+      <c r="A15" s="64"/>
+      <c r="B15" s="64" t="s">
         <v>383</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>384</v>
       </c>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="66" t="s">
+      <c r="A16" s="64" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="66"/>
-      <c r="B17" s="66" t="s">
+      <c r="A17" s="64"/>
+      <c r="B17" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="64" t="s">
         <v>398</v>
       </c>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="64" t="s">
         <v>386</v>
       </c>
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="64" t="s">
         <v>392</v>
       </c>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="66"/>
-      <c r="B19" s="66" t="s">
+      <c r="A19" s="64"/>
+      <c r="B19" s="64" t="s">
         <v>393</v>
       </c>
-      <c r="C19" s="66" t="s">
+      <c r="C19" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="D19" s="66" t="s">
+      <c r="D19" s="64" t="s">
         <v>400</v>
       </c>
-      <c r="E19" s="66" t="s">
+      <c r="E19" s="64" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="66"/>
-      <c r="B20" s="66" t="s">
+      <c r="A20" s="64"/>
+      <c r="B20" s="64" t="s">
         <v>394</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="64" t="s">
         <v>402</v>
       </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="66" t="s">
+      <c r="A21" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="64" t="s">
         <v>395</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="64" t="s">
         <v>403</v>
       </c>
-      <c r="D21" s="66" t="s">
+      <c r="D21" s="64" t="s">
         <v>404</v>
       </c>
-      <c r="E21" s="66"/>
+      <c r="E21" s="64"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="66" t="s">
+      <c r="A22" s="64" t="s">
         <v>388</v>
       </c>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="64" t="s">
         <v>396</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="64" t="s">
         <v>405</v>
       </c>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
     </row>
     <row r="23" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="66"/>
-      <c r="B23" s="66" t="s">
+      <c r="A23" s="64"/>
+      <c r="B23" s="64" t="s">
         <v>397</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="64" t="s">
         <v>406</v>
       </c>
-      <c r="D23" s="66" t="s">
+      <c r="D23" s="64" t="s">
         <v>410</v>
       </c>
-      <c r="E23" s="66"/>
+      <c r="E23" s="64"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="64" t="s">
         <v>389</v>
       </c>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="64" t="s">
         <v>536</v>
       </c>
-      <c r="C24" s="66" t="s">
+      <c r="C24" s="64" t="s">
         <v>407</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="D24" s="64" t="s">
         <v>408</v>
       </c>
-      <c r="E24" s="66" t="s">
+      <c r="E24" s="64" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="64" t="s">
         <v>532</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="64" t="s">
         <v>533</v>
       </c>
-      <c r="D25" s="66" t="s">
+      <c r="D25" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="E25" s="66" t="s">
+      <c r="E25" s="64" t="s">
         <v>535</v>
       </c>
     </row>
@@ -4810,30 +5187,30 @@
       <c r="A1" s="19" t="s">
         <v>555</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28" t="s">
+      <c r="C1" s="67"/>
+      <c r="D1" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28" t="s">
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
     </row>
     <row r="2" spans="1:17" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19"/>
@@ -5509,6 +5886,328 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF92F2CA-29A6-4C2C-9AA2-481D5812D9FC}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="29.375" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="29.375" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="69" t="s">
+        <v>565</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>603</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>600</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>605</v>
+      </c>
+      <c r="F1" s="75" t="s">
+        <v>597</v>
+      </c>
+      <c r="G1" s="75" t="s">
+        <v>604</v>
+      </c>
+      <c r="H1" s="73" t="s">
+        <v>579</v>
+      </c>
+      <c r="I1" s="73" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" s="73" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="69" t="s">
+        <v>566</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>590</v>
+      </c>
+      <c r="D2" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="G2" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="H2" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="I2" s="70" t="s">
+        <v>577</v>
+      </c>
+      <c r="J2" s="71" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="69" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="F3" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="G3" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="I3" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="J3" s="71" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="69" t="s">
+        <v>568</v>
+      </c>
+      <c r="B4" s="70" t="s">
+        <v>581</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>571</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>599</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>593</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>465</v>
+      </c>
+      <c r="I4" s="70" t="s">
+        <v>588</v>
+      </c>
+      <c r="J4" s="70" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="70" t="s">
+        <v>575</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>601</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>586</v>
+      </c>
+      <c r="F5" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="G5" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="H5" s="70" t="s">
+        <v>585</v>
+      </c>
+      <c r="I5" s="70" t="s">
+        <v>572</v>
+      </c>
+      <c r="J5" s="71" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="29" t="s">
+        <v>574</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>594</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>595</v>
+      </c>
+      <c r="F6" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="G6" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="H6" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="I6" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="J6" s="72" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="69" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" s="70" t="s">
+        <v>581</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>591</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>602</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>587</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>599</v>
+      </c>
+      <c r="G7" s="70" t="s">
+        <v>423</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>465</v>
+      </c>
+      <c r="I7" s="70" t="s">
+        <v>588</v>
+      </c>
+      <c r="J7" s="71" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="70" t="s">
+        <v>582</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>598</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>584</v>
+      </c>
+      <c r="H8" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="I8" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="J8" s="70" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="70" t="s">
+        <v>575</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="D9" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>586</v>
+      </c>
+      <c r="F9" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="H9" s="70" t="s">
+        <v>465</v>
+      </c>
+      <c r="I9" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="J9" s="71" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="69" t="s">
+        <v>570</v>
+      </c>
+      <c r="B10" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>573</v>
+      </c>
+      <c r="F10" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="G10" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>592</v>
+      </c>
+      <c r="I10" s="71" t="s">
+        <v>576</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB1C697-67FB-443F-8AB8-2C5FFD2F2A32}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5781,158 +6480,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD81312-882A-486A-ADF8-D79AE3D92F2E}">
-  <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="15.875" defaultRowHeight="38.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>447</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>448</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G5" t="s">
-        <v>451</v>
-      </c>
-      <c r="H5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J5" t="s">
-        <v>450</v>
-      </c>
-      <c r="K5" t="s">
-        <v>450</v>
-      </c>
-      <c r="L5" t="s">
-        <v>253</v>
-      </c>
-      <c r="M5" t="s">
-        <v>204</v>
-      </c>
-      <c r="N5" t="s">
-        <v>254</v>
-      </c>
-      <c r="O5" t="s">
-        <v>452</v>
-      </c>
-      <c r="P5" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>